--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -861,12 +861,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2204,8 +2204,8 @@
       <c r="K14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L14" s="12" t="b">
-        <v>1</v>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M14" s="12"/>
       <c r="N14" s="4" t="s">

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -861,12 +861,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2204,8 +2204,8 @@
       <c r="K14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L14" s="2" t="b">
-        <v>0</v>
+      <c r="L14" s="12" t="b">
+        <v>1</v>
       </c>
       <c r="M14" s="12"/>
       <c r="N14" s="4" t="s">
@@ -2749,8 +2749,8 @@
       <c r="K28" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L28" s="2" t="b">
-        <v>0</v>
+      <c r="L28" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>40</v>
@@ -3091,8 +3091,8 @@
       <c r="K38" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L38" s="14" t="b">
-        <v>1</v>
+      <c r="L38" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>40</v>
@@ -3126,8 +3126,8 @@
       <c r="K39" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L39" s="14" t="b">
-        <v>1</v>
+      <c r="L39" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>40</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -169,6 +169,8 @@
 1：显示在大厅对应位置
 2：显示在游戏界面对应位置
 3：显示在登陆界面对应位置
+4：显示在活动页面（仅限web端)
+5:显示在最下方导航栏（仅限web端）
 参数：位置1_位置2  即 大厅显示_游戏界面显示</t>
         </r>
       </text>
@@ -861,12 +863,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1851,7 +1853,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" ht="22" customHeight="1" spans="1:14">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -169,6 +169,8 @@
 1：显示在大厅对应位置
 2：显示在游戏界面对应位置
 3：显示在登陆界面对应位置
+4：显示在活动页面（仅限web端）
+5: 显示在最下方导航栏（仅限web端）
 参数：位置1_位置2  即 大厅显示_游戏界面显示</t>
         </r>
       </text>
@@ -321,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="141">
   <si>
     <t>id</t>
   </si>
@@ -359,6 +361,12 @@
     <t>提示文本ID</t>
   </si>
   <si>
+    <t>web活动宣传图</t>
+  </si>
+  <si>
+    <t>web触发弹出对应活动</t>
+  </si>
+  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -410,6 +418,12 @@
     <t>tips</t>
   </si>
   <si>
+    <t>webimg</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
     <t>client</t>
   </si>
   <si>
@@ -443,6 +457,9 @@
     <t>官方派奖</t>
   </si>
   <si>
+    <t>Grid (27)</t>
+  </si>
+  <si>
     <t>显示位置：大厅</t>
   </si>
   <si>
@@ -455,6 +472,9 @@
     <t>分享推广</t>
   </si>
   <si>
+    <t>Grid (28)</t>
+  </si>
+  <si>
     <t>VIP功能</t>
   </si>
   <si>
@@ -654,6 +674,78 @@
   </si>
   <si>
     <t>Grid (26)</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>tap_home</t>
+  </si>
+  <si>
+    <t>活动</t>
+  </si>
+  <si>
+    <t>tap_activity</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>btn_shop</t>
+  </si>
+  <si>
+    <t>赌场</t>
+  </si>
+  <si>
+    <t>btn_casino</t>
+  </si>
+  <si>
+    <t>创房间</t>
+  </si>
+  <si>
+    <t>btn_create</t>
+  </si>
+  <si>
+    <t>sc-7</t>
+  </si>
+  <si>
+    <t>btn_first</t>
+  </si>
+  <si>
+    <t>djlb-3</t>
+  </si>
+  <si>
+    <t>btn_stage_rechare</t>
+  </si>
+  <si>
+    <t>qtlc-6</t>
+  </si>
+  <si>
+    <t>btn_first_daily</t>
+  </si>
+  <si>
+    <t>mrjj-5</t>
+  </si>
+  <si>
+    <t>btn_privilege</t>
+  </si>
+  <si>
+    <t>cqg-1</t>
+  </si>
+  <si>
+    <t>btn_pig</t>
+  </si>
+  <si>
+    <t>czjj-2</t>
+  </si>
+  <si>
+    <t>btn_growth_fund</t>
+  </si>
+  <si>
+    <t>ggk-4</t>
+  </si>
+  <si>
+    <t>btn_lottery</t>
   </si>
 </sst>
 </file>
@@ -1709,7 +1801,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1724,12 +1816,12 @@
     <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
     <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
     <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="14" max="14" width="26" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="4"/>
+    <col min="13" max="15" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="16" max="16" width="26" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:16">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1769,89 +1861,107 @@
       <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:14">
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:16">
       <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>13</v>
-      </c>
       <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="K2" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:14">
+        <v>15</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:16">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1861,50 +1971,58 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="N4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="12"/>
-      <c r="N5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1913,66 +2031,74 @@
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L6" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M6" s="12"/>
-      <c r="N6" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
       <c r="C7" s="12">
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="12"/>
+        <v>43</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>44</v>
+      </c>
       <c r="F7" s="12"/>
       <c r="G7" s="13">
         <v>1</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L7" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M7" s="12"/>
-      <c r="N7" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -1981,10 +2107,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -1994,67 +2120,75 @@
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L8" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M8" s="12"/>
-      <c r="N8" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="12">
         <v>5</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
       <c r="C9" s="12">
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="12"/>
+        <v>48</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="F9" s="12"/>
       <c r="G9" s="13">
         <v>1</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L9" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M9" s="12"/>
-      <c r="N9" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -2062,30 +2196,32 @@
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L10" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M10" s="12"/>
-      <c r="N10" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="12">
         <v>7</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -2094,30 +2230,32 @@
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L11" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M11" s="12"/>
-      <c r="N11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="12">
         <v>8</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2126,55 +2264,59 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L12" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M12" s="12"/>
-      <c r="N12" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="12">
         <v>9</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L13" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M13" s="12"/>
-      <c r="N13" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2183,10 +2325,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2196,23 +2338,25 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L14" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M14" s="12"/>
-      <c r="N14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="14">
         <v>101</v>
       </c>
@@ -2221,10 +2365,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2234,13 +2378,13 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L15" s="14" t="b">
         <v>1</v>
@@ -2248,11 +2392,13 @@
       <c r="M15" s="14">
         <v>47061</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="14">
         <v>102</v>
       </c>
@@ -2263,10 +2409,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2276,23 +2422,25 @@
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L16" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M16" s="14"/>
-      <c r="N16" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="14">
         <v>103</v>
       </c>
@@ -2303,10 +2451,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2316,23 +2464,25 @@
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L17" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M17" s="14"/>
-      <c r="N17" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="14">
         <v>104</v>
       </c>
@@ -2343,10 +2493,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2356,23 +2506,25 @@
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L18" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M18" s="14"/>
-      <c r="N18" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -2381,10 +2533,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2394,23 +2546,25 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L19" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M19" s="14"/>
-      <c r="N19" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="14">
         <v>106</v>
       </c>
@@ -2421,10 +2575,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2434,23 +2588,25 @@
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L20" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M20" s="14"/>
-      <c r="N20" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="14">
         <v>107</v>
       </c>
@@ -2461,10 +2617,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2474,23 +2630,25 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L21" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M21" s="14"/>
-      <c r="N21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="14">
         <v>108</v>
       </c>
@@ -2501,10 +2659,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2514,23 +2672,25 @@
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L22" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M22" s="14"/>
-      <c r="N22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="14">
         <v>109</v>
       </c>
@@ -2539,10 +2699,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2552,23 +2712,25 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L23" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M23" s="14"/>
-      <c r="N23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="14">
         <v>110</v>
       </c>
@@ -2577,10 +2739,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2590,23 +2752,25 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L24" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="14">
         <v>111</v>
       </c>
@@ -2615,10 +2779,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2628,23 +2792,25 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L25" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M25" s="14"/>
-      <c r="N25" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="14">
         <v>112</v>
       </c>
@@ -2653,10 +2819,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2666,23 +2832,25 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L26" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M26" s="14"/>
-      <c r="N26" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:14">
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:16">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2691,10 +2859,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2704,22 +2872,22 @@
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:14">
+      <c r="P27" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:16">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2728,10 +2896,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2741,22 +2909,22 @@
       </c>
       <c r="H28" s="19"/>
       <c r="I28" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L28" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="N28" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:14">
+      <c r="P28" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:16">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2765,10 +2933,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2778,22 +2946,22 @@
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:14">
+      <c r="P29" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:16">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2802,10 +2970,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2815,22 +2983,22 @@
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:14">
+      <c r="P30" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:16">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2839,10 +3007,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2852,22 +3020,22 @@
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N31" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:14">
+      <c r="P31" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:16">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2876,10 +3044,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2889,22 +3057,22 @@
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:14">
+      <c r="P32" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:16">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -2912,10 +3080,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2925,22 +3093,22 @@
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="P33" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -2949,10 +3117,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2962,23 +3130,25 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L34" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M34" s="3"/>
-      <c r="N34" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="4">
         <v>121</v>
       </c>
@@ -2986,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -2995,43 +3165,45 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="2"/>
-      <c r="N35" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" s="4">
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:16">
       <c r="A37" s="4">
         <v>123</v>
       </c>
@@ -3039,10 +3211,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F37" s="4">
         <v>24</v>
@@ -3051,19 +3223,19 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L37" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:16">
       <c r="A38" s="4">
         <v>124</v>
       </c>
@@ -3071,10 +3243,10 @@
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F38" s="4">
         <v>25</v>
@@ -3083,22 +3255,22 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L38" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="P38" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" s="4">
         <v>125</v>
       </c>
@@ -3106,10 +3278,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F39" s="4">
         <v>26</v>
@@ -3118,19 +3290,523 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L39" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N39" s="2" t="s">
-        <v>40</v>
+      <c r="P39" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:16">
+      <c r="A40" s="4">
+        <v>1001</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5">
+        <v>5</v>
+      </c>
+      <c r="H40" s="5"/>
+      <c r="I40" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L40" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:16">
+      <c r="A41" s="4">
+        <v>1002</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="4">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5">
+        <v>5</v>
+      </c>
+      <c r="H41" s="5"/>
+      <c r="I41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:16">
+      <c r="A42" s="4">
+        <v>1003</v>
+      </c>
+      <c r="B42" s="4">
+        <v>1</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="4">
+        <v>3</v>
+      </c>
+      <c r="G42" s="5">
+        <v>5</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="I42" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:16">
+      <c r="A43" s="4">
+        <v>1004</v>
+      </c>
+      <c r="B43" s="4">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="4">
+        <v>4</v>
+      </c>
+      <c r="G43" s="5">
+        <v>5</v>
+      </c>
+      <c r="H43" s="5"/>
+      <c r="I43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:16">
+      <c r="A44" s="4">
+        <v>1005</v>
+      </c>
+      <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="4">
+        <v>5</v>
+      </c>
+      <c r="G44" s="5">
+        <v>5</v>
+      </c>
+      <c r="H44" s="5"/>
+      <c r="I44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:16">
+      <c r="A45" s="4">
+        <v>2001</v>
+      </c>
+      <c r="B45" s="4">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4">
+        <v>11</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5">
+        <v>4</v>
+      </c>
+      <c r="H45" s="5"/>
+      <c r="I45" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:16">
+      <c r="A46" s="4">
+        <v>2002</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4">
+        <v>2</v>
+      </c>
+      <c r="G46" s="5">
+        <v>4</v>
+      </c>
+      <c r="H46" s="5"/>
+      <c r="I46" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:16">
+      <c r="A47" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" s="18"/>
+      <c r="F47" s="4">
+        <v>3</v>
+      </c>
+      <c r="G47" s="19">
+        <v>4</v>
+      </c>
+      <c r="H47" s="19"/>
+      <c r="I47" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:16">
+      <c r="A48" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B48" s="4">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4">
+        <v>2</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4">
+        <v>4</v>
+      </c>
+      <c r="G48" s="5">
+        <v>4</v>
+      </c>
+      <c r="H48" s="5"/>
+      <c r="I48" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:16">
+      <c r="A49" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B49" s="14">
+        <v>1</v>
+      </c>
+      <c r="C49" s="14">
+        <v>4</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="14"/>
+      <c r="F49" s="4">
+        <v>5</v>
+      </c>
+      <c r="G49" s="15">
+        <v>4</v>
+      </c>
+      <c r="H49" s="15"/>
+      <c r="I49" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="O49" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:16">
+      <c r="A50" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B50" s="14">
+        <v>1</v>
+      </c>
+      <c r="C50" s="14">
+        <v>15</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14">
+        <v>6</v>
+      </c>
+      <c r="G50" s="15">
+        <v>4</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L50" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="O50" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:16">
+      <c r="A51" s="4">
+        <v>2007</v>
+      </c>
+      <c r="B51" s="14">
+        <v>1</v>
+      </c>
+      <c r="C51" s="14">
+        <v>5</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14">
+        <v>7</v>
+      </c>
+      <c r="G51" s="15">
+        <v>4</v>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L51" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" s="14"/>
+      <c r="N51" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="O51" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -472,6 +472,9 @@
     <t>1_15;3_1</t>
   </si>
   <si>
+    <t>AND(playerLevel(1),playerVipLevel(1))</t>
+  </si>
+  <si>
     <t>AND(playerLevel(15),playerVipLevel(1))</t>
   </si>
   <si>
@@ -493,60 +496,60 @@
     <t>1_20</t>
   </si>
   <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>刮刮乐</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
+    <t>等级礼包</t>
+  </si>
+  <si>
+    <t>Grid (2)</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
+    <t>首充礼包</t>
+  </si>
+  <si>
+    <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>remainingAttempts(57011,1,1)</t>
+  </si>
+  <si>
+    <t>成长基金</t>
+  </si>
+  <si>
+    <t>Grid (1)</t>
+  </si>
+  <si>
+    <t>1_10</t>
+  </si>
+  <si>
     <t>playerLevel(10)</t>
   </si>
   <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>刮刮乐</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>储钱罐</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
-    <t>等级礼包</t>
-  </si>
-  <si>
-    <t>Grid (2)</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>playerLevel(30)</t>
-  </si>
-  <si>
-    <t>首充礼包</t>
-  </si>
-  <si>
-    <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>remainingAttempts(57011,1,1)</t>
-  </si>
-  <si>
-    <t>成长基金</t>
-  </si>
-  <si>
-    <t>Grid (1)</t>
-  </si>
-  <si>
-    <t>1_10</t>
-  </si>
-  <si>
     <t>签到奖励</t>
   </si>
   <si>
@@ -656,6 +659,84 @@
   </si>
   <si>
     <t>Grid (26)</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>tap_home</t>
+  </si>
+  <si>
+    <t>活动</t>
+  </si>
+  <si>
+    <t>tap_activity</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>btn_shop</t>
+  </si>
+  <si>
+    <t>赌场</t>
+  </si>
+  <si>
+    <t>btn_casino</t>
+  </si>
+  <si>
+    <t>创房间</t>
+  </si>
+  <si>
+    <t>btn_create</t>
+  </si>
+  <si>
+    <t>sc-7</t>
+  </si>
+  <si>
+    <t>btn_first</t>
+  </si>
+  <si>
+    <t>djlb-3</t>
+  </si>
+  <si>
+    <t>btn_stage_rechare</t>
+  </si>
+  <si>
+    <t>qtlc-6</t>
+  </si>
+  <si>
+    <t>btn_first_daily</t>
+  </si>
+  <si>
+    <t>mrjj-5</t>
+  </si>
+  <si>
+    <t>btn_privilege</t>
+  </si>
+  <si>
+    <t>cqg-1</t>
+  </si>
+  <si>
+    <t>btn_pig</t>
+  </si>
+  <si>
+    <t>czjj-2</t>
+  </si>
+  <si>
+    <t>btn_growth_fund</t>
+  </si>
+  <si>
+    <t>ggk-4</t>
+  </si>
+  <si>
+    <t>btn_lottery</t>
+  </si>
+  <si>
+    <t>充值引导</t>
+  </si>
+  <si>
+    <t>NOT(accountTotalRecharge(0.001))</t>
   </si>
 </sst>
 </file>
@@ -1711,7 +1792,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -2134,7 +2215,7 @@
         <v>49</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L12" s="12" t="b">
         <v>1</v>
@@ -2151,7 +2232,7 @@
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -2185,10 +2266,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2223,10 +2304,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2236,10 +2317,10 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>57</v>
@@ -2479,10 +2560,10 @@
         <v>73</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L21" s="14" t="b">
         <v>1</v>
@@ -2503,10 +2584,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2541,10 +2622,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2579,10 +2660,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2617,10 +2698,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2643,7 +2724,7 @@
       </c>
       <c r="M25" s="14"/>
       <c r="N25" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2655,10 +2736,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2693,10 +2774,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2706,13 +2787,13 @@
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
@@ -2730,10 +2811,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2767,10 +2848,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2780,13 +2861,13 @@
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
@@ -2804,10 +2885,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2817,13 +2898,13 @@
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
@@ -2841,10 +2922,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2854,13 +2935,13 @@
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
@@ -2878,10 +2959,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2891,13 +2972,13 @@
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
@@ -2906,7 +2987,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" s="3" customFormat="1" spans="1:14">
+    <row r="33" s="3" customFormat="1" spans="1:16">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -2914,10 +2995,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -2942,7 +3023,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:16">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -2951,10 +3032,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -2980,7 +3061,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:16">
       <c r="A35" s="4">
         <v>121</v>
       </c>
@@ -2988,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -3013,12 +3094,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:16">
       <c r="A36" s="4">
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>33</v>
@@ -3033,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:16">
       <c r="A37" s="4">
         <v>123</v>
       </c>
@@ -3041,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F37" s="4">
         <v>24</v>
@@ -3065,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:16">
       <c r="A38" s="4">
         <v>124</v>
       </c>
@@ -3073,10 +3154,10 @@
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F38" s="4">
         <v>25</v>
@@ -3100,7 +3181,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:16">
       <c r="A39" s="4">
         <v>125</v>
       </c>
@@ -3108,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F39" s="4">
         <v>26</v>
@@ -3133,6 +3214,488 @@
       </c>
       <c r="N39" s="2" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="4">
+        <v>1001</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5">
+        <v>5</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="4">
+        <v>1002</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" s="4">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5">
+        <v>5</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="4">
+        <v>1003</v>
+      </c>
+      <c r="B42" s="4">
+        <v>1</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" s="4">
+        <v>3</v>
+      </c>
+      <c r="G42" s="5">
+        <v>5</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="4">
+        <v>1004</v>
+      </c>
+      <c r="B43" s="4">
+        <v>1</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="4">
+        <v>4</v>
+      </c>
+      <c r="G43" s="5">
+        <v>5</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="4">
+        <v>1005</v>
+      </c>
+      <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="4">
+        <v>5</v>
+      </c>
+      <c r="G44" s="5">
+        <v>5</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="4">
+        <v>2001</v>
+      </c>
+      <c r="B45" s="4">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4">
+        <v>11</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5">
+        <v>4</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="4">
+        <v>2002</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2</v>
+      </c>
+      <c r="G46" s="5">
+        <v>4</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" s="4">
+        <v>3</v>
+      </c>
+      <c r="G47" s="5">
+        <v>4</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B48" s="4">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4">
+        <v>2</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="4">
+        <v>4</v>
+      </c>
+      <c r="G48" s="5">
+        <v>4</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B49" s="4">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4">
+        <v>4</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="4">
+        <v>5</v>
+      </c>
+      <c r="G49" s="5">
+        <v>4</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B50" s="4">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4">
+        <v>15</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="4">
+        <v>6</v>
+      </c>
+      <c r="G50" s="5">
+        <v>4</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="4">
+        <v>2007</v>
+      </c>
+      <c r="B51" s="4">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4">
+        <v>5</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="4">
+        <v>7</v>
+      </c>
+      <c r="G51" s="5">
+        <v>4</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="4">
+        <v>126</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -3691,8 +3691,8 @@
       <c r="K52" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="L52" s="2" t="b">
-        <v>0</v>
+      <c r="L52" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="N52" s="4" t="s">
         <v>35</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -169,8 +169,8 @@
 1：显示在大厅对应位置
 2：显示在游戏界面对应位置
 3：显示在登陆界面对应位置
-4：显示在活动页面（仅限web端)
-5:显示在最下方导航栏（仅限web端）
+4：显示在活动页面（仅限web端）
+5: 显示在最下方导航栏（仅限web端）
 参数：位置1_位置2  即 大厅显示_游戏界面显示</t>
         </r>
       </text>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="142">
   <si>
     <t>id</t>
   </si>
@@ -361,6 +361,12 @@
     <t>提示文本ID</t>
   </si>
   <si>
+    <t>web活动宣传图</t>
+  </si>
+  <si>
+    <t>web触发弹出对应活动</t>
+  </si>
+  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -412,6 +418,12 @@
     <t>tips</t>
   </si>
   <si>
+    <t>webimg</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
     <t>client</t>
   </si>
   <si>
@@ -445,6 +457,9 @@
     <t>官方派奖</t>
   </si>
   <si>
+    <t>Grid (27)</t>
+  </si>
+  <si>
     <t>显示位置：大厅</t>
   </si>
   <si>
@@ -457,6 +472,9 @@
     <t>分享推广</t>
   </si>
   <si>
+    <t>Grid (28)</t>
+  </si>
+  <si>
     <t>VIP功能</t>
   </si>
   <si>
@@ -472,6 +490,9 @@
     <t>1_15;3_1</t>
   </si>
   <si>
+    <t>AND(playerLevel(1),playerVipLevel(1))</t>
+  </si>
+  <si>
     <t>AND(playerLevel(15),playerVipLevel(1))</t>
   </si>
   <si>
@@ -493,60 +514,60 @@
     <t>1_20</t>
   </si>
   <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>刮刮乐</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
+    <t>等级礼包</t>
+  </si>
+  <si>
+    <t>Grid (2)</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
+    <t>首充礼包</t>
+  </si>
+  <si>
+    <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>remainingAttempts(57011,1,1)</t>
+  </si>
+  <si>
+    <t>成长基金</t>
+  </si>
+  <si>
+    <t>Grid (1)</t>
+  </si>
+  <si>
+    <t>1_10</t>
+  </si>
+  <si>
     <t>playerLevel(10)</t>
   </si>
   <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>刮刮乐</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>储钱罐</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
-    <t>等级礼包</t>
-  </si>
-  <si>
-    <t>Grid (2)</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>playerLevel(30)</t>
-  </si>
-  <si>
-    <t>首充礼包</t>
-  </si>
-  <si>
-    <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>remainingAttempts(57011,1,1)</t>
-  </si>
-  <si>
-    <t>成长基金</t>
-  </si>
-  <si>
-    <t>Grid (1)</t>
-  </si>
-  <si>
-    <t>1_10</t>
-  </si>
-  <si>
     <t>签到奖励</t>
   </si>
   <si>
@@ -656,6 +677,78 @@
   </si>
   <si>
     <t>Grid (26)</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>tap_home</t>
+  </si>
+  <si>
+    <t>活动</t>
+  </si>
+  <si>
+    <t>tap_activity</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>btn_shop</t>
+  </si>
+  <si>
+    <t>赌场</t>
+  </si>
+  <si>
+    <t>btn_casino</t>
+  </si>
+  <si>
+    <t>创房间</t>
+  </si>
+  <si>
+    <t>btn_create</t>
+  </si>
+  <si>
+    <t>sc-7</t>
+  </si>
+  <si>
+    <t>btn_first</t>
+  </si>
+  <si>
+    <t>djlb-3</t>
+  </si>
+  <si>
+    <t>btn_stage_rechare</t>
+  </si>
+  <si>
+    <t>qtlc-6</t>
+  </si>
+  <si>
+    <t>btn_first_daily</t>
+  </si>
+  <si>
+    <t>mrjj-5</t>
+  </si>
+  <si>
+    <t>btn_privilege</t>
+  </si>
+  <si>
+    <t>cqg-1</t>
+  </si>
+  <si>
+    <t>btn_pig</t>
+  </si>
+  <si>
+    <t>czjj-2</t>
+  </si>
+  <si>
+    <t>btn_growth_fund</t>
+  </si>
+  <si>
+    <t>ggk-4</t>
+  </si>
+  <si>
+    <t>btn_lottery</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1429,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1347,6 +1440,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1399,6 +1495,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1711,980 +1810,1056 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
-    <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="14" max="14" width="26" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="19.7" style="6" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="36.6083333333333" style="5" customWidth="1"/>
+    <col min="11" max="11" width="40.375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="5" customWidth="1"/>
+    <col min="13" max="15" width="11.9083333333333" style="5" customWidth="1"/>
+    <col min="16" max="16" width="26" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:16">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:14">
-      <c r="A2" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="6" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:16">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="F2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:14">
-      <c r="A3" s="6" t="s">
+      <c r="H2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:16">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="J3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="K3" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:14">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="9" t="s">
+      <c r="L3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="M3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="12">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12" t="s">
+      <c r="N3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13" t="s">
+      <c r="O3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="12" t="s">
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>34</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="13">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="12">
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13">
         <v>3</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="12" t="s">
+      <c r="H6" s="14"/>
+      <c r="I6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="13">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13">
+        <v>9</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="12">
+      <c r="J7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="13">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="13">
+        <v>5</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="13">
+        <v>5</v>
+      </c>
+      <c r="B9" s="13">
+        <v>1</v>
+      </c>
+      <c r="C9" s="13">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="13">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="13">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14">
+        <v>1</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="13">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14">
+        <v>1</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="13">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="13">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="13">
+        <v>4</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="15">
+        <v>101</v>
+      </c>
+      <c r="B15" s="15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15">
+        <v>47061</v>
+      </c>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="15">
+        <v>102</v>
+      </c>
+      <c r="B16" s="15">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="15">
+        <v>2</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="16"/>
+      <c r="I16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="15">
+        <v>103</v>
+      </c>
+      <c r="B17" s="15">
+        <v>1</v>
+      </c>
+      <c r="C17" s="15">
+        <v>5</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="15">
+        <v>9</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="15">
+        <v>104</v>
+      </c>
+      <c r="B18" s="15">
+        <v>1</v>
+      </c>
+      <c r="C18" s="15">
+        <v>4</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="15">
         <v>3</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12">
-        <v>9</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="G18" s="16">
+        <v>1</v>
+      </c>
+      <c r="H18" s="16"/>
+      <c r="I18" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="12">
-        <v>4</v>
-      </c>
-      <c r="B8" s="12">
-        <v>1</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12" t="s">
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="15">
+        <v>105</v>
+      </c>
+      <c r="B19" s="15">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="15">
+        <v>6</v>
+      </c>
+      <c r="G19" s="16">
+        <v>1</v>
+      </c>
+      <c r="H19" s="16"/>
+      <c r="I19" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="15">
+        <v>106</v>
+      </c>
+      <c r="B20" s="15">
+        <v>1</v>
+      </c>
+      <c r="C20" s="15">
+        <v>11</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="15">
+        <v>7</v>
+      </c>
+      <c r="G20" s="16">
+        <v>1</v>
+      </c>
+      <c r="H20" s="16"/>
+      <c r="I20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="12">
-        <v>5</v>
-      </c>
-      <c r="G8" s="13">
-        <v>1</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="12">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12">
-        <v>6</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="12">
-        <v>6</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="J20" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13">
-        <v>1</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="12">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="12">
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="15">
+        <v>107</v>
+      </c>
+      <c r="B21" s="15">
+        <v>1</v>
+      </c>
+      <c r="C21" s="15">
+        <v>15</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="15">
         <v>8</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13">
-        <v>1</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="12">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="12">
+      <c r="G21" s="16">
+        <v>1</v>
+      </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="15">
+        <v>108</v>
+      </c>
+      <c r="B22" s="15">
+        <v>1</v>
+      </c>
+      <c r="C22" s="15">
         <v>10</v>
       </c>
-      <c r="B14" s="12">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="12">
-        <v>4</v>
-      </c>
-      <c r="G14" s="13">
-        <v>1</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="14">
-        <v>101</v>
-      </c>
-      <c r="B15" s="14">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="L15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="14">
-        <v>47061</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="14">
-        <v>102</v>
-      </c>
-      <c r="B16" s="14">
-        <v>1</v>
-      </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="14">
-        <v>2</v>
-      </c>
-      <c r="G16" s="15">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="N16" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="14">
-        <v>103</v>
-      </c>
-      <c r="B17" s="14">
-        <v>1</v>
-      </c>
-      <c r="C17" s="14">
-        <v>5</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="14">
-        <v>9</v>
-      </c>
-      <c r="G17" s="15">
-        <v>1</v>
-      </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="14"/>
-      <c r="N17" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="14">
-        <v>104</v>
-      </c>
-      <c r="B18" s="14">
-        <v>1</v>
-      </c>
-      <c r="C18" s="14">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="14">
-        <v>3</v>
-      </c>
-      <c r="G18" s="15">
-        <v>1</v>
-      </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="14"/>
-      <c r="N18" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="14">
-        <v>105</v>
-      </c>
-      <c r="B19" s="14">
-        <v>1</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="14">
-        <v>6</v>
-      </c>
-      <c r="G19" s="15">
-        <v>1</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L19" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="14">
-        <v>106</v>
-      </c>
-      <c r="B20" s="14">
-        <v>1</v>
-      </c>
-      <c r="C20" s="14">
+      <c r="D22" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="15">
         <v>11</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="14">
-        <v>7</v>
-      </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14" t="s">
+      <c r="G22" s="16">
+        <v>1</v>
+      </c>
+      <c r="H22" s="16"/>
+      <c r="I22" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="14"/>
-      <c r="N20" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="14">
-        <v>107</v>
-      </c>
-      <c r="B21" s="14">
-        <v>1</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="J22" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="15">
+        <v>109</v>
+      </c>
+      <c r="B23" s="15">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="15">
+        <v>12</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1</v>
+      </c>
+      <c r="H23" s="16"/>
+      <c r="I23" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="15">
+        <v>110</v>
+      </c>
+      <c r="B24" s="15">
+        <v>1</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="15">
+        <v>13</v>
+      </c>
+      <c r="G24" s="16">
+        <v>1</v>
+      </c>
+      <c r="H24" s="16"/>
+      <c r="I24" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="15">
+        <v>111</v>
+      </c>
+      <c r="B25" s="15">
+        <v>1</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="15">
+        <v>14</v>
+      </c>
+      <c r="G25" s="16">
+        <v>1</v>
+      </c>
+      <c r="H25" s="16"/>
+      <c r="I25" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="15">
+        <v>112</v>
+      </c>
+      <c r="B26" s="15">
+        <v>1</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="15">
         <v>15</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="14">
-        <v>8</v>
-      </c>
-      <c r="G21" s="15">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="14"/>
-      <c r="N21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="14">
-        <v>108</v>
-      </c>
-      <c r="B22" s="14">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14">
-        <v>10</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="14">
-        <v>11</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L22" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="14">
-        <v>109</v>
-      </c>
-      <c r="B23" s="14">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" s="14">
-        <v>12</v>
-      </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="14">
-        <v>110</v>
-      </c>
-      <c r="B24" s="14">
-        <v>1</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F24" s="14">
-        <v>13</v>
-      </c>
-      <c r="G24" s="15">
-        <v>1</v>
-      </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="14"/>
-      <c r="N24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="14">
-        <v>111</v>
-      </c>
-      <c r="B25" s="14">
-        <v>1</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="14">
-        <v>14</v>
-      </c>
-      <c r="G25" s="15">
-        <v>1</v>
-      </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="14"/>
-      <c r="N25" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="14">
-        <v>112</v>
-      </c>
-      <c r="B26" s="14">
-        <v>1</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="14">
-        <v>15</v>
-      </c>
-      <c r="G26" s="15">
-        <v>1</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L26" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:14">
+      <c r="G26" s="16">
+        <v>1</v>
+      </c>
+      <c r="H26" s="16"/>
+      <c r="I26" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:16">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2693,35 +2868,35 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="17">
-        <v>1</v>
-      </c>
-      <c r="H27" s="17"/>
+      <c r="G27" s="18">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18"/>
       <c r="I27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:14">
+      <c r="P27" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:16">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2730,35 +2905,35 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>90</v>
+        <v>96</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>97</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="19">
-        <v>1</v>
-      </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:14">
+      <c r="G28" s="20">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:16">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2767,35 +2942,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="17">
-        <v>1</v>
-      </c>
-      <c r="H29" s="17"/>
+      <c r="G29" s="18">
+        <v>1</v>
+      </c>
+      <c r="H29" s="18"/>
       <c r="I29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:14">
+      <c r="P29" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:16">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2804,35 +2979,35 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>101</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="17">
-        <v>1</v>
-      </c>
-      <c r="H30" s="17"/>
+      <c r="G30" s="18">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
       <c r="I30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:14">
+      <c r="P30" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:16">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2841,35 +3016,35 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>103</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="17">
-        <v>1</v>
-      </c>
-      <c r="H31" s="17"/>
+      <c r="G31" s="18">
+        <v>1</v>
+      </c>
+      <c r="H31" s="18"/>
       <c r="I31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N31" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:14">
+      <c r="P31" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:16">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2878,35 +3053,35 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="17">
-        <v>1</v>
-      </c>
-      <c r="H32" s="17"/>
+      <c r="G32" s="18">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18"/>
       <c r="I32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:14">
+      <c r="P32" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:16">
       <c r="A33" s="3">
         <v>119</v>
       </c>
@@ -2914,35 +3089,35 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="19">
-        <v>1</v>
-      </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>34</v>
+      <c r="G33" s="20">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20"/>
+      <c r="I33" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="P33" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -2951,188 +3126,696 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="20">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L34" s="14" t="b">
+        <v>37</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" s="15" t="b">
         <v>1</v>
       </c>
       <c r="M34" s="3"/>
-      <c r="N34" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="4">
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="5">
         <v>121</v>
       </c>
-      <c r="B35" s="4">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="4">
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="5">
         <v>23</v>
       </c>
-      <c r="G35" s="5">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>34</v>
+      <c r="G35" s="6">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="2"/>
-      <c r="N35" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="4">
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="5">
         <v>122</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>34</v>
+      <c r="D36" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="4">
+    <row r="37" spans="1:16">
+      <c r="A37" s="5">
         <v>123</v>
       </c>
-      <c r="B37" s="4">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>105</v>
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F37" s="4">
+        <v>113</v>
+      </c>
+      <c r="F37" s="5">
         <v>24</v>
       </c>
-      <c r="G37" s="5">
-        <v>1</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>34</v>
+      <c r="G37" s="6">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="L37" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="4">
+    <row r="38" spans="1:16">
+      <c r="A38" s="5">
         <v>124</v>
       </c>
-      <c r="B38" s="4">
-        <v>1</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>107</v>
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F38" s="4">
+        <v>115</v>
+      </c>
+      <c r="F38" s="5">
         <v>25</v>
       </c>
-      <c r="G38" s="5">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L38" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="4">
+      <c r="G38" s="6">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="5">
         <v>125</v>
       </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>109</v>
+      <c r="B39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F39" s="4">
+        <v>117</v>
+      </c>
+      <c r="F39" s="5">
         <v>26</v>
       </c>
-      <c r="G39" s="5">
-        <v>1</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="L39" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>40</v>
+      <c r="G39" s="6">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:16">
+      <c r="A40" s="5">
+        <v>1001</v>
+      </c>
+      <c r="B40" s="5">
+        <v>1</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="6">
+        <v>5</v>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L40" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:16">
+      <c r="A41" s="5">
+        <v>1002</v>
+      </c>
+      <c r="B41" s="5">
+        <v>1</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="5">
+        <v>2</v>
+      </c>
+      <c r="G41" s="6">
+        <v>5</v>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:16">
+      <c r="A42" s="5">
+        <v>1003</v>
+      </c>
+      <c r="B42" s="5">
+        <v>1</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="5">
+        <v>3</v>
+      </c>
+      <c r="G42" s="6">
+        <v>5</v>
+      </c>
+      <c r="H42" s="6"/>
+      <c r="I42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" s="4" customFormat="1" spans="1:16">
+      <c r="A43" s="4">
+        <v>1004</v>
+      </c>
+      <c r="B43" s="4">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4">
+        <v>4</v>
+      </c>
+      <c r="G43" s="22">
+        <v>5</v>
+      </c>
+      <c r="H43" s="22"/>
+      <c r="I43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" s="4" customFormat="1" spans="1:16">
+      <c r="A44" s="4">
+        <v>1005</v>
+      </c>
+      <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4">
+        <v>5</v>
+      </c>
+      <c r="G44" s="22">
+        <v>5</v>
+      </c>
+      <c r="H44" s="22"/>
+      <c r="I44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:16">
+      <c r="A45" s="5">
+        <v>2001</v>
+      </c>
+      <c r="B45" s="5">
+        <v>1</v>
+      </c>
+      <c r="C45" s="5">
+        <v>11</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5">
+        <v>1</v>
+      </c>
+      <c r="G45" s="6">
+        <v>4</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:16">
+      <c r="A46" s="5">
+        <v>2002</v>
+      </c>
+      <c r="B46" s="5">
+        <v>1</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5">
+        <v>2</v>
+      </c>
+      <c r="G46" s="6">
+        <v>4</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:16">
+      <c r="A47" s="5">
+        <v>2003</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="19"/>
+      <c r="F47" s="5">
+        <v>3</v>
+      </c>
+      <c r="G47" s="20">
+        <v>4</v>
+      </c>
+      <c r="H47" s="20"/>
+      <c r="I47" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:16">
+      <c r="A48" s="5">
+        <v>2004</v>
+      </c>
+      <c r="B48" s="5">
+        <v>1</v>
+      </c>
+      <c r="C48" s="5">
+        <v>2</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5">
+        <v>4</v>
+      </c>
+      <c r="G48" s="6">
+        <v>4</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="P48" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:16">
+      <c r="A49" s="5">
+        <v>2005</v>
+      </c>
+      <c r="B49" s="15">
+        <v>1</v>
+      </c>
+      <c r="C49" s="15">
+        <v>4</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="5">
+        <v>5</v>
+      </c>
+      <c r="G49" s="16">
+        <v>4</v>
+      </c>
+      <c r="H49" s="16"/>
+      <c r="I49" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="O49" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="P49" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:16">
+      <c r="A50" s="5">
+        <v>2006</v>
+      </c>
+      <c r="B50" s="15">
+        <v>1</v>
+      </c>
+      <c r="C50" s="15">
+        <v>15</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15">
+        <v>6</v>
+      </c>
+      <c r="G50" s="16">
+        <v>4</v>
+      </c>
+      <c r="H50" s="16"/>
+      <c r="I50" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J50" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L50" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="O50" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="P50" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:16">
+      <c r="A51" s="5">
+        <v>2007</v>
+      </c>
+      <c r="B51" s="15">
+        <v>1</v>
+      </c>
+      <c r="C51" s="15">
+        <v>5</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15">
+        <v>7</v>
+      </c>
+      <c r="G51" s="16">
+        <v>4</v>
+      </c>
+      <c r="H51" s="16"/>
+      <c r="I51" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L51" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="O51" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="P51" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="142">
   <si>
     <t>id</t>
   </si>
@@ -490,6 +490,9 @@
     <t>1_15;3_1</t>
   </si>
   <si>
+    <t>AND(playerLevel(1),playerVipLevel(1))</t>
+  </si>
+  <si>
     <t>AND(playerLevel(15),playerVipLevel(1))</t>
   </si>
   <si>
@@ -511,58 +514,58 @@
     <t>1_20</t>
   </si>
   <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>刮刮乐</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
+    <t>等级礼包</t>
+  </si>
+  <si>
+    <t>Grid (2)</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
+    <t>首充礼包</t>
+  </si>
+  <si>
+    <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>remainingAttempts(57011,1,1)</t>
+  </si>
+  <si>
+    <t>成长基金</t>
+  </si>
+  <si>
+    <t>Grid (1)</t>
+  </si>
+  <si>
+    <t>1_10</t>
+  </si>
+  <si>
     <t>playerLevel(10)</t>
-  </si>
-  <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>刮刮乐</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>储钱罐</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
-    <t>等级礼包</t>
-  </si>
-  <si>
-    <t>Grid (2)</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>playerLevel(30)</t>
-  </si>
-  <si>
-    <t>首充礼包</t>
-  </si>
-  <si>
-    <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>remainingAttempts(57011,1,1)</t>
-  </si>
-  <si>
-    <t>成长基金</t>
-  </si>
-  <si>
-    <t>Grid (1)</t>
-  </si>
-  <si>
-    <t>1_10</t>
   </si>
   <si>
     <t>签到奖励</t>
@@ -1426,7 +1429,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1437,6 +1440,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1489,6 +1495,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1804,67 +1813,67 @@
   <dimension ref="A1:P51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
-    <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
-    <col min="13" max="15" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="16" max="16" width="26" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="19.7" style="6" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="36.6083333333333" style="5" customWidth="1"/>
+    <col min="11" max="11" width="40.375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="5" customWidth="1"/>
+    <col min="13" max="15" width="11.9083333333333" style="5" customWidth="1"/>
+    <col min="16" max="16" width="26" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1872,981 +1881,981 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="9" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9" t="s">
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="12">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12" t="s">
+      <c r="A5" s="13">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="12" t="s">
+      <c r="H5" s="14"/>
+      <c r="I5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="J5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>38</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="4" t="s">
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13">
         <v>3</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="12" t="s">
+      <c r="H6" s="14"/>
+      <c r="I6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="4" t="s">
+      <c r="L6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>3</v>
       </c>
-      <c r="B7" s="12">
-        <v>1</v>
-      </c>
-      <c r="C7" s="12">
+      <c r="B7" s="13">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13">
         <v>9</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="12" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="14">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="4" t="s">
+      <c r="J7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>4</v>
       </c>
-      <c r="B8" s="12">
-        <v>1</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12" t="s">
+      <c r="B8" s="13">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <v>5</v>
       </c>
-      <c r="G8" s="13">
-        <v>1</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="12" t="s">
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="4" t="s">
+      <c r="J8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>5</v>
       </c>
-      <c r="B9" s="12">
-        <v>1</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="B9" s="13">
+        <v>1</v>
+      </c>
+      <c r="C9" s="13">
         <v>6</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="12" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="14">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="4" t="s">
+      <c r="J9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>6</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13">
-        <v>1</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="12" t="s">
+      <c r="F10" s="13"/>
+      <c r="G10" s="14">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="4" t="s">
+      <c r="J10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>7</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="12" t="s">
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14">
+        <v>1</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="4" t="s">
+      <c r="J11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>8</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12" t="s">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13">
-        <v>1</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="12" t="s">
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14">
+        <v>1</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="4" t="s">
+      <c r="K12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>9</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="12" t="s">
+      <c r="H13" s="14"/>
+      <c r="I13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="4" t="s">
+      <c r="J13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>10</v>
       </c>
-      <c r="B14" s="12">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="B14" s="13">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="12">
+      <c r="E14" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="13">
         <v>4</v>
       </c>
-      <c r="G14" s="13">
-        <v>1</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="12" t="s">
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="4" t="s">
+      <c r="J14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="14">
+      <c r="A15" s="15">
         <v>101</v>
       </c>
-      <c r="B15" s="14">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="14" t="s">
+      <c r="B15" s="15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14" t="s">
+      <c r="E15" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="F15" s="15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="J15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="L15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="14">
+      <c r="L15" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15">
         <v>47061</v>
       </c>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="4" t="s">
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="14">
+      <c r="A16" s="15">
         <v>102</v>
       </c>
-      <c r="B16" s="14">
-        <v>1</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="B16" s="15">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="15">
         <v>2</v>
       </c>
-      <c r="G16" s="15">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14" t="s">
+      <c r="G16" s="16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="16"/>
+      <c r="I16" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="4" t="s">
+      <c r="J16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="14">
+      <c r="A17" s="15">
         <v>103</v>
       </c>
-      <c r="B17" s="14">
-        <v>1</v>
-      </c>
-      <c r="C17" s="14">
+      <c r="B17" s="15">
+        <v>1</v>
+      </c>
+      <c r="C17" s="15">
         <v>5</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="15">
         <v>9</v>
       </c>
-      <c r="G17" s="15">
-        <v>1</v>
-      </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14" t="s">
+      <c r="G17" s="16">
+        <v>1</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="4" t="s">
+      <c r="J17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="14">
+      <c r="A18" s="15">
         <v>104</v>
       </c>
-      <c r="B18" s="14">
-        <v>1</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="15">
+        <v>1</v>
+      </c>
+      <c r="C18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="15">
         <v>3</v>
       </c>
-      <c r="G18" s="15">
-        <v>1</v>
-      </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14" t="s">
+      <c r="G18" s="16">
+        <v>1</v>
+      </c>
+      <c r="H18" s="16"/>
+      <c r="I18" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="4" t="s">
+      <c r="J18" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <v>105</v>
       </c>
-      <c r="B19" s="14">
-        <v>1</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14" t="s">
+      <c r="B19" s="15">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="15">
         <v>6</v>
       </c>
-      <c r="G19" s="15">
-        <v>1</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14" t="s">
+      <c r="G19" s="16">
+        <v>1</v>
+      </c>
+      <c r="H19" s="16"/>
+      <c r="I19" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="L19" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="4" t="s">
+      <c r="L19" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>106</v>
       </c>
-      <c r="B20" s="14">
-        <v>1</v>
-      </c>
-      <c r="C20" s="14">
+      <c r="B20" s="15">
+        <v>1</v>
+      </c>
+      <c r="C20" s="15">
         <v>11</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="15">
         <v>7</v>
       </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14" t="s">
+      <c r="G20" s="16">
+        <v>1</v>
+      </c>
+      <c r="H20" s="16"/>
+      <c r="I20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="L20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="4" t="s">
+      <c r="L20" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <v>107</v>
       </c>
-      <c r="B21" s="14">
-        <v>1</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="B21" s="15">
+        <v>1</v>
+      </c>
+      <c r="C21" s="15">
         <v>15</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="15">
         <v>8</v>
       </c>
-      <c r="G21" s="15">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14" t="s">
+      <c r="G21" s="16">
+        <v>1</v>
+      </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="J21" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="4" t="s">
+      <c r="J21" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <v>108</v>
       </c>
-      <c r="B22" s="14">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14">
+      <c r="B22" s="15">
+        <v>1</v>
+      </c>
+      <c r="C22" s="15">
         <v>10</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="D22" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="14">
+      <c r="E22" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="15">
         <v>11</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14" t="s">
+      <c r="G22" s="16">
+        <v>1</v>
+      </c>
+      <c r="H22" s="16"/>
+      <c r="I22" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="4" t="s">
+      <c r="J22" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <v>109</v>
       </c>
-      <c r="B23" s="14">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="14" t="s">
+      <c r="B23" s="15">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="14">
+      <c r="E23" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="15">
         <v>12</v>
       </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="14" t="s">
+      <c r="G23" s="16">
+        <v>1</v>
+      </c>
+      <c r="H23" s="16"/>
+      <c r="I23" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="4" t="s">
+      <c r="J23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <v>110</v>
       </c>
-      <c r="B24" s="14">
-        <v>1</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="14" t="s">
+      <c r="B24" s="15">
+        <v>1</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F24" s="14">
+      <c r="E24" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="15">
         <v>13</v>
       </c>
-      <c r="G24" s="15">
-        <v>1</v>
-      </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="14" t="s">
+      <c r="G24" s="16">
+        <v>1</v>
+      </c>
+      <c r="H24" s="16"/>
+      <c r="I24" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J24" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="4" t="s">
+      <c r="J24" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <v>111</v>
       </c>
-      <c r="B25" s="14">
-        <v>1</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" s="14" t="s">
+      <c r="B25" s="15">
+        <v>1</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="F25" s="14">
+      <c r="E25" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="15">
         <v>14</v>
       </c>
-      <c r="G25" s="15">
-        <v>1</v>
-      </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="14" t="s">
+      <c r="G25" s="16">
+        <v>1</v>
+      </c>
+      <c r="H25" s="16"/>
+      <c r="I25" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="4" t="s">
-        <v>88</v>
+      <c r="J25" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <v>112</v>
       </c>
-      <c r="B26" s="14">
-        <v>1</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="14" t="s">
+      <c r="B26" s="15">
+        <v>1</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="14">
+      <c r="E26" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="15">
         <v>15</v>
       </c>
-      <c r="G26" s="15">
-        <v>1</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="14" t="s">
+      <c r="G26" s="16">
+        <v>1</v>
+      </c>
+      <c r="H26" s="16"/>
+      <c r="I26" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L26" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="4" t="s">
+      <c r="J26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2859,26 +2868,26 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="17">
-        <v>1</v>
-      </c>
-      <c r="H27" s="17"/>
+      <c r="G27" s="18">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18"/>
       <c r="I27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J27" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K27" s="14" t="s">
-        <v>94</v>
+      <c r="J27" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
@@ -2896,28 +2905,28 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="18" t="s">
         <v>96</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>97</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="19">
-        <v>1</v>
-      </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="14" t="s">
+      <c r="G28" s="20">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J28" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L28" s="14" t="b">
+      <c r="J28" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" s="15" t="b">
         <v>1</v>
       </c>
       <c r="P28" s="3" t="s">
@@ -2933,26 +2942,26 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="20" t="s">
         <v>98</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="17">
-        <v>1</v>
-      </c>
-      <c r="H29" s="17"/>
+      <c r="G29" s="18">
+        <v>1</v>
+      </c>
+      <c r="H29" s="18"/>
       <c r="I29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J29" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K29" s="14" t="s">
-        <v>94</v>
+      <c r="J29" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
@@ -2970,26 +2979,26 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="20" t="s">
         <v>100</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>101</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="17">
-        <v>1</v>
-      </c>
-      <c r="H30" s="17"/>
+      <c r="G30" s="18">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
       <c r="I30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J30" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K30" s="14" t="s">
-        <v>94</v>
+      <c r="J30" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
@@ -3007,26 +3016,26 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="20" t="s">
         <v>102</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>103</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="17">
-        <v>1</v>
-      </c>
-      <c r="H31" s="17"/>
+      <c r="G31" s="18">
+        <v>1</v>
+      </c>
+      <c r="H31" s="18"/>
       <c r="I31" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J31" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K31" s="14" t="s">
-        <v>94</v>
+      <c r="J31" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
@@ -3044,26 +3053,26 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="20" t="s">
         <v>104</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="17">
-        <v>1</v>
-      </c>
-      <c r="H32" s="17"/>
+      <c r="G32" s="18">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18"/>
       <c r="I32" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J32" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K32" s="14" t="s">
-        <v>94</v>
+      <c r="J32" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
@@ -3080,25 +3089,25 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" s="18" t="s">
         <v>106</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="19">
-        <v>1</v>
-      </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="14" t="s">
+      <c r="G33" s="20">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20"/>
+      <c r="I33" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J33" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="14" t="s">
+      <c r="J33" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="15" t="s">
         <v>38</v>
       </c>
       <c r="L33" s="2" t="b">
@@ -3117,28 +3126,28 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="20">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J34" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" s="14" t="b">
+      <c r="J34" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" s="15" t="b">
         <v>1</v>
       </c>
       <c r="M34" s="3"/>
@@ -3149,28 +3158,28 @@
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="4">
+      <c r="A35" s="5">
         <v>121</v>
       </c>
-      <c r="B35" s="4">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F35" s="4">
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="5">
         <v>23</v>
       </c>
-      <c r="G35" s="5">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4" t="s">
+      <c r="G35" s="6">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K35" s="14" t="s">
+      <c r="J35" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="15" t="s">
         <v>38</v>
       </c>
       <c r="L35" s="2" t="b">
@@ -3184,19 +3193,19 @@
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="4">
+      <c r="A36" s="5">
         <v>122</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I36" s="4" t="s">
+      <c r="D36" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J36" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K36" s="14" t="s">
+      <c r="J36" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="15" t="s">
         <v>38</v>
       </c>
       <c r="L36" s="2" t="b">
@@ -3204,31 +3213,31 @@
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="4">
+      <c r="A37" s="5">
         <v>123</v>
       </c>
-      <c r="B37" s="4">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>111</v>
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F37" s="4">
+        <v>113</v>
+      </c>
+      <c r="F37" s="5">
         <v>24</v>
       </c>
-      <c r="G37" s="5">
-        <v>1</v>
-      </c>
-      <c r="I37" s="4" t="s">
+      <c r="G37" s="6">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J37" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="14" t="s">
+      <c r="J37" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37" s="15" t="s">
         <v>38</v>
       </c>
       <c r="L37" s="2" t="b">
@@ -3236,31 +3245,31 @@
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="4">
+      <c r="A38" s="5">
         <v>124</v>
       </c>
-      <c r="B38" s="4">
-        <v>1</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>113</v>
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="4">
+        <v>115</v>
+      </c>
+      <c r="F38" s="5">
         <v>25</v>
       </c>
-      <c r="G38" s="5">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4" t="s">
+      <c r="G38" s="6">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J38" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K38" s="14" t="s">
+      <c r="J38" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="15" t="s">
         <v>38</v>
       </c>
       <c r="L38" s="2" t="b">
@@ -3271,31 +3280,31 @@
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="4">
+      <c r="A39" s="5">
         <v>125</v>
       </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>115</v>
+      <c r="B39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="4">
+        <v>117</v>
+      </c>
+      <c r="F39" s="5">
         <v>26</v>
       </c>
-      <c r="G39" s="5">
-        <v>1</v>
-      </c>
-      <c r="I39" s="4" t="s">
+      <c r="G39" s="6">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J39" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K39" s="14" t="s">
+      <c r="J39" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K39" s="15" t="s">
         <v>38</v>
       </c>
       <c r="L39" s="2" t="b">
@@ -3306,126 +3315,126 @@
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:16">
-      <c r="A40" s="4">
+      <c r="A40" s="5">
         <v>1001</v>
       </c>
-      <c r="B40" s="4">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4" t="s">
-        <v>117</v>
+      <c r="B40" s="5">
+        <v>1</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="E40" s="3"/>
-      <c r="F40" s="4">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5">
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="6">
         <v>5</v>
       </c>
-      <c r="H40" s="5"/>
-      <c r="I40" s="4" t="s">
+      <c r="H40" s="6"/>
+      <c r="I40" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J40" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L40" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4" t="s">
-        <v>118</v>
+      <c r="J40" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L40" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:16">
-      <c r="A41" s="4">
+      <c r="A41" s="5">
         <v>1002</v>
       </c>
-      <c r="B41" s="4">
-        <v>1</v>
-      </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4" t="s">
-        <v>119</v>
+      <c r="B41" s="5">
+        <v>1</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="F41" s="4">
+      <c r="F41" s="5">
         <v>2</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="6">
         <v>5</v>
       </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="4" t="s">
+      <c r="H41" s="6"/>
+      <c r="I41" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L41" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4" t="s">
-        <v>120</v>
+      <c r="J41" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:16">
-      <c r="A42" s="4">
+      <c r="A42" s="5">
         <v>1003</v>
       </c>
-      <c r="B42" s="4">
-        <v>1</v>
-      </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4" t="s">
-        <v>121</v>
+      <c r="B42" s="5">
+        <v>1</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="4">
+      <c r="F42" s="5">
         <v>3</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="6">
         <v>5</v>
       </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="4" t="s">
+      <c r="H42" s="6"/>
+      <c r="I42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J42" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4" t="s">
-        <v>122</v>
+      <c r="J42" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="43" customFormat="1" spans="1:16">
+    <row r="43" s="4" customFormat="1" spans="1:16">
       <c r="A43" s="4">
         <v>1004</v>
       </c>
@@ -3434,38 +3443,38 @@
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="E43" s="4"/>
       <c r="F43" s="4">
         <v>4</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="22">
         <v>5</v>
       </c>
-      <c r="H43" s="5"/>
+      <c r="H43" s="22"/>
       <c r="I43" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J43" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L43" s="14" t="b">
+      <c r="J43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L43" s="4" t="b">
         <v>1</v>
       </c>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="P43" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P43" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="1:16">
+    <row r="44" s="4" customFormat="1" spans="1:16">
       <c r="A44" s="4">
         <v>1005</v>
       </c>
@@ -3474,125 +3483,125 @@
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="E44" s="4"/>
       <c r="F44" s="4">
         <v>5</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="22">
         <v>5</v>
       </c>
-      <c r="H44" s="5"/>
+      <c r="H44" s="22"/>
       <c r="I44" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L44" s="14" t="b">
+      <c r="J44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="4" t="b">
         <v>1</v>
       </c>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="P44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P44" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:16">
-      <c r="A45" s="4">
+      <c r="A45" s="5">
         <v>2001</v>
       </c>
-      <c r="B45" s="4">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4">
+      <c r="B45" s="5">
+        <v>1</v>
+      </c>
+      <c r="C45" s="5">
         <v>11</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5">
+      <c r="E45" s="5"/>
+      <c r="F45" s="5">
+        <v>1</v>
+      </c>
+      <c r="G45" s="6">
         <v>4</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="4" t="s">
+      <c r="H45" s="6"/>
+      <c r="I45" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="J45" s="4" t="s">
+      <c r="J45" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K45" s="4" t="s">
+      <c r="K45" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="L45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="O45" s="4" t="s">
+      <c r="L45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="P45" s="4" t="s">
+      <c r="O45" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="P45" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:16">
-      <c r="A46" s="4">
+      <c r="A46" s="5">
         <v>2002</v>
       </c>
-      <c r="B46" s="4">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4" t="s">
+      <c r="B46" s="5">
+        <v>1</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4">
+      <c r="E46" s="5"/>
+      <c r="F46" s="5">
         <v>2</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="6">
         <v>4</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="4" t="s">
+      <c r="H46" s="6"/>
+      <c r="I46" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J46" s="4" t="s">
+      <c r="J46" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K46" s="4" t="s">
+      <c r="K46" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="O46" s="4" t="s">
+      <c r="L46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="P46" s="4" t="s">
+      <c r="O46" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="P46" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:16">
-      <c r="A47" s="4">
+      <c r="A47" s="5">
         <v>2003</v>
       </c>
       <c r="B47" s="3">
@@ -3600,23 +3609,23 @@
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E47" s="18"/>
-      <c r="F47" s="4">
+        <v>96</v>
+      </c>
+      <c r="E47" s="19"/>
+      <c r="F47" s="5">
         <v>3</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="20">
         <v>4</v>
       </c>
-      <c r="H47" s="19"/>
-      <c r="I47" s="14" t="s">
+      <c r="H47" s="20"/>
+      <c r="I47" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K47" s="14" t="s">
+      <c r="J47" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="15" t="s">
         <v>38</v>
       </c>
       <c r="L47" s="2" t="b">
@@ -3624,188 +3633,188 @@
       </c>
       <c r="M47" s="3"/>
       <c r="N47" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:16">
-      <c r="A48" s="4">
+      <c r="A48" s="5">
         <v>2004</v>
       </c>
-      <c r="B48" s="4">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4">
+      <c r="B48" s="5">
+        <v>1</v>
+      </c>
+      <c r="C48" s="5">
         <v>2</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4">
+      <c r="E48" s="5"/>
+      <c r="F48" s="5">
         <v>4</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="6">
         <v>4</v>
       </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="4" t="s">
+      <c r="H48" s="6"/>
+      <c r="I48" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="O48" s="4" t="s">
+      <c r="J48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="P48" s="4" t="s">
+      <c r="O48" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="P48" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:16">
-      <c r="A49" s="4">
+      <c r="A49" s="5">
         <v>2005</v>
       </c>
-      <c r="B49" s="14">
-        <v>1</v>
-      </c>
-      <c r="C49" s="14">
+      <c r="B49" s="15">
+        <v>1</v>
+      </c>
+      <c r="C49" s="15">
         <v>4</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E49" s="14"/>
-      <c r="F49" s="4">
+      <c r="E49" s="15"/>
+      <c r="F49" s="5">
         <v>5</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="16">
         <v>4</v>
       </c>
-      <c r="H49" s="15"/>
-      <c r="I49" s="14" t="s">
+      <c r="H49" s="16"/>
+      <c r="I49" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J49" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K49" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="O49" s="14" t="s">
+      <c r="J49" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="P49" s="4" t="s">
+      <c r="O49" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="P49" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:16">
-      <c r="A50" s="4">
+      <c r="A50" s="5">
         <v>2006</v>
       </c>
-      <c r="B50" s="14">
-        <v>1</v>
-      </c>
-      <c r="C50" s="14">
+      <c r="B50" s="15">
+        <v>1</v>
+      </c>
+      <c r="C50" s="15">
         <v>15</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14">
+      <c r="E50" s="15"/>
+      <c r="F50" s="15">
         <v>6</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="16">
         <v>4</v>
       </c>
-      <c r="H50" s="15"/>
-      <c r="I50" s="14" t="s">
+      <c r="H50" s="16"/>
+      <c r="I50" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="J50" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="K50" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="L50" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="O50" s="14" t="s">
+      <c r="J50" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L50" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="P50" s="4" t="s">
+      <c r="O50" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="P50" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:16">
-      <c r="A51" s="4">
+      <c r="A51" s="5">
         <v>2007</v>
       </c>
-      <c r="B51" s="14">
-        <v>1</v>
-      </c>
-      <c r="C51" s="14">
+      <c r="B51" s="15">
+        <v>1</v>
+      </c>
+      <c r="C51" s="15">
         <v>5</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14">
+      <c r="E51" s="15"/>
+      <c r="F51" s="15">
         <v>7</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="16">
         <v>4</v>
       </c>
-      <c r="H51" s="15"/>
-      <c r="I51" s="14" t="s">
+      <c r="H51" s="16"/>
+      <c r="I51" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J51" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K51" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="O51" s="14" t="s">
+      <c r="J51" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L51" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="P51" s="4" t="s">
+      <c r="O51" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="P51" s="5" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -169,8 +169,8 @@
 1：显示在大厅对应位置
 2：显示在游戏界面对应位置
 3：显示在登陆界面对应位置
-4：显示在活动页面（仅限web端）
-5: 显示在最下方导航栏（仅限web端）
+4：显示在活动页面（仅限web端)
+5:显示在最下方导航栏（仅限web端）
 参数：位置1_位置2  即 大厅显示_游戏界面显示</t>
         </r>
       </text>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -361,12 +361,6 @@
     <t>提示文本ID</t>
   </si>
   <si>
-    <t>web活动宣传图</t>
-  </si>
-  <si>
-    <t>web触发弹出对应活动</t>
-  </si>
-  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -418,12 +412,6 @@
     <t>tips</t>
   </si>
   <si>
-    <t>webimg</t>
-  </si>
-  <si>
-    <t>trigger</t>
-  </si>
-  <si>
     <t>client</t>
   </si>
   <si>
@@ -457,9 +445,6 @@
     <t>官方派奖</t>
   </si>
   <si>
-    <t>Grid (27)</t>
-  </si>
-  <si>
     <t>显示位置：大厅</t>
   </si>
   <si>
@@ -472,9 +457,6 @@
     <t>分享推广</t>
   </si>
   <si>
-    <t>Grid (28)</t>
-  </si>
-  <si>
     <t>VIP功能</t>
   </si>
   <si>
@@ -749,6 +731,12 @@
   </si>
   <si>
     <t>btn_lottery</t>
+  </si>
+  <si>
+    <t>充值引导</t>
+  </si>
+  <si>
+    <t>NOT(accountTotalRecharge(0.001))</t>
   </si>
 </sst>
 </file>
@@ -1429,7 +1417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1440,9 +1428,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1495,9 +1480,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1810,1056 +1792,980 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="10.125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="19.7" style="6" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="36.6083333333333" style="5" customWidth="1"/>
-    <col min="11" max="11" width="40.375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="5" customWidth="1"/>
-    <col min="13" max="15" width="11.9083333333333" style="5" customWidth="1"/>
-    <col min="16" max="16" width="26" style="5" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="19.7" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
+    <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="14" max="14" width="26" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:14">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="7" t="s">
+      <c r="F2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7" t="s">
+      <c r="H2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="J2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="M2" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:14">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="L3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="M3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="7" t="s">
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:14">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="J4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="K4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="12">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="10" t="s">
+      <c r="H5" s="13"/>
+      <c r="I5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="13">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>38</v>
+      <c r="J5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="5" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="12">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12">
+        <v>3</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="12">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12">
+        <v>9</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="13">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="12">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="12">
+        <v>5</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="12">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12">
+        <v>6</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="12">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="12">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="13">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="12">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="13">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="12">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="12">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="12">
+        <v>4</v>
+      </c>
+      <c r="G14" s="13">
+        <v>1</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="14">
+        <v>101</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="14">
+        <v>47061</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="14">
+        <v>102</v>
+      </c>
+      <c r="B16" s="14">
+        <v>1</v>
+      </c>
+      <c r="C16" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13">
+      <c r="D16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="14">
+        <v>2</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="14"/>
+      <c r="N16" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="14">
+        <v>103</v>
+      </c>
+      <c r="B17" s="14">
+        <v>1</v>
+      </c>
+      <c r="C17" s="14">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="14">
+        <v>9</v>
+      </c>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="14"/>
+      <c r="N17" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="14">
+        <v>104</v>
+      </c>
+      <c r="B18" s="14">
+        <v>1</v>
+      </c>
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="14">
         <v>3</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="14"/>
+      <c r="N18" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="14">
+        <v>105</v>
+      </c>
+      <c r="B19" s="14">
+        <v>1</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="14">
+        <v>6</v>
+      </c>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L19" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="14"/>
+      <c r="N19" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="14">
+        <v>106</v>
+      </c>
+      <c r="B20" s="14">
+        <v>1</v>
+      </c>
+      <c r="C20" s="14">
+        <v>11</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="14">
+        <v>7</v>
+      </c>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="14"/>
+      <c r="N20" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="13">
-        <v>3</v>
-      </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
-        <v>9</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="13">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="13">
-        <v>5</v>
-      </c>
-      <c r="G8" s="14">
-        <v>1</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="13">
-        <v>5</v>
-      </c>
-      <c r="B9" s="13">
-        <v>1</v>
-      </c>
-      <c r="C9" s="13">
-        <v>6</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14">
-        <v>1</v>
-      </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="13">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14">
-        <v>1</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="13">
-        <v>7</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14">
-        <v>1</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="13">
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="14">
+        <v>107</v>
+      </c>
+      <c r="B21" s="14">
+        <v>1</v>
+      </c>
+      <c r="C21" s="14">
+        <v>15</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="14">
         <v>8</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14">
-        <v>1</v>
-      </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="13">
-        <v>9</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="13">
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="14"/>
+      <c r="N21" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="14">
+        <v>108</v>
+      </c>
+      <c r="B22" s="14">
+        <v>1</v>
+      </c>
+      <c r="C22" s="14">
         <v>10</v>
       </c>
-      <c r="B14" s="13">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="13">
-        <v>4</v>
-      </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="15">
-        <v>101</v>
-      </c>
-      <c r="B15" s="15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="16">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="L15" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="15">
-        <v>47061</v>
-      </c>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="15">
-        <v>102</v>
-      </c>
-      <c r="B16" s="15">
-        <v>1</v>
-      </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="15">
-        <v>2</v>
-      </c>
-      <c r="G16" s="16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="15">
-        <v>103</v>
-      </c>
-      <c r="B17" s="15">
-        <v>1</v>
-      </c>
-      <c r="C17" s="15">
-        <v>5</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="15">
-        <v>9</v>
-      </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="15">
-        <v>104</v>
-      </c>
-      <c r="B18" s="15">
-        <v>1</v>
-      </c>
-      <c r="C18" s="15">
-        <v>4</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="15">
-        <v>3</v>
-      </c>
-      <c r="G18" s="16">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="15">
-        <v>105</v>
-      </c>
-      <c r="B19" s="15">
-        <v>1</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" s="15">
-        <v>6</v>
-      </c>
-      <c r="G19" s="16">
-        <v>1</v>
-      </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="15">
-        <v>106</v>
-      </c>
-      <c r="B20" s="15">
-        <v>1</v>
-      </c>
-      <c r="C20" s="15">
+      <c r="D22" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="14">
         <v>11</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="15">
-        <v>7</v>
-      </c>
-      <c r="G20" s="16">
-        <v>1</v>
-      </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="L20" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="15">
-        <v>107</v>
-      </c>
-      <c r="B21" s="15">
-        <v>1</v>
-      </c>
-      <c r="C21" s="15">
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="14"/>
+      <c r="N22" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="14">
+        <v>109</v>
+      </c>
+      <c r="B23" s="14">
+        <v>1</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="14">
+        <v>12</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="14"/>
+      <c r="N23" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="14">
+        <v>110</v>
+      </c>
+      <c r="B24" s="14">
+        <v>1</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="14">
+        <v>13</v>
+      </c>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="14"/>
+      <c r="N24" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="14">
+        <v>111</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="14">
+        <v>14</v>
+      </c>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="14"/>
+      <c r="N25" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="14">
+        <v>112</v>
+      </c>
+      <c r="B26" s="14">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="14">
         <v>15</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="15">
-        <v>8</v>
-      </c>
-      <c r="G21" s="16">
-        <v>1</v>
-      </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="L21" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="15">
-        <v>108</v>
-      </c>
-      <c r="B22" s="15">
-        <v>1</v>
-      </c>
-      <c r="C22" s="15">
-        <v>10</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="15">
-        <v>11</v>
-      </c>
-      <c r="G22" s="16">
-        <v>1</v>
-      </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="15">
-        <v>109</v>
-      </c>
-      <c r="B23" s="15">
-        <v>1</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="15">
-        <v>12</v>
-      </c>
-      <c r="G23" s="16">
-        <v>1</v>
-      </c>
-      <c r="H23" s="16"/>
-      <c r="I23" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L23" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="15">
-        <v>110</v>
-      </c>
-      <c r="B24" s="15">
-        <v>1</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="15">
-        <v>13</v>
-      </c>
-      <c r="G24" s="16">
-        <v>1</v>
-      </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L24" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="15">
-        <v>111</v>
-      </c>
-      <c r="B25" s="15">
-        <v>1</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="15">
-        <v>14</v>
-      </c>
-      <c r="G25" s="16">
-        <v>1</v>
-      </c>
-      <c r="H25" s="16"/>
-      <c r="I25" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="15">
-        <v>112</v>
-      </c>
-      <c r="B26" s="15">
-        <v>1</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="15">
-        <v>15</v>
-      </c>
-      <c r="G26" s="16">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16"/>
-      <c r="I26" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L26" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:16">
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="14"/>
+      <c r="N26" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:14">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2868,35 +2774,35 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="18">
-        <v>1</v>
-      </c>
-      <c r="H27" s="18"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="17"/>
       <c r="I27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:16">
+      <c r="N27" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:14">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2905,35 +2811,35 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>97</v>
+        <v>90</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
       </c>
-      <c r="G28" s="20">
-        <v>1</v>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L28" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:16">
+      <c r="G28" s="19">
+        <v>1</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:14">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2942,35 +2848,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>99</v>
+        <v>92</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="18">
-        <v>1</v>
-      </c>
-      <c r="H29" s="18"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="17"/>
       <c r="I29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:16">
+      <c r="N29" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:14">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2979,35 +2885,35 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="18">
-        <v>1</v>
-      </c>
-      <c r="H30" s="18"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="17"/>
       <c r="I30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:16">
+      <c r="N30" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:14">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -3016,35 +2922,35 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>103</v>
+        <v>96</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>97</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="18">
-        <v>1</v>
-      </c>
-      <c r="H31" s="18"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="17"/>
       <c r="I31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P31" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:16">
+      <c r="N31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:14">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -3053,32 +2959,32 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>99</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="18">
-        <v>1</v>
-      </c>
-      <c r="H32" s="18"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="17"/>
       <c r="I32" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J32" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>45</v>
+      <c r="N32" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:16">
@@ -3089,32 +2995,32 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>107</v>
+        <v>100</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>101</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
       </c>
-      <c r="G33" s="20">
-        <v>1</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>38</v>
+      <c r="G33" s="19">
+        <v>1</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>45</v>
+      <c r="N33" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3126,696 +3032,670 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="19">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" s="15" t="b">
+        <v>33</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3" t="s">
-        <v>45</v>
+      <c r="N34" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>121</v>
       </c>
-      <c r="B35" s="5">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="5">
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="4">
         <v>23</v>
       </c>
-      <c r="G35" s="6">
-        <v>1</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>38</v>
+      <c r="G35" s="5">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2" t="s">
-        <v>45</v>
+      <c r="N35" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="5">
+      <c r="A36" s="4">
         <v>122</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>38</v>
+      <c r="D36" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="5">
+      <c r="A37" s="4">
         <v>123</v>
       </c>
-      <c r="B37" s="5">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>112</v>
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="5">
+        <v>107</v>
+      </c>
+      <c r="F37" s="4">
         <v>24</v>
       </c>
-      <c r="G37" s="6">
-        <v>1</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>38</v>
+      <c r="G37" s="5">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="L37" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="5">
+      <c r="A38" s="4">
         <v>124</v>
       </c>
-      <c r="B38" s="5">
-        <v>1</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="B38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="4">
+        <v>25</v>
+      </c>
+      <c r="G38" s="5">
+        <v>1</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="4">
+        <v>125</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="4">
+        <v>26</v>
+      </c>
+      <c r="G39" s="5">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="4">
+        <v>1001</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5">
+        <v>5</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="4">
+        <v>1002</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F41" s="4">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5">
+        <v>5</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F38" s="5">
-        <v>25</v>
-      </c>
-      <c r="G38" s="6">
-        <v>1</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L38" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="A39" s="5">
-        <v>125</v>
-      </c>
-      <c r="B39" s="5">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="P41" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="4">
+        <v>1003</v>
+      </c>
+      <c r="B42" s="4">
+        <v>1</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F42" s="4">
+        <v>3</v>
+      </c>
+      <c r="G42" s="5">
+        <v>5</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F39" s="5">
-        <v>26</v>
-      </c>
-      <c r="G39" s="6">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J39" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K39" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" spans="1:16">
-      <c r="A40" s="5">
-        <v>1001</v>
-      </c>
-      <c r="B40" s="5">
-        <v>1</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="5">
-        <v>1</v>
-      </c>
-      <c r="G40" s="6">
-        <v>5</v>
-      </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L40" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:16">
-      <c r="A41" s="5">
-        <v>1002</v>
-      </c>
-      <c r="B41" s="5">
-        <v>1</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="5">
-        <v>2</v>
-      </c>
-      <c r="G41" s="6">
-        <v>5</v>
-      </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J41" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L41" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:16">
-      <c r="A42" s="5">
-        <v>1003</v>
-      </c>
-      <c r="B42" s="5">
-        <v>1</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="5">
-        <v>3</v>
-      </c>
-      <c r="G42" s="6">
-        <v>5</v>
-      </c>
-      <c r="H42" s="6"/>
-      <c r="I42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" s="4" customFormat="1" spans="1:16">
+      <c r="P42" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="4">
         <v>1004</v>
       </c>
       <c r="B43" s="4">
         <v>1</v>
       </c>
-      <c r="C43" s="4"/>
       <c r="D43" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" s="4"/>
+        <v>118</v>
+      </c>
       <c r="F43" s="4">
         <v>4</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="5">
         <v>5</v>
       </c>
-      <c r="H43" s="22"/>
       <c r="I43" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L43" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
       <c r="O43" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" s="4" customFormat="1" spans="1:16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="4">
         <v>1005</v>
       </c>
       <c r="B44" s="4">
         <v>1</v>
       </c>
-      <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" s="4"/>
+        <v>120</v>
+      </c>
       <c r="F44" s="4">
         <v>5</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="5">
         <v>5</v>
       </c>
-      <c r="H44" s="22"/>
       <c r="I44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="4">
+        <v>2001</v>
+      </c>
+      <c r="B45" s="4">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4">
+        <v>11</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5">
+        <v>4</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="L44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4" t="s">
+      <c r="J45" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="4">
+        <v>2002</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2</v>
+      </c>
+      <c r="G46" s="5">
+        <v>4</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" s="4">
+        <v>3</v>
+      </c>
+      <c r="G47" s="5">
+        <v>4</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="O47" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="P44" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:16">
-      <c r="A45" s="5">
-        <v>2001</v>
-      </c>
-      <c r="B45" s="5">
-        <v>1</v>
-      </c>
-      <c r="C45" s="5">
-        <v>11</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="P47" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B48" s="4">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4">
+        <v>2</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="4">
+        <v>4</v>
+      </c>
+      <c r="G48" s="5">
+        <v>4</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B49" s="4">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4">
+        <v>4</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="4">
+        <v>5</v>
+      </c>
+      <c r="G49" s="5">
+        <v>4</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B50" s="4">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4">
+        <v>15</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="4">
+        <v>6</v>
+      </c>
+      <c r="G50" s="5">
+        <v>4</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5">
-        <v>1</v>
-      </c>
-      <c r="G45" s="6">
+      <c r="K50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="4">
+        <v>2007</v>
+      </c>
+      <c r="B51" s="4">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4">
+        <v>5</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="4">
+        <v>7</v>
+      </c>
+      <c r="G51" s="5">
         <v>4</v>
       </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="O45" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="P45" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:16">
-      <c r="A46" s="5">
-        <v>2002</v>
-      </c>
-      <c r="B46" s="5">
-        <v>1</v>
-      </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5">
-        <v>2</v>
-      </c>
-      <c r="G46" s="6">
-        <v>4</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J46" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K46" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="L46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="O46" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="P46" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:16">
-      <c r="A47" s="5">
-        <v>2003</v>
-      </c>
-      <c r="B47" s="3">
-        <v>1</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" s="19"/>
-      <c r="F47" s="5">
-        <v>3</v>
-      </c>
-      <c r="G47" s="20">
-        <v>4</v>
-      </c>
-      <c r="H47" s="20"/>
-      <c r="I47" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J47" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:16">
-      <c r="A48" s="5">
-        <v>2004</v>
-      </c>
-      <c r="B48" s="5">
-        <v>1</v>
-      </c>
-      <c r="C48" s="5">
-        <v>2</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5">
-        <v>4</v>
-      </c>
-      <c r="G48" s="6">
-        <v>4</v>
-      </c>
-      <c r="H48" s="6"/>
-      <c r="I48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5" t="s">
+      <c r="I51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="O48" s="5" t="s">
+      <c r="O51" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="P48" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:16">
-      <c r="A49" s="5">
-        <v>2005</v>
-      </c>
-      <c r="B49" s="15">
-        <v>1</v>
-      </c>
-      <c r="C49" s="15">
-        <v>4</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="5">
-        <v>5</v>
-      </c>
-      <c r="G49" s="16">
-        <v>4</v>
-      </c>
-      <c r="H49" s="16"/>
-      <c r="I49" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J49" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K49" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15" t="s">
+      <c r="P51" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="4">
+        <v>126</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="O49" s="15" t="s">
+      <c r="G52" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="P49" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:16">
-      <c r="A50" s="5">
-        <v>2006</v>
-      </c>
-      <c r="B50" s="15">
-        <v>1</v>
-      </c>
-      <c r="C50" s="15">
-        <v>15</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15">
-        <v>6</v>
-      </c>
-      <c r="G50" s="16">
-        <v>4</v>
-      </c>
-      <c r="H50" s="16"/>
-      <c r="I50" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K50" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="L50" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="15"/>
-      <c r="N50" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="O50" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="P50" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:16">
-      <c r="A51" s="5">
-        <v>2007</v>
-      </c>
-      <c r="B51" s="15">
-        <v>1</v>
-      </c>
-      <c r="C51" s="15">
-        <v>5</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15">
-        <v>7</v>
-      </c>
-      <c r="G51" s="16">
-        <v>4</v>
-      </c>
-      <c r="H51" s="16"/>
-      <c r="I51" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K51" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="15"/>
-      <c r="N51" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="O51" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="P51" s="5" t="s">
-        <v>39</v>
+      <c r="K52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -661,6 +661,12 @@
     <t>Grid (26)</t>
   </si>
   <si>
+    <t>充值引导</t>
+  </si>
+  <si>
+    <t>NOT(accountTotalRecharge(0.001))</t>
+  </si>
+  <si>
     <t>首页</t>
   </si>
   <si>
@@ -731,12 +737,6 @@
   </si>
   <si>
     <t>btn_lottery</t>
-  </si>
-  <si>
-    <t>充值引导</t>
-  </si>
-  <si>
-    <t>NOT(accountTotalRecharge(0.001))</t>
   </si>
 </sst>
 </file>
@@ -944,12 +944,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3218,42 +3218,33 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="4">
-        <v>1001</v>
-      </c>
-      <c r="B40" s="4">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F40" s="4">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5">
-        <v>5</v>
-      </c>
-      <c r="I40" s="4" t="s">
+      <c r="G40" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J40" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>34</v>
+      <c r="J40" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="L40" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="O40" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>40</v>
+      <c r="N40" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="4">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B41" s="4">
         <v>1</v>
@@ -3262,7 +3253,7 @@
         <v>114</v>
       </c>
       <c r="F41" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="5">
         <v>5</v>
@@ -3288,7 +3279,7 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="4">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B42" s="4">
         <v>1</v>
@@ -3297,7 +3288,7 @@
         <v>116</v>
       </c>
       <c r="F42" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="5">
         <v>5</v>
@@ -3323,7 +3314,7 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="4">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B43" s="4">
         <v>1</v>
@@ -3332,7 +3323,7 @@
         <v>118</v>
       </c>
       <c r="F43" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="5">
         <v>5</v>
@@ -3344,7 +3335,7 @@
         <v>34</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L43" s="4" t="b">
         <v>1</v>
@@ -3358,7 +3349,7 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="4">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B44" s="4">
         <v>1</v>
@@ -3367,7 +3358,7 @@
         <v>120</v>
       </c>
       <c r="F44" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G44" s="5">
         <v>5</v>
@@ -3376,10 +3367,10 @@
         <v>33</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="L44" s="4" t="b">
         <v>1</v>
@@ -3393,37 +3384,31 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="4">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="B45" s="4">
         <v>1</v>
       </c>
-      <c r="C45" s="4">
-        <v>11</v>
-      </c>
       <c r="D45" s="4" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="F45" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G45" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="L45" s="4" t="b">
         <v>1</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="O45" s="4" t="s">
         <v>123</v>
@@ -3434,28 +3419,31 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="4">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
       </c>
+      <c r="C46" s="4">
+        <v>11</v>
+      </c>
       <c r="D46" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F46" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="5">
         <v>4</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L46" s="4" t="b">
         <v>1</v>
@@ -3467,36 +3455,36 @@
         <v>125</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="4">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B47" s="4">
         <v>1</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="F47" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5">
         <v>4</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="L47" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>126</v>
@@ -3505,24 +3493,21 @@
         <v>127</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="4">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B48" s="4">
         <v>1</v>
       </c>
-      <c r="C48" s="4">
-        <v>2</v>
-      </c>
       <c r="D48" s="4" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="F48" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="5">
         <v>4</v>
@@ -3537,7 +3522,7 @@
         <v>34</v>
       </c>
       <c r="L48" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>128</v>
@@ -3551,19 +3536,19 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="4">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B49" s="4">
         <v>1</v>
       </c>
       <c r="C49" s="4">
+        <v>2</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="4">
         <v>4</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="4">
-        <v>5</v>
       </c>
       <c r="G49" s="5">
         <v>4</v>
@@ -3587,36 +3572,36 @@
         <v>131</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="4">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B50" s="4">
         <v>1</v>
       </c>
       <c r="C50" s="4">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F50" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G50" s="5">
         <v>4</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="L50" s="4" t="b">
         <v>1</v>
@@ -3628,36 +3613,36 @@
         <v>133</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="4">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B51" s="4">
         <v>1</v>
       </c>
       <c r="C51" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F51" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G51" s="5">
         <v>4</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="L51" s="4" t="b">
         <v>1</v>
@@ -3669,32 +3654,47 @@
         <v>135</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="4">
-        <v>126</v>
+        <v>2007</v>
+      </c>
+      <c r="B52" s="4">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4">
+        <v>5</v>
       </c>
       <c r="D52" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F52" s="4">
+        <v>7</v>
+      </c>
+      <c r="G52" s="5">
+        <v>4</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J52" s="3" t="s">
+      <c r="O52" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="L52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N52" s="4" t="s">
+      <c r="P52" s="4" t="s">
         <v>35</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28770" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="142">
   <si>
     <t>id</t>
   </si>
@@ -361,6 +361,12 @@
     <t>提示文本ID</t>
   </si>
   <si>
+    <t>web端</t>
+  </si>
+  <si>
+    <t>前端触发</t>
+  </si>
+  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -412,6 +418,12 @@
     <t>tips</t>
   </si>
   <si>
+    <t>webimg</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
     <t>client</t>
   </si>
   <si>
@@ -679,16 +691,16 @@
     <t>tap_activity</t>
   </si>
   <si>
-    <t>商城</t>
-  </si>
-  <si>
-    <t>btn_shop</t>
-  </si>
-  <si>
-    <t>赌场</t>
-  </si>
-  <si>
-    <t>btn_casino</t>
+    <t>菜单</t>
+  </si>
+  <si>
+    <t>btn_muen</t>
+  </si>
+  <si>
+    <t>分享</t>
+  </si>
+  <si>
+    <t>btn_share</t>
   </si>
   <si>
     <t>创房间</t>
@@ -1808,11 +1820,13 @@
     <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
     <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
     <col min="13" max="13" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="14" max="14" width="26" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="4"/>
+    <col min="14" max="14" width="12.9416666666667" style="4" customWidth="1"/>
+    <col min="15" max="15" width="14.4083333333333" style="4" customWidth="1"/>
+    <col min="16" max="16" width="26" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:16">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1852,89 +1866,107 @@
       <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:14">
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:16">
       <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>13</v>
-      </c>
       <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="K2" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:14">
+        <v>15</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:16">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:16">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1944,50 +1976,53 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="12"/>
-      <c r="N5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5" s="4"/>
+      <c r="P5" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1996,32 +2031,33 @@
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L6" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M6" s="12"/>
-      <c r="N6" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="N6" s="4"/>
+      <c r="P6" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2030,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -2039,23 +2075,24 @@
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L7" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M7" s="12"/>
-      <c r="N7" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7" s="4"/>
+      <c r="P7" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2064,10 +2101,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -2077,23 +2114,24 @@
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L8" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M8" s="12"/>
-      <c r="N8" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8" s="4"/>
+      <c r="P8" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2102,7 +2140,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -2111,33 +2149,34 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L9" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M9" s="12"/>
-      <c r="N9" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9" s="4"/>
+      <c r="P9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -2145,30 +2184,31 @@
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L10" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M10" s="12"/>
-      <c r="N10" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10" s="4"/>
+      <c r="P10" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="12">
         <v>7</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -2177,30 +2217,31 @@
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L11" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M11" s="12"/>
-      <c r="N11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11" s="4"/>
+      <c r="P11" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="12">
         <v>8</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2209,55 +2250,57 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L12" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M12" s="12"/>
-      <c r="N12" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="N12" s="4"/>
+      <c r="P12" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="12">
         <v>9</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L13" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M13" s="12"/>
-      <c r="N13" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="N13" s="4"/>
+      <c r="P13" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2266,10 +2309,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2279,23 +2322,24 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="12"/>
-      <c r="N14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="N14" s="4"/>
+      <c r="P14" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="14">
         <v>101</v>
       </c>
@@ -2304,10 +2348,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2317,13 +2361,13 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L15" s="14" t="b">
         <v>1</v>
@@ -2331,11 +2375,12 @@
       <c r="M15" s="14">
         <v>47061</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="N15" s="4"/>
+      <c r="P15" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="14">
         <v>102</v>
       </c>
@@ -2346,10 +2391,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2359,23 +2404,24 @@
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L16" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M16" s="14"/>
-      <c r="N16" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="N16" s="4"/>
+      <c r="P16" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="14">
         <v>103</v>
       </c>
@@ -2386,10 +2432,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2399,23 +2445,24 @@
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L17" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M17" s="14"/>
-      <c r="N17" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="N17" s="4"/>
+      <c r="P17" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="14">
         <v>104</v>
       </c>
@@ -2426,10 +2473,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2439,23 +2486,24 @@
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L18" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M18" s="14"/>
-      <c r="N18" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="N18" s="4"/>
+      <c r="P18" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -2464,10 +2512,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2477,23 +2525,24 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L19" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M19" s="14"/>
-      <c r="N19" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="N19" s="4"/>
+      <c r="P19" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="14">
         <v>106</v>
       </c>
@@ -2504,10 +2553,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2517,23 +2566,24 @@
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L20" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M20" s="14"/>
-      <c r="N20" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="N20" s="4"/>
+      <c r="P20" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="14">
         <v>107</v>
       </c>
@@ -2544,10 +2594,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2557,23 +2607,24 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L21" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M21" s="14"/>
-      <c r="N21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="N21" s="4"/>
+      <c r="P21" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="14">
         <v>108</v>
       </c>
@@ -2584,10 +2635,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2597,23 +2648,24 @@
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L22" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M22" s="14"/>
-      <c r="N22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="N22" s="4"/>
+      <c r="P22" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="14">
         <v>109</v>
       </c>
@@ -2622,10 +2674,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2635,23 +2687,24 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L23" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M23" s="14"/>
-      <c r="N23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="N23" s="4"/>
+      <c r="P23" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="14">
         <v>110</v>
       </c>
@@ -2660,10 +2713,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2673,23 +2726,24 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L24" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="N24" s="4"/>
+      <c r="P24" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="14">
         <v>111</v>
       </c>
@@ -2698,10 +2752,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2711,23 +2765,24 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L25" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M25" s="14"/>
-      <c r="N25" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="N25" s="4"/>
+      <c r="P25" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="14">
         <v>112</v>
       </c>
@@ -2736,10 +2791,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2749,23 +2804,24 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L26" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M26" s="14"/>
-      <c r="N26" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:14">
+      <c r="N26" s="4"/>
+      <c r="P26" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:16">
       <c r="A27" s="2">
         <v>113</v>
       </c>
@@ -2774,10 +2830,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2787,22 +2843,22 @@
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:14">
+      <c r="P27" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:16">
       <c r="A28" s="3">
         <v>114</v>
       </c>
@@ -2811,10 +2867,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2824,22 +2880,22 @@
       </c>
       <c r="H28" s="19"/>
       <c r="I28" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N28" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:14">
+      <c r="P28" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:16">
       <c r="A29" s="2">
         <v>115</v>
       </c>
@@ -2848,10 +2904,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2861,22 +2917,22 @@
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:14">
+      <c r="P29" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:16">
       <c r="A30" s="2">
         <v>116</v>
       </c>
@@ -2885,10 +2941,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2898,22 +2954,22 @@
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:14">
+      <c r="P30" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:16">
       <c r="A31" s="2">
         <v>117</v>
       </c>
@@ -2922,10 +2978,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2935,22 +2991,22 @@
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N31" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:14">
+      <c r="P31" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:16">
       <c r="A32" s="2">
         <v>118</v>
       </c>
@@ -2959,10 +3015,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -2972,19 +3028,19 @@
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>40</v>
+      <c r="P32" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:16">
@@ -2995,10 +3051,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -3008,19 +3064,19 @@
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>40</v>
+      <c r="P33" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3032,10 +3088,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -3045,20 +3101,21 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L34" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M34" s="3"/>
-      <c r="N34" s="3" t="s">
-        <v>40</v>
+      <c r="N34" s="3"/>
+      <c r="P34" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3069,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -3078,20 +3135,21 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="2"/>
-      <c r="N35" s="2" t="s">
-        <v>40</v>
+      <c r="N35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3099,16 +3157,16 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
@@ -3122,10 +3180,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F37" s="4">
         <v>24</v>
@@ -3134,13 +3192,13 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L37" s="2" t="b">
         <v>0</v>
@@ -3154,10 +3212,10 @@
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F38" s="4">
         <v>25</v>
@@ -3166,19 +3224,20 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L38" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>40</v>
+      <c r="N38" s="2"/>
+      <c r="P38" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3189,10 +3248,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F39" s="4">
         <v>26</v>
@@ -3201,19 +3260,20 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L39" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="s">
-        <v>40</v>
+      <c r="N39" s="2"/>
+      <c r="P39" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3221,25 +3281,25 @@
         <v>126</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L40" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N40" s="4" t="s">
-        <v>35</v>
+      <c r="P40" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3250,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F41" s="4">
         <v>1</v>
@@ -3259,22 +3319,22 @@
         <v>5</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L41" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3285,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F42" s="4">
         <v>2</v>
@@ -3294,22 +3354,22 @@
         <v>5</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L42" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3320,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F43" s="4">
         <v>3</v>
@@ -3329,22 +3389,22 @@
         <v>5</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L43" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3354,8 +3414,11 @@
       <c r="B44" s="4">
         <v>1</v>
       </c>
+      <c r="C44" s="4">
+        <v>6</v>
+      </c>
       <c r="D44" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F44" s="4">
         <v>4</v>
@@ -3364,22 +3427,22 @@
         <v>5</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L44" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3390,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F45" s="4">
         <v>5</v>
@@ -3399,22 +3462,22 @@
         <v>5</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3428,7 +3491,7 @@
         <v>11</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F46" s="4">
         <v>1</v>
@@ -3437,25 +3500,25 @@
         <v>4</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L46" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3466,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F47" s="4">
         <v>2</v>
@@ -3475,25 +3538,25 @@
         <v>4</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L47" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3504,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F48" s="4">
         <v>3</v>
@@ -3513,25 +3576,25 @@
         <v>4</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L48" s="4" t="b">
         <v>0</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3545,7 +3608,7 @@
         <v>2</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F49" s="4">
         <v>4</v>
@@ -3554,25 +3617,25 @@
         <v>4</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L49" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3586,7 +3649,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F50" s="4">
         <v>5</v>
@@ -3595,25 +3658,25 @@
         <v>4</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L50" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3627,7 +3690,7 @@
         <v>15</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F51" s="4">
         <v>6</v>
@@ -3636,25 +3699,25 @@
         <v>4</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L51" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3668,7 +3731,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F52" s="4">
         <v>7</v>
@@ -3677,25 +3740,25 @@
         <v>4</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L52" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="143">
   <si>
     <t>id</t>
   </si>
@@ -457,6 +457,9 @@
     <t>官方派奖</t>
   </si>
   <si>
+    <t>Grid (27)</t>
+  </si>
+  <si>
     <t>显示位置：大厅</t>
   </si>
   <si>
@@ -718,7 +721,7 @@
     <t>djlb-3</t>
   </si>
   <si>
-    <t>btn_stage_rechare</t>
+    <t>btn_level_gift</t>
   </si>
   <si>
     <t>qtlc-6</t>
@@ -956,12 +959,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2017,7 +2020,6 @@
         <v>0</v>
       </c>
       <c r="M5" s="12"/>
-      <c r="N5" s="4"/>
       <c r="P5" s="4" t="s">
         <v>39</v>
       </c>
@@ -2052,7 +2054,6 @@
         <v>1</v>
       </c>
       <c r="M6" s="12"/>
-      <c r="N6" s="4"/>
       <c r="P6" s="4" t="s">
         <v>39</v>
       </c>
@@ -2061,14 +2062,18 @@
       <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
       <c r="C7" s="12">
         <v>9</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>44</v>
+      </c>
       <c r="F7" s="12"/>
       <c r="G7" s="13">
         <v>1</v>
@@ -2087,9 +2092,8 @@
         <v>1</v>
       </c>
       <c r="M7" s="12"/>
-      <c r="N7" s="4"/>
       <c r="P7" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2101,10 +2105,10 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" s="12">
         <v>5</v>
@@ -2126,9 +2130,8 @@
         <v>1</v>
       </c>
       <c r="M8" s="12"/>
-      <c r="N8" s="4"/>
       <c r="P8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2140,7 +2143,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -2161,9 +2164,8 @@
         <v>1</v>
       </c>
       <c r="M9" s="12"/>
-      <c r="N9" s="4"/>
       <c r="P9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2173,10 +2175,10 @@
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="13">
@@ -2196,9 +2198,8 @@
         <v>1</v>
       </c>
       <c r="M10" s="12"/>
-      <c r="N10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2208,7 +2209,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -2229,9 +2230,8 @@
         <v>1</v>
       </c>
       <c r="M11" s="12"/>
-      <c r="N11" s="4"/>
       <c r="P11" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2241,7 +2241,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -2250,21 +2250,20 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L12" s="12" t="b">
         <v>1</v>
       </c>
       <c r="M12" s="12"/>
-      <c r="N12" s="4"/>
       <c r="P12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2274,7 +2273,7 @@
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -2295,7 +2294,6 @@
         <v>1</v>
       </c>
       <c r="M13" s="12"/>
-      <c r="N13" s="4"/>
       <c r="P13" s="4" t="s">
         <v>39</v>
       </c>
@@ -2309,10 +2307,10 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
@@ -2334,9 +2332,8 @@
         <v>0</v>
       </c>
       <c r="M14" s="12"/>
-      <c r="N14" s="4"/>
       <c r="P14" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2348,10 +2345,10 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -2361,13 +2358,13 @@
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L15" s="14" t="b">
         <v>1</v>
@@ -2375,7 +2372,6 @@
       <c r="M15" s="14">
         <v>47061</v>
       </c>
-      <c r="N15" s="4"/>
       <c r="P15" s="4" t="s">
         <v>39</v>
       </c>
@@ -2391,10 +2387,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
@@ -2416,9 +2412,8 @@
         <v>1</v>
       </c>
       <c r="M16" s="14"/>
-      <c r="N16" s="4"/>
       <c r="P16" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2432,10 +2427,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" s="14">
         <v>9</v>
@@ -2457,7 +2452,6 @@
         <v>1</v>
       </c>
       <c r="M17" s="14"/>
-      <c r="N17" s="4"/>
       <c r="P17" s="4" t="s">
         <v>39</v>
       </c>
@@ -2473,10 +2467,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -2498,7 +2492,6 @@
         <v>1</v>
       </c>
       <c r="M18" s="14"/>
-      <c r="N18" s="4"/>
       <c r="P18" s="4" t="s">
         <v>39</v>
       </c>
@@ -2512,10 +2505,10 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="14">
         <v>6</v>
@@ -2525,19 +2518,18 @@
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L19" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M19" s="14"/>
-      <c r="N19" s="4"/>
       <c r="P19" s="4" t="s">
         <v>39</v>
       </c>
@@ -2553,10 +2545,10 @@
         <v>11</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" s="14">
         <v>7</v>
@@ -2569,18 +2561,17 @@
         <v>41</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L20" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M20" s="14"/>
-      <c r="N20" s="4"/>
       <c r="P20" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2594,10 +2585,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="14">
         <v>8</v>
@@ -2607,21 +2598,20 @@
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L21" s="14" t="b">
         <v>1</v>
       </c>
       <c r="M21" s="14"/>
-      <c r="N21" s="4"/>
       <c r="P21" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2635,10 +2625,10 @@
         <v>10</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -2660,9 +2650,8 @@
         <v>1</v>
       </c>
       <c r="M22" s="14"/>
-      <c r="N22" s="4"/>
       <c r="P22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2674,10 +2663,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
@@ -2699,9 +2688,8 @@
         <v>1</v>
       </c>
       <c r="M23" s="14"/>
-      <c r="N23" s="4"/>
       <c r="P23" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2713,10 +2701,10 @@
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F24" s="14">
         <v>13</v>
@@ -2738,9 +2726,8 @@
         <v>1</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="4"/>
       <c r="P24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2752,10 +2739,10 @@
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
@@ -2777,9 +2764,8 @@
         <v>1</v>
       </c>
       <c r="M25" s="14"/>
-      <c r="N25" s="4"/>
       <c r="P25" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2791,10 +2777,10 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F26" s="14">
         <v>15</v>
@@ -2816,9 +2802,8 @@
         <v>1</v>
       </c>
       <c r="M26" s="14"/>
-      <c r="N26" s="4"/>
       <c r="P26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:16">
@@ -2830,10 +2815,10 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F27" s="2">
         <v>16</v>
@@ -2843,13 +2828,13 @@
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
@@ -2867,10 +2852,10 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" s="3">
         <v>17</v>
@@ -2892,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:16">
@@ -2904,10 +2889,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
@@ -2917,19 +2902,19 @@
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:16">
@@ -2941,10 +2926,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
@@ -2954,19 +2939,19 @@
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:16">
@@ -2978,10 +2963,10 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
@@ -2991,19 +2976,19 @@
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:16">
@@ -3015,10 +3000,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
@@ -3028,19 +3013,19 @@
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:16">
@@ -3051,10 +3036,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F33" s="3">
         <v>22</v>
@@ -3076,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3088,10 +3073,10 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
@@ -3115,7 +3100,7 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="P34" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3126,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F35" s="4">
         <v>23</v>
@@ -3149,7 +3134,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="P35" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3157,7 +3142,7 @@
         <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>37</v>
@@ -3180,10 +3165,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F37" s="4">
         <v>24</v>
@@ -3212,10 +3197,10 @@
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F38" s="4">
         <v>25</v>
@@ -3237,7 +3222,7 @@
       </c>
       <c r="N38" s="2"/>
       <c r="P38" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3248,10 +3233,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F39" s="4">
         <v>26</v>
@@ -3273,7 +3258,7 @@
       </c>
       <c r="N39" s="2"/>
       <c r="P39" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3281,7 +3266,7 @@
         <v>126</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>36</v>
@@ -3290,10 +3275,10 @@
         <v>37</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L40" s="4" t="b">
         <v>1</v>
@@ -3310,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F41" s="4">
         <v>1</v>
@@ -3331,10 +3316,10 @@
         <v>1</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3345,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F42" s="4">
         <v>2</v>
@@ -3366,10 +3351,10 @@
         <v>1</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3380,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F43" s="4">
         <v>3</v>
@@ -3401,10 +3386,10 @@
         <v>1</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3418,7 +3403,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F44" s="4">
         <v>4</v>
@@ -3439,10 +3424,10 @@
         <v>1</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3453,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F45" s="4">
         <v>5</v>
@@ -3465,19 +3450,19 @@
         <v>37</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3491,7 +3476,7 @@
         <v>11</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F46" s="4">
         <v>1</v>
@@ -3503,22 +3488,22 @@
         <v>41</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L46" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3529,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F47" s="4">
         <v>2</v>
@@ -3538,22 +3523,22 @@
         <v>4</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L47" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P47" s="4" t="s">
         <v>39</v>
@@ -3567,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F48" s="4">
         <v>3</v>
@@ -3588,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3608,7 +3593,7 @@
         <v>2</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F49" s="4">
         <v>4</v>
@@ -3629,13 +3614,13 @@
         <v>1</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3649,7 +3634,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F50" s="4">
         <v>5</v>
@@ -3670,10 +3655,10 @@
         <v>1</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P50" s="4" t="s">
         <v>39</v>
@@ -3690,7 +3675,7 @@
         <v>15</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F51" s="4">
         <v>6</v>
@@ -3699,25 +3684,25 @@
         <v>4</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L51" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3731,7 +3716,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F52" s="4">
         <v>7</v>
@@ -3752,10 +3737,10 @@
         <v>1</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P52" s="4" t="s">
         <v>39</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28770" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -680,6 +680,9 @@
   </si>
   <si>
     <t>NOT(accountTotalRecharge(0.001))</t>
+  </si>
+  <si>
+    <t>免费旋转</t>
   </si>
   <si>
     <t>首页</t>
@@ -1807,7 +1810,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -3289,34 +3292,25 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="4">
-        <v>1001</v>
-      </c>
-      <c r="B41" s="4">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F41" s="4">
-        <v>1</v>
-      </c>
       <c r="G41" s="5">
-        <v>5</v>
-      </c>
-      <c r="I41" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K41" s="4" t="s">
+      <c r="J41" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="14" t="s">
         <v>38</v>
       </c>
       <c r="L41" s="4" t="b">
         <v>1</v>
-      </c>
-      <c r="O41" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="P41" s="4" t="s">
         <v>45</v>
@@ -3324,16 +3318,16 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="4">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B42" s="4">
         <v>1</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F42" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="5">
         <v>5</v>
@@ -3351,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P42" s="4" t="s">
         <v>45</v>
@@ -3359,16 +3353,16 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="4">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B43" s="4">
         <v>1</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F43" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="5">
         <v>5</v>
@@ -3386,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P43" s="4" t="s">
         <v>45</v>
@@ -3394,19 +3388,16 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="4">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B44" s="4">
         <v>1</v>
       </c>
-      <c r="C44" s="4">
-        <v>6</v>
-      </c>
       <c r="D44" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F44" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G44" s="5">
         <v>5</v>
@@ -3424,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P44" s="4" t="s">
         <v>45</v>
@@ -3432,16 +3423,19 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="4">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B45" s="4">
         <v>1</v>
       </c>
+      <c r="C45" s="4">
+        <v>6</v>
+      </c>
       <c r="D45" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F45" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G45" s="5">
         <v>5</v>
@@ -3450,16 +3444,16 @@
         <v>37</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P45" s="4" t="s">
         <v>45</v>
@@ -3467,40 +3461,34 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="4">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
       </c>
-      <c r="C46" s="4">
-        <v>11</v>
-      </c>
       <c r="D46" s="4" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="F46" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G46" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="L46" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N46" s="4" t="s">
+      <c r="O46" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="P46" s="4" t="s">
         <v>45</v>
@@ -3508,95 +3496,95 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="4">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B47" s="4">
         <v>1</v>
       </c>
+      <c r="C47" s="4">
+        <v>11</v>
+      </c>
       <c r="D47" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F47" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="5">
         <v>4</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L47" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O47" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="O47" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="P47" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="4">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B48" s="4">
         <v>1</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F48" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="5">
         <v>4</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L48" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="O48" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="O48" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="P48" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="4">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B49" s="4">
         <v>1</v>
       </c>
-      <c r="C49" s="4">
-        <v>2</v>
-      </c>
       <c r="D49" s="4" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="F49" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" s="5">
         <v>4</v>
@@ -3611,13 +3599,13 @@
         <v>38</v>
       </c>
       <c r="L49" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="O49" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="O49" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="P49" s="4" t="s">
         <v>45</v>
@@ -3625,19 +3613,19 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="4">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B50" s="4">
         <v>1</v>
       </c>
       <c r="C50" s="4">
+        <v>2</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" s="4">
         <v>4</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F50" s="4">
-        <v>5</v>
       </c>
       <c r="G50" s="5">
         <v>4</v>
@@ -3655,94 +3643,135 @@
         <v>1</v>
       </c>
       <c r="N50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="O50" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="O50" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="P50" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="4">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B51" s="4">
         <v>1</v>
       </c>
       <c r="C51" s="4">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F51" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G51" s="5">
         <v>4</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="L51" s="4" t="b">
         <v>1</v>
       </c>
       <c r="N51" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="O51" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="O51" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="P51" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="4">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
       </c>
       <c r="C52" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F52" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G52" s="5">
         <v>4</v>
       </c>
       <c r="I52" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="4">
+        <v>2007</v>
+      </c>
+      <c r="B53" s="4">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4">
+        <v>5</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F53" s="4">
+        <v>7</v>
+      </c>
+      <c r="G53" s="5">
+        <v>4</v>
+      </c>
+      <c r="I53" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J52" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N52" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="O52" s="4" t="s">
+      <c r="J53" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="P52" s="4" t="s">
+      <c r="O53" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="P53" s="4" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28770" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="142">
   <si>
     <t>id</t>
   </si>
@@ -703,16 +703,10 @@
     <t>btn_muen</t>
   </si>
   <si>
-    <t>分享</t>
-  </si>
-  <si>
-    <t>btn_share</t>
-  </si>
-  <si>
-    <t>创房间</t>
-  </si>
-  <si>
-    <t>btn_create</t>
+    <t>btn_service</t>
+  </si>
+  <si>
+    <t>btn_shop</t>
   </si>
   <si>
     <t>sc-7</t>
@@ -3428,11 +3422,8 @@
       <c r="B45" s="4">
         <v>1</v>
       </c>
-      <c r="C45" s="4">
-        <v>6</v>
-      </c>
       <c r="D45" s="4" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="F45" s="4">
         <v>4</v>
@@ -3453,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P45" s="4" t="s">
         <v>45</v>
@@ -3467,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="F46" s="4">
         <v>5</v>
@@ -3479,16 +3470,16 @@
         <v>37</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L46" s="4" t="b">
         <v>1</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P46" s="4" t="s">
         <v>45</v>
@@ -3526,10 +3517,10 @@
         <v>1</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P47" s="4" t="s">
         <v>45</v>
@@ -3564,10 +3555,10 @@
         <v>1</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P48" s="4" t="s">
         <v>39</v>
@@ -3602,10 +3593,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P49" s="4" t="s">
         <v>45</v>
@@ -3643,10 +3634,10 @@
         <v>1</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P50" s="4" t="s">
         <v>45</v>
@@ -3684,10 +3675,10 @@
         <v>1</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P51" s="4" t="s">
         <v>39</v>
@@ -3725,10 +3716,10 @@
         <v>1</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P52" s="4" t="s">
         <v>45</v>
@@ -3766,10 +3757,10 @@
         <v>1</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P53" s="4" t="s">
         <v>39</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28770" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -602,12 +602,6 @@
   </si>
   <si>
     <t>Grid (12)</t>
-  </si>
-  <si>
-    <t>1_999</t>
-  </si>
-  <si>
-    <t>playerLevel(999)</t>
   </si>
   <si>
     <t>每日充值</t>
@@ -761,7 +755,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,30 +778,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -967,7 +944,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -983,12 +960,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1299,137 +1270,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1466,29 +1437,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1989,817 +1945,817 @@
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
     </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="12">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12" t="s">
+    <row r="5" s="2" customFormat="1" spans="1:16">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="H5" s="12"/>
+      <c r="I5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="P5" s="4" t="s">
+      <c r="M5" s="2"/>
+      <c r="P5" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="12">
+    <row r="6" s="3" customFormat="1" spans="1:16">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
       <c r="G6" s="13" t="s">
         <v>36</v>
       </c>
       <c r="H6" s="13"/>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="P6" s="4" t="s">
+      <c r="L6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="P6" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="12">
+    <row r="7" s="3" customFormat="1" spans="1:16">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="12">
-        <v>1</v>
-      </c>
-      <c r="C7" s="12">
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
         <v>9</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="13">
         <v>1</v>
       </c>
       <c r="H7" s="13"/>
-      <c r="I7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="12"/>
-      <c r="P7" s="4" t="s">
+      <c r="I7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="P7" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="12">
+    <row r="8" s="3" customFormat="1" spans="1:16">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="12">
-        <v>1</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12" t="s">
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="3">
         <v>5</v>
       </c>
       <c r="G8" s="13">
         <v>1</v>
       </c>
       <c r="H8" s="13"/>
-      <c r="I8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="P8" s="4" t="s">
+      <c r="I8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="P8" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="12">
+    <row r="9" s="3" customFormat="1" spans="1:16">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="13">
         <v>1</v>
       </c>
       <c r="H9" s="13"/>
-      <c r="I9" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="P9" s="4" t="s">
+      <c r="I9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="P9" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="12">
+    <row r="10" s="3" customFormat="1" spans="1:16">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="13">
         <v>1</v>
       </c>
       <c r="H10" s="13"/>
-      <c r="I10" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="12"/>
-      <c r="P10" s="4" t="s">
+      <c r="I10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="P10" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="12">
+    <row r="11" s="3" customFormat="1" spans="1:16">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="13">
         <v>1</v>
       </c>
       <c r="H11" s="13"/>
-      <c r="I11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="12"/>
-      <c r="P11" s="4" t="s">
+      <c r="I11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="P11" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="12">
+    <row r="12" s="3" customFormat="1" spans="1:16">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="13">
         <v>1</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="12"/>
-      <c r="P12" s="4" t="s">
+      <c r="L12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3"/>
+      <c r="P12" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="12">
+    <row r="13" s="3" customFormat="1" spans="1:16">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12" t="s">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="13" t="s">
         <v>36</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="12"/>
-      <c r="P13" s="4" t="s">
+      <c r="I13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="P13" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="12">
+    <row r="14" s="3" customFormat="1" spans="1:16">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="12">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12" t="s">
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="3">
         <v>4</v>
       </c>
       <c r="G14" s="13">
         <v>1</v>
       </c>
       <c r="H14" s="13"/>
-      <c r="I14" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="2" t="b">
+      <c r="I14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="P14" s="4" t="s">
+      <c r="M14" s="3"/>
+      <c r="P14" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="14">
+    <row r="15" s="3" customFormat="1" spans="1:16">
+      <c r="A15" s="3">
         <v>101</v>
       </c>
-      <c r="B15" s="14">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14" t="s">
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14" t="s">
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13">
+        <v>1</v>
+      </c>
+      <c r="H15" s="13"/>
+      <c r="I15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="K15" s="14" t="s">
+      <c r="J15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="L15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="14">
+      <c r="L15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3">
         <v>47061</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="P15" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="14">
+    <row r="16" s="3" customFormat="1" spans="1:16">
+      <c r="A16" s="3">
         <v>102</v>
       </c>
-      <c r="B16" s="14">
-        <v>1</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
         <v>2</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="3">
         <v>2</v>
       </c>
-      <c r="G16" s="15">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="P16" s="4" t="s">
+      <c r="G16" s="13">
+        <v>1</v>
+      </c>
+      <c r="H16" s="13"/>
+      <c r="I16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3"/>
+      <c r="P16" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="14">
+    <row r="17" s="3" customFormat="1" spans="1:16">
+      <c r="A17" s="3">
         <v>103</v>
       </c>
-      <c r="B17" s="14">
-        <v>1</v>
-      </c>
-      <c r="C17" s="14">
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
         <v>5</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="3">
         <v>9</v>
       </c>
-      <c r="G17" s="15">
-        <v>1</v>
-      </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="14"/>
-      <c r="P17" s="4" t="s">
+      <c r="G17" s="13">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3"/>
+      <c r="P17" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="14">
+    <row r="18" s="3" customFormat="1" spans="1:16">
+      <c r="A18" s="3">
         <v>104</v>
       </c>
-      <c r="B18" s="14">
-        <v>1</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
         <v>4</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="15">
-        <v>1</v>
-      </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="14"/>
-      <c r="P18" s="4" t="s">
+      <c r="G18" s="13">
+        <v>1</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="P18" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="14">
+    <row r="19" s="3" customFormat="1" spans="1:16">
+      <c r="A19" s="3">
         <v>105</v>
       </c>
-      <c r="B19" s="14">
-        <v>1</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14" t="s">
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="3">
         <v>6</v>
       </c>
-      <c r="G19" s="15">
-        <v>1</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14" t="s">
+      <c r="G19" s="13">
+        <v>1</v>
+      </c>
+      <c r="H19" s="13"/>
+      <c r="I19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="14"/>
-      <c r="P19" s="4" t="s">
+      <c r="L19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3"/>
+      <c r="P19" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="14">
+    <row r="20" s="3" customFormat="1" spans="1:16">
+      <c r="A20" s="3">
         <v>106</v>
       </c>
-      <c r="B20" s="14">
-        <v>1</v>
-      </c>
-      <c r="C20" s="14">
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3">
         <v>11</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="3">
         <v>7</v>
       </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14" t="s">
+      <c r="G20" s="13">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="L20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="14"/>
-      <c r="P20" s="4" t="s">
+      <c r="L20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3"/>
+      <c r="P20" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="14">
+    <row r="21" s="3" customFormat="1" spans="1:16">
+      <c r="A21" s="3">
         <v>107</v>
       </c>
-      <c r="B21" s="14">
-        <v>1</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
         <v>15</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="3">
         <v>8</v>
       </c>
-      <c r="G21" s="15">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14" t="s">
+      <c r="G21" s="13">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13"/>
+      <c r="I21" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="L21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="14"/>
-      <c r="P21" s="4" t="s">
+      <c r="L21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="3"/>
+      <c r="P21" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="14">
+    <row r="22" s="3" customFormat="1" spans="1:16">
+      <c r="A22" s="3">
         <v>108</v>
       </c>
-      <c r="B22" s="14">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14">
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3">
         <v>10</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="3">
         <v>11</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="P22" s="4" t="s">
+      <c r="G22" s="13">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="I22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3"/>
+      <c r="P22" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="14">
+    <row r="23" s="3" customFormat="1" spans="1:16">
+      <c r="A23" s="3">
         <v>109</v>
       </c>
-      <c r="B23" s="14">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14" t="s">
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="3">
         <v>12</v>
       </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="P23" s="4" t="s">
+      <c r="G23" s="13">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="P23" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="14">
+    <row r="24" s="3" customFormat="1" spans="1:16">
+      <c r="A24" s="3">
         <v>110</v>
       </c>
-      <c r="B24" s="14">
-        <v>1</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14" t="s">
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="3">
         <v>13</v>
       </c>
-      <c r="G24" s="15">
-        <v>1</v>
-      </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="14"/>
-      <c r="P24" s="4" t="s">
+      <c r="G24" s="13">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13"/>
+      <c r="I24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="P24" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="14">
+    <row r="25" s="3" customFormat="1" spans="1:16">
+      <c r="A25" s="3">
         <v>111</v>
       </c>
-      <c r="B25" s="14">
-        <v>1</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14" t="s">
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="3">
         <v>14</v>
       </c>
-      <c r="G25" s="15">
-        <v>1</v>
-      </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="14"/>
-      <c r="P25" s="4" t="s">
+      <c r="G25" s="13">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3"/>
+      <c r="P25" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="14">
+    <row r="26" s="3" customFormat="1" spans="1:16">
+      <c r="A26" s="3">
         <v>112</v>
       </c>
-      <c r="B26" s="14">
-        <v>1</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14" t="s">
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="3">
         <v>15</v>
       </c>
-      <c r="G26" s="15">
-        <v>1</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L26" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="P26" s="4" t="s">
+      <c r="G26" s="13">
+        <v>1</v>
+      </c>
+      <c r="H26" s="13"/>
+      <c r="I26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="P26" s="3" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2820,18 +2776,18 @@
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="17">
-        <v>1</v>
-      </c>
-      <c r="H27" s="17"/>
+      <c r="G27" s="12">
+        <v>1</v>
+      </c>
+      <c r="H27" s="12"/>
       <c r="I27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>94</v>
+        <v>37</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
@@ -2840,40 +2796,40 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:16">
-      <c r="A28" s="3">
+    <row r="28" s="2" customFormat="1" spans="1:16">
+      <c r="A28" s="2">
         <v>114</v>
       </c>
-      <c r="B28" s="3">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" s="3">
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="2">
         <v>17</v>
       </c>
-      <c r="G28" s="19">
-        <v>1</v>
-      </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="14" t="s">
+      <c r="G28" s="12">
+        <v>1</v>
+      </c>
+      <c r="H28" s="12"/>
+      <c r="I28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P28" s="3" t="s">
+      <c r="P28" s="2" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2886,26 +2842,26 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>98</v>
+        <v>95</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="F29" s="2">
         <v>18</v>
       </c>
-      <c r="G29" s="17">
-        <v>1</v>
-      </c>
-      <c r="H29" s="17"/>
+      <c r="G29" s="12">
+        <v>1</v>
+      </c>
+      <c r="H29" s="12"/>
       <c r="I29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>94</v>
+        <v>37</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
@@ -2923,26 +2879,26 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>100</v>
+        <v>97</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="F30" s="2">
         <v>19</v>
       </c>
-      <c r="G30" s="17">
-        <v>1</v>
-      </c>
-      <c r="H30" s="17"/>
+      <c r="G30" s="12">
+        <v>1</v>
+      </c>
+      <c r="H30" s="12"/>
       <c r="I30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>94</v>
+        <v>37</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
@@ -2960,26 +2916,26 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="F31" s="2">
         <v>20</v>
       </c>
-      <c r="G31" s="17">
-        <v>1</v>
-      </c>
-      <c r="H31" s="17"/>
+      <c r="G31" s="12">
+        <v>1</v>
+      </c>
+      <c r="H31" s="12"/>
       <c r="I31" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>94</v>
+        <v>37</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
@@ -2997,26 +2953,26 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>104</v>
+        <v>101</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="F32" s="2">
         <v>21</v>
       </c>
-      <c r="G32" s="17">
-        <v>1</v>
-      </c>
-      <c r="H32" s="17"/>
+      <c r="G32" s="12">
+        <v>1</v>
+      </c>
+      <c r="H32" s="12"/>
       <c r="I32" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>94</v>
+        <v>37</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
@@ -3025,43 +2981,43 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" s="3" customFormat="1" spans="1:16">
-      <c r="A33" s="3">
+    <row r="33" s="2" customFormat="1" spans="1:16">
+      <c r="A33" s="2">
         <v>119</v>
       </c>
-      <c r="B33" s="3">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="B33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="2">
         <v>22</v>
       </c>
-      <c r="G33" s="19">
-        <v>1</v>
-      </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="14" t="s">
+      <c r="G33" s="12">
+        <v>1</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="s">
+      <c r="P33" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" s="3" customFormat="1" spans="1:16">
       <c r="A34" s="3">
         <v>120</v>
       </c>
@@ -3070,28 +3026,28 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F34" s="3">
         <v>10</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="13">
         <v>1</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J34" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" s="14" t="b">
+      <c r="J34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" s="3" t="b">
         <v>1</v>
       </c>
       <c r="M34" s="3"/>
@@ -3100,29 +3056,32 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="4">
+    <row r="35" s="2" customFormat="1" spans="1:16">
+      <c r="A35" s="2">
         <v>121</v>
       </c>
-      <c r="B35" s="4">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F35" s="4">
+      <c r="B35" s="2">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2">
         <v>23</v>
       </c>
-      <c r="G35" s="5">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K35" s="14" t="s">
+      <c r="G35" s="12">
+        <v>1</v>
+      </c>
+      <c r="H35" s="12"/>
+      <c r="I35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L35" s="2" t="b">
@@ -3134,635 +3093,686 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="4">
+    <row r="36" s="2" customFormat="1" spans="1:16">
+      <c r="A36" s="2">
         <v>122</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K36" s="14" t="s">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="4">
+    <row r="37" s="2" customFormat="1" spans="1:16">
+      <c r="A37" s="2">
         <v>123</v>
       </c>
-      <c r="B37" s="4">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F37" s="4">
+      <c r="B37" s="2">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="2">
         <v>24</v>
       </c>
-      <c r="G37" s="5">
-        <v>1</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="14" t="s">
+      <c r="G37" s="12">
+        <v>1</v>
+      </c>
+      <c r="H37" s="12"/>
+      <c r="I37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L37" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
-      <c r="A38" s="4">
+    <row r="38" s="3" customFormat="1" spans="1:16">
+      <c r="A38" s="3">
         <v>124</v>
       </c>
-      <c r="B38" s="4">
-        <v>1</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="B38" s="3">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F38" s="3">
+        <v>25</v>
+      </c>
+      <c r="G38" s="13">
+        <v>1</v>
+      </c>
+      <c r="H38" s="13"/>
+      <c r="I38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" spans="1:16">
+      <c r="A39" s="3">
+        <v>125</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="4">
-        <v>25</v>
-      </c>
-      <c r="G38" s="5">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L38" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="P38" s="2" t="s">
+      <c r="F39" s="3">
+        <v>26</v>
+      </c>
+      <c r="G39" s="13">
+        <v>1</v>
+      </c>
+      <c r="H39" s="13"/>
+      <c r="I39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
-      <c r="A39" s="4">
+    <row r="40" s="3" customFormat="1" spans="1:16">
+      <c r="A40" s="3">
+        <v>126</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" s="13"/>
+      <c r="I40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1" spans="1:16">
+      <c r="A41" s="3">
+        <v>127</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="13">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13"/>
+      <c r="I41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:16">
+      <c r="A42" s="3">
+        <v>1001</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
+        <v>1</v>
+      </c>
+      <c r="G42" s="13">
+        <v>5</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="1" spans="1:16">
+      <c r="A43" s="3">
+        <v>1002</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3">
+        <v>2</v>
+      </c>
+      <c r="G43" s="13">
+        <v>5</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" s="3" customFormat="1" spans="1:16">
+      <c r="A44" s="3">
+        <v>1003</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3">
+        <v>3</v>
+      </c>
+      <c r="G44" s="13">
+        <v>5</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="1" spans="1:16">
+      <c r="A45" s="3">
+        <v>1004</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3">
+        <v>4</v>
+      </c>
+      <c r="G45" s="13">
+        <v>5</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" s="3" customFormat="1" spans="1:16">
+      <c r="A46" s="3">
+        <v>1005</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3">
+        <v>5</v>
+      </c>
+      <c r="G46" s="13">
+        <v>5</v>
+      </c>
+      <c r="H46" s="13"/>
+      <c r="I46" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="4">
-        <v>26</v>
-      </c>
-      <c r="G39" s="5">
-        <v>1</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L39" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="P39" s="2" t="s">
+      <c r="P46" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
-      <c r="A40" s="4">
+    <row r="47" s="3" customFormat="1" spans="1:16">
+      <c r="A47" s="3">
+        <v>2001</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3">
+        <v>11</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3">
+        <v>1</v>
+      </c>
+      <c r="G47" s="13">
+        <v>4</v>
+      </c>
+      <c r="H47" s="13"/>
+      <c r="I47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P40" s="4" t="s">
+      <c r="O47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" s="3" customFormat="1" spans="1:16">
+      <c r="A48" s="3">
+        <v>2002</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3">
+        <v>2</v>
+      </c>
+      <c r="G48" s="13">
+        <v>4</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="P48" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
-      <c r="A41" s="4">
-        <v>127</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G41" s="5">
-        <v>1</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P41" s="4" t="s">
+    <row r="49" s="2" customFormat="1" spans="1:16">
+      <c r="A49" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B49" s="2">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2">
+        <v>3</v>
+      </c>
+      <c r="G49" s="12">
+        <v>4</v>
+      </c>
+      <c r="H49" s="12"/>
+      <c r="I49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P49" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
-      <c r="A42" s="4">
-        <v>1001</v>
-      </c>
-      <c r="B42" s="4">
-        <v>1</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F42" s="4">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5">
+    <row r="50" s="3" customFormat="1" spans="1:16">
+      <c r="A50" s="3">
+        <v>2004</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3">
+        <v>4</v>
+      </c>
+      <c r="G50" s="13">
+        <v>4</v>
+      </c>
+      <c r="H50" s="13"/>
+      <c r="I50" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:16">
+      <c r="A51" s="3">
+        <v>2005</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3">
+        <v>4</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3">
         <v>5</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O42" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="P42" s="4" t="s">
+      <c r="G51" s="13">
+        <v>4</v>
+      </c>
+      <c r="H51" s="13"/>
+      <c r="I51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" s="3" customFormat="1" spans="1:16">
+      <c r="A52" s="3">
+        <v>2006</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
+        <v>6</v>
+      </c>
+      <c r="G52" s="13">
+        <v>4</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="I52" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="P52" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
-      <c r="A43" s="4">
-        <v>1002</v>
-      </c>
-      <c r="B43" s="4">
-        <v>1</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F43" s="4">
-        <v>2</v>
-      </c>
-      <c r="G43" s="5">
+    <row r="53" s="3" customFormat="1" spans="1:16">
+      <c r="A53" s="3">
+        <v>2007</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3">
         <v>5</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O43" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" s="4">
-        <v>1003</v>
-      </c>
-      <c r="B44" s="4">
-        <v>1</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="4">
-        <v>3</v>
-      </c>
-      <c r="G44" s="5">
-        <v>5</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="4">
-        <v>1004</v>
-      </c>
-      <c r="B45" s="4">
-        <v>1</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" s="4">
+      <c r="D53" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3">
+        <v>7</v>
+      </c>
+      <c r="G53" s="13">
         <v>4</v>
       </c>
-      <c r="G45" s="5">
-        <v>5</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="4">
-        <v>1005</v>
-      </c>
-      <c r="B46" s="4">
-        <v>1</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" s="4">
-        <v>5</v>
-      </c>
-      <c r="G46" s="5">
-        <v>5</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="4">
-        <v>2001</v>
-      </c>
-      <c r="B47" s="4">
-        <v>1</v>
-      </c>
-      <c r="C47" s="4">
-        <v>11</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F47" s="4">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5">
-        <v>4</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="4">
-        <v>2002</v>
-      </c>
-      <c r="B48" s="4">
-        <v>1</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F48" s="4">
-        <v>2</v>
-      </c>
-      <c r="G48" s="5">
-        <v>4</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="A49" s="4">
-        <v>2003</v>
-      </c>
-      <c r="B49" s="4">
-        <v>1</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F49" s="4">
-        <v>3</v>
-      </c>
-      <c r="G49" s="5">
-        <v>4</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="O49" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
-      <c r="A50" s="4">
-        <v>2004</v>
-      </c>
-      <c r="B50" s="4">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4">
-        <v>2</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F50" s="4">
-        <v>4</v>
-      </c>
-      <c r="G50" s="5">
-        <v>4</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="O50" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16">
-      <c r="A51" s="4">
-        <v>2005</v>
-      </c>
-      <c r="B51" s="4">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4">
-        <v>4</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F51" s="4">
-        <v>5</v>
-      </c>
-      <c r="G51" s="5">
-        <v>4</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
-      <c r="A52" s="4">
-        <v>2006</v>
-      </c>
-      <c r="B52" s="4">
-        <v>1</v>
-      </c>
-      <c r="C52" s="4">
-        <v>15</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F52" s="4">
-        <v>6</v>
-      </c>
-      <c r="G52" s="5">
-        <v>4</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="L52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N52" s="4" t="s">
+      <c r="H53" s="13"/>
+      <c r="I53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="O52" s="4" t="s">
+      <c r="O53" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="P52" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="4">
-        <v>2007</v>
-      </c>
-      <c r="B53" s="4">
-        <v>1</v>
-      </c>
-      <c r="C53" s="4">
-        <v>5</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F53" s="4">
-        <v>7</v>
-      </c>
-      <c r="G53" s="5">
-        <v>4</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="O53" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="P53" s="4" t="s">
+      <c r="P53" s="3" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -2079,8 +2079,8 @@
       <c r="K8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="3" t="b">
-        <v>1</v>
+      <c r="L8" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M8" s="3"/>
       <c r="P8" s="3" t="s">

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -2079,8 +2079,8 @@
       <c r="K8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="2" t="b">
-        <v>0</v>
+      <c r="L8" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="M8" s="3"/>
       <c r="P8" s="3" t="s">

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="143">
   <si>
     <t>id</t>
   </si>
@@ -679,6 +679,15 @@
     <t>Grid (26)</t>
   </si>
   <si>
+    <t>充值引导</t>
+  </si>
+  <si>
+    <t>NOT(accountTotalRecharge(0.001))</t>
+  </si>
+  <si>
+    <t>免费旋转</t>
+  </si>
+  <si>
     <t>首页</t>
   </si>
   <si>
@@ -691,24 +700,18 @@
     <t>tap_activity</t>
   </si>
   <si>
-    <t>商城</t>
+    <t>菜单</t>
+  </si>
+  <si>
+    <t>btn_muen</t>
+  </si>
+  <si>
+    <t>btn_service</t>
   </si>
   <si>
     <t>btn_shop</t>
   </si>
   <si>
-    <t>赌场</t>
-  </si>
-  <si>
-    <t>btn_casino</t>
-  </si>
-  <si>
-    <t>创房间</t>
-  </si>
-  <si>
-    <t>btn_create</t>
-  </si>
-  <si>
     <t>sc-7</t>
   </si>
   <si>
@@ -718,7 +721,7 @@
     <t>djlb-3</t>
   </si>
   <si>
-    <t>btn_stage_rechare</t>
+    <t>btn_level_gift</t>
   </si>
   <si>
     <t>qtlc-6</t>
@@ -956,12 +959,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1810,7 +1813,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
@@ -3273,7 +3276,7 @@
         <v>38</v>
       </c>
       <c r="L38" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>45</v>
@@ -3308,7 +3311,7 @@
         <v>38</v>
       </c>
       <c r="L39" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>45</v>
@@ -3316,61 +3319,51 @@
     </row>
     <row r="40" customFormat="1" spans="1:16">
       <c r="A40" s="5">
-        <v>1001</v>
-      </c>
-      <c r="B40" s="5">
-        <v>1</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E40" s="3"/>
-      <c r="F40" s="5">
-        <v>1</v>
-      </c>
-      <c r="G40" s="6">
-        <v>5</v>
+      <c r="F40" s="5"/>
+      <c r="G40" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L40" s="15" t="b">
+        <v>119</v>
+      </c>
+      <c r="L40" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="5" t="s">
-        <v>119</v>
-      </c>
+      <c r="O40" s="5"/>
       <c r="P40" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:16">
       <c r="A41" s="5">
-        <v>1002</v>
-      </c>
-      <c r="B41" s="5">
-        <v>1</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5" t="s">
         <v>120</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="F41" s="5">
-        <v>2</v>
-      </c>
+      <c r="F41" s="5"/>
       <c r="G41" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="5" t="s">
@@ -3382,32 +3375,30 @@
       <c r="K41" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="15" t="b">
+      <c r="L41" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="5" t="s">
-        <v>121</v>
-      </c>
+      <c r="O41" s="5"/>
       <c r="P41" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:16">
       <c r="A42" s="5">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B42" s="5">
         <v>1</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="6">
         <v>5</v>
@@ -3428,285 +3419,277 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="43" s="4" customFormat="1" spans="1:16">
-      <c r="A43" s="4">
+    <row r="43" customFormat="1" spans="1:16">
+      <c r="A43" s="5">
+        <v>1002</v>
+      </c>
+      <c r="B43" s="5">
+        <v>1</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="5">
+        <v>2</v>
+      </c>
+      <c r="G43" s="6">
+        <v>5</v>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:16">
+      <c r="A44" s="5">
+        <v>1003</v>
+      </c>
+      <c r="B44" s="5">
+        <v>1</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="5">
+        <v>3</v>
+      </c>
+      <c r="G44" s="6">
+        <v>5</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" s="4" customFormat="1" spans="1:16">
+      <c r="A45" s="4">
         <v>1004</v>
       </c>
-      <c r="B43" s="4">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4">
+      <c r="B45" s="4">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4">
         <v>4</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G45" s="22">
         <v>5</v>
       </c>
-      <c r="H43" s="22"/>
-      <c r="I43" s="4" t="s">
+      <c r="H45" s="22"/>
+      <c r="I45" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="P43" s="4" t="s">
+      <c r="J45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" s="4" customFormat="1" spans="1:16">
-      <c r="A44" s="4">
+    <row r="46" s="4" customFormat="1" spans="1:16">
+      <c r="A46" s="4">
         <v>1005</v>
       </c>
-      <c r="B44" s="4">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4">
+      <c r="B46" s="4">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4">
         <v>5</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G46" s="22">
         <v>5</v>
       </c>
-      <c r="H44" s="22"/>
-      <c r="I44" s="4" t="s">
+      <c r="H46" s="22"/>
+      <c r="I46" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="L44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="P44" s="4" t="s">
+      <c r="J46" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="P46" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:16">
-      <c r="A45" s="5">
-        <v>2001</v>
-      </c>
-      <c r="B45" s="5">
-        <v>1</v>
-      </c>
-      <c r="C45" s="5">
-        <v>11</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5">
-        <v>1</v>
-      </c>
-      <c r="G45" s="6">
-        <v>4</v>
-      </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="O45" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="P45" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:16">
-      <c r="A46" s="5">
-        <v>2002</v>
-      </c>
-      <c r="B46" s="5">
-        <v>1</v>
-      </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5">
-        <v>2</v>
-      </c>
-      <c r="G46" s="6">
-        <v>4</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J46" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K46" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="L46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="O46" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="P46" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:16">
       <c r="A47" s="5">
-        <v>2003</v>
-      </c>
-      <c r="B47" s="3">
-        <v>1</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" s="19"/>
+        <v>2001</v>
+      </c>
+      <c r="B47" s="5">
+        <v>1</v>
+      </c>
+      <c r="C47" s="5">
+        <v>11</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E47" s="5"/>
       <c r="F47" s="5">
-        <v>3</v>
-      </c>
-      <c r="G47" s="20">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6">
         <v>4</v>
       </c>
-      <c r="H47" s="20"/>
-      <c r="I47" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J47" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="P47" s="3" t="s">
+      <c r="H47" s="6"/>
+      <c r="I47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="P47" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:16">
       <c r="A48" s="5">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B48" s="5">
         <v>1</v>
       </c>
-      <c r="C48" s="5">
-        <v>2</v>
-      </c>
+      <c r="C48" s="5"/>
       <c r="D48" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G48" s="6">
         <v>4</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="5" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="L48" s="5" t="b">
         <v>1</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:16">
       <c r="A49" s="5">
-        <v>2005</v>
-      </c>
-      <c r="B49" s="15">
-        <v>1</v>
-      </c>
-      <c r="C49" s="15">
+        <v>2003</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E49" s="19"/>
+      <c r="F49" s="5">
+        <v>3</v>
+      </c>
+      <c r="G49" s="20">
         <v>4</v>
       </c>
-      <c r="D49" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="5">
-        <v>5</v>
-      </c>
-      <c r="G49" s="16">
-        <v>4</v>
-      </c>
-      <c r="H49" s="16"/>
+      <c r="H49" s="20"/>
       <c r="I49" s="15" t="s">
         <v>37</v>
       </c>
@@ -3716,59 +3699,59 @@
       <c r="K49" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L49" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="O49" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="P49" s="5" t="s">
-        <v>39</v>
+      <c r="L49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:16">
       <c r="A50" s="5">
-        <v>2006</v>
-      </c>
-      <c r="B50" s="15">
-        <v>1</v>
-      </c>
-      <c r="C50" s="15">
-        <v>15</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15">
-        <v>6</v>
-      </c>
-      <c r="G50" s="16">
+        <v>2004</v>
+      </c>
+      <c r="B50" s="5">
+        <v>1</v>
+      </c>
+      <c r="C50" s="5">
+        <v>2</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5">
         <v>4</v>
       </c>
-      <c r="H50" s="16"/>
-      <c r="I50" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K50" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="L50" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="15"/>
-      <c r="N50" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="O50" s="15" t="s">
-        <v>139</v>
+      <c r="G50" s="6">
+        <v>4</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="P50" s="5" t="s">
         <v>45</v>
@@ -3776,20 +3759,20 @@
     </row>
     <row r="51" customFormat="1" spans="1:16">
       <c r="A51" s="5">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B51" s="15">
         <v>1</v>
       </c>
       <c r="C51" s="15">
+        <v>4</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="5">
         <v>5</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15">
-        <v>7</v>
       </c>
       <c r="G51" s="16">
         <v>4</v>
@@ -3809,12 +3792,100 @@
       </c>
       <c r="M51" s="15"/>
       <c r="N51" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="O51" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="P51" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:16">
+      <c r="A52" s="5">
+        <v>2006</v>
+      </c>
+      <c r="B52" s="15">
+        <v>1</v>
+      </c>
+      <c r="C52" s="15">
+        <v>15</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15">
+        <v>6</v>
+      </c>
+      <c r="G52" s="16">
+        <v>4</v>
+      </c>
+      <c r="H52" s="16"/>
+      <c r="I52" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L52" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="O52" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="O51" s="15" t="s">
+      <c r="P52" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:16">
+      <c r="A53" s="5">
+        <v>2007</v>
+      </c>
+      <c r="B53" s="15">
+        <v>1</v>
+      </c>
+      <c r="C53" s="15">
+        <v>5</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15">
+        <v>7</v>
+      </c>
+      <c r="G53" s="16">
+        <v>4</v>
+      </c>
+      <c r="H53" s="16"/>
+      <c r="I53" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="P51" s="5" t="s">
+      <c r="O53" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="P53" s="5" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -959,12 +959,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2024,8 +2024,8 @@
       <c r="K5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="2" t="b">
-        <v>0</v>
+      <c r="L5" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="M5" s="13"/>
       <c r="N5" s="13"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -2024,8 +2024,8 @@
       <c r="K5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="13" t="b">
-        <v>1</v>
+      <c r="L5" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M5" s="13"/>
       <c r="N5" s="13"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="145">
   <si>
     <t>id</t>
   </si>
@@ -686,6 +686,12 @@
   </si>
   <si>
     <t>免费旋转</t>
+  </si>
+  <si>
+    <t>进SLOT大厅</t>
+  </si>
+  <si>
+    <t>对战</t>
   </si>
   <si>
     <t>首页</t>
@@ -1813,13 +1819,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="5" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="10.125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.9083333333333" style="5" customWidth="1"/>
     <col min="5" max="5" width="21.5" style="5" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="5" customWidth="1"/>
     <col min="7" max="7" width="11.875" style="6" customWidth="1"/>
@@ -3387,21 +3393,17 @@
     </row>
     <row r="42" customFormat="1" spans="1:16">
       <c r="A42" s="5">
-        <v>1001</v>
-      </c>
-      <c r="B42" s="5">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5" t="s">
         <v>121</v>
       </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="5">
-        <v>1</v>
-      </c>
+      <c r="F42" s="5"/>
       <c r="G42" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="5" t="s">
@@ -3413,35 +3415,27 @@
       <c r="K42" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L42" s="15" t="b">
+      <c r="L42" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="O42" s="5"/>
+      <c r="P42" s="2"/>
     </row>
     <row r="43" customFormat="1" spans="1:16">
       <c r="A43" s="5">
-        <v>1002</v>
-      </c>
-      <c r="B43" s="5">
-        <v>1</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="5">
-        <v>2</v>
-      </c>
+      <c r="F43" s="5"/>
       <c r="G43" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="5" t="s">
@@ -3453,32 +3447,28 @@
       <c r="K43" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L43" s="15" t="b">
+      <c r="L43" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="O43" s="5"/>
+      <c r="P43" s="2"/>
     </row>
     <row r="44" customFormat="1" spans="1:16">
       <c r="A44" s="5">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B44" s="5">
         <v>1</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" s="6">
         <v>5</v>
@@ -3499,285 +3489,277 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="45" s="4" customFormat="1" spans="1:16">
-      <c r="A45" s="4">
+    <row r="45" customFormat="1" spans="1:16">
+      <c r="A45" s="5">
+        <v>1002</v>
+      </c>
+      <c r="B45" s="5">
+        <v>1</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="5">
+        <v>2</v>
+      </c>
+      <c r="G45" s="6">
+        <v>5</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:16">
+      <c r="A46" s="5">
+        <v>1003</v>
+      </c>
+      <c r="B46" s="5">
+        <v>1</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="5">
+        <v>3</v>
+      </c>
+      <c r="G46" s="6">
+        <v>5</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" s="4" customFormat="1" spans="1:16">
+      <c r="A47" s="4">
         <v>1004</v>
       </c>
-      <c r="B45" s="4">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4" t="s">
+      <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4">
+      <c r="E47" s="4"/>
+      <c r="F47" s="4">
         <v>4</v>
       </c>
-      <c r="G45" s="22">
+      <c r="G47" s="22">
         <v>5</v>
       </c>
-      <c r="H45" s="22"/>
-      <c r="I45" s="4" t="s">
+      <c r="H47" s="22"/>
+      <c r="I47" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="P45" s="4" t="s">
+      <c r="J47" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="P47" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46" s="4" customFormat="1" spans="1:16">
-      <c r="A46" s="4">
+    <row r="48" s="4" customFormat="1" spans="1:16">
+      <c r="A48" s="4">
         <v>1005</v>
       </c>
-      <c r="B46" s="4">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4" t="s">
+      <c r="B48" s="4">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4">
+      <c r="E48" s="4"/>
+      <c r="F48" s="4">
         <v>5</v>
       </c>
-      <c r="G46" s="22">
+      <c r="G48" s="22">
         <v>5</v>
       </c>
-      <c r="H46" s="22"/>
-      <c r="I46" s="4" t="s">
+      <c r="H48" s="22"/>
+      <c r="I48" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="P46" s="4" t="s">
+      <c r="J48" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="P48" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:16">
-      <c r="A47" s="5">
-        <v>2001</v>
-      </c>
-      <c r="B47" s="5">
-        <v>1</v>
-      </c>
-      <c r="C47" s="5">
-        <v>11</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5">
-        <v>1</v>
-      </c>
-      <c r="G47" s="6">
-        <v>4</v>
-      </c>
-      <c r="H47" s="6"/>
-      <c r="I47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="O47" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="P47" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:16">
-      <c r="A48" s="5">
-        <v>2002</v>
-      </c>
-      <c r="B48" s="5">
-        <v>1</v>
-      </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5">
-        <v>2</v>
-      </c>
-      <c r="G48" s="6">
-        <v>4</v>
-      </c>
-      <c r="H48" s="6"/>
-      <c r="I48" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K48" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="L48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="O48" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="P48" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:16">
       <c r="A49" s="5">
-        <v>2003</v>
-      </c>
-      <c r="B49" s="3">
-        <v>1</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E49" s="19"/>
+        <v>2001</v>
+      </c>
+      <c r="B49" s="5">
+        <v>1</v>
+      </c>
+      <c r="C49" s="5">
+        <v>11</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" s="5"/>
       <c r="F49" s="5">
-        <v>3</v>
-      </c>
-      <c r="G49" s="20">
+        <v>1</v>
+      </c>
+      <c r="G49" s="6">
         <v>4</v>
       </c>
-      <c r="H49" s="20"/>
-      <c r="I49" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J49" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K49" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="P49" s="3" t="s">
+      <c r="H49" s="6"/>
+      <c r="I49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="P49" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:16">
       <c r="A50" s="5">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B50" s="5">
         <v>1</v>
       </c>
-      <c r="C50" s="5">
-        <v>2</v>
-      </c>
+      <c r="C50" s="5"/>
       <c r="D50" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50" s="6">
         <v>4</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="5" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="L50" s="5" t="b">
         <v>1</v>
       </c>
       <c r="M50" s="5"/>
       <c r="N50" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O50" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:16">
       <c r="A51" s="5">
-        <v>2005</v>
-      </c>
-      <c r="B51" s="15">
-        <v>1</v>
-      </c>
-      <c r="C51" s="15">
+        <v>2003</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="19"/>
+      <c r="F51" s="5">
+        <v>3</v>
+      </c>
+      <c r="G51" s="20">
         <v>4</v>
       </c>
-      <c r="D51" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="5">
-        <v>5</v>
-      </c>
-      <c r="G51" s="16">
-        <v>4</v>
-      </c>
-      <c r="H51" s="16"/>
+      <c r="H51" s="20"/>
       <c r="I51" s="15" t="s">
         <v>37</v>
       </c>
@@ -3787,59 +3769,59 @@
       <c r="K51" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L51" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="15"/>
-      <c r="N51" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="O51" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="P51" s="5" t="s">
-        <v>39</v>
+      <c r="L51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:16">
       <c r="A52" s="5">
-        <v>2006</v>
-      </c>
-      <c r="B52" s="15">
-        <v>1</v>
-      </c>
-      <c r="C52" s="15">
-        <v>15</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15">
-        <v>6</v>
-      </c>
-      <c r="G52" s="16">
+        <v>2004</v>
+      </c>
+      <c r="B52" s="5">
+        <v>1</v>
+      </c>
+      <c r="C52" s="5">
+        <v>2</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5">
         <v>4</v>
       </c>
-      <c r="H52" s="16"/>
-      <c r="I52" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="J52" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K52" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="L52" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="O52" s="15" t="s">
-        <v>140</v>
+      <c r="G52" s="6">
+        <v>4</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="P52" s="5" t="s">
         <v>45</v>
@@ -3847,20 +3829,20 @@
     </row>
     <row r="53" customFormat="1" spans="1:16">
       <c r="A53" s="5">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B53" s="15">
         <v>1</v>
       </c>
       <c r="C53" s="15">
+        <v>4</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="15"/>
+      <c r="F53" s="5">
         <v>5</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15">
-        <v>7</v>
       </c>
       <c r="G53" s="16">
         <v>4</v>
@@ -3880,12 +3862,100 @@
       </c>
       <c r="M53" s="15"/>
       <c r="N53" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="O53" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="P53" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:16">
+      <c r="A54" s="5">
+        <v>2006</v>
+      </c>
+      <c r="B54" s="15">
+        <v>1</v>
+      </c>
+      <c r="C54" s="15">
+        <v>15</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15">
+        <v>6</v>
+      </c>
+      <c r="G54" s="16">
+        <v>4</v>
+      </c>
+      <c r="H54" s="16"/>
+      <c r="I54" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L54" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="O53" s="15" t="s">
+      <c r="O54" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="P53" s="5" t="s">
+      <c r="P54" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:16">
+      <c r="A55" s="5">
+        <v>2007</v>
+      </c>
+      <c r="B55" s="15">
+        <v>1</v>
+      </c>
+      <c r="C55" s="15">
+        <v>5</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15">
+        <v>7</v>
+      </c>
+      <c r="G55" s="16">
+        <v>4</v>
+      </c>
+      <c r="H55" s="16"/>
+      <c r="I55" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="O55" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="P55" s="5" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -965,12 +965,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1825,7 +1825,7 @@
     <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="5" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.9083333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.6416666666667" style="5" customWidth="1"/>
     <col min="5" max="5" width="21.5" style="5" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="5" customWidth="1"/>
     <col min="7" max="7" width="11.875" style="6" customWidth="1"/>
@@ -3348,7 +3348,7 @@
         <v>119</v>
       </c>
       <c r="L40" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="146">
   <si>
     <t>id</t>
   </si>
@@ -692,6 +692,9 @@
   </si>
   <si>
     <t>对战</t>
+  </si>
+  <si>
+    <t>指定生成游客</t>
   </si>
   <si>
     <t>首页</t>
@@ -965,12 +968,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1819,7 +1822,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
@@ -3457,21 +3460,17 @@
     </row>
     <row r="44" customFormat="1" spans="1:16">
       <c r="A44" s="5">
-        <v>1001</v>
-      </c>
-      <c r="B44" s="5">
-        <v>1</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
         <v>123</v>
       </c>
       <c r="E44" s="3"/>
-      <c r="F44" s="5">
-        <v>1</v>
-      </c>
+      <c r="F44" s="5"/>
       <c r="G44" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5" t="s">
@@ -3483,32 +3482,30 @@
       <c r="K44" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L44" s="15" t="b">
-        <v>1</v>
+      <c r="L44" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="5" t="s">
-        <v>124</v>
-      </c>
+      <c r="O44" s="5"/>
       <c r="P44" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:16">
       <c r="A45" s="5">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B45" s="5">
         <v>1</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="6">
         <v>5</v>
@@ -3529,7 +3526,7 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>45</v>
@@ -3537,18 +3534,18 @@
     </row>
     <row r="46" customFormat="1" spans="1:16">
       <c r="A46" s="5">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B46" s="5">
         <v>1</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="6">
         <v>5</v>
@@ -3569,66 +3566,66 @@
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" s="4" customFormat="1" spans="1:16">
-      <c r="A47" s="4">
-        <v>1004</v>
-      </c>
-      <c r="B47" s="4">
-        <v>1</v>
-      </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4">
-        <v>4</v>
-      </c>
-      <c r="G47" s="22">
+    <row r="47" customFormat="1" spans="1:16">
+      <c r="A47" s="5">
+        <v>1003</v>
+      </c>
+      <c r="B47" s="5">
+        <v>1</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="5">
+        <v>3</v>
+      </c>
+      <c r="G47" s="6">
         <v>5</v>
       </c>
-      <c r="H47" s="22"/>
-      <c r="I47" s="4" t="s">
+      <c r="H47" s="6"/>
+      <c r="I47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4" t="s">
+      <c r="J47" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="P47" s="4" t="s">
+      <c r="P47" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" s="4" customFormat="1" spans="1:16">
       <c r="A48" s="4">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B48" s="4">
         <v>1</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G48" s="22">
         <v>5</v>
@@ -3655,307 +3652,347 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" customFormat="1" spans="1:16">
-      <c r="A49" s="5">
-        <v>2001</v>
-      </c>
-      <c r="B49" s="5">
-        <v>1</v>
-      </c>
-      <c r="C49" s="5">
-        <v>11</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5">
-        <v>1</v>
-      </c>
-      <c r="G49" s="6">
-        <v>4</v>
-      </c>
-      <c r="H49" s="6"/>
-      <c r="I49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="K49" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5" t="s">
+    <row r="49" s="4" customFormat="1" spans="1:16">
+      <c r="A49" s="4">
+        <v>1005</v>
+      </c>
+      <c r="B49" s="4">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4">
+        <v>5</v>
+      </c>
+      <c r="G49" s="22">
+        <v>5</v>
+      </c>
+      <c r="H49" s="22"/>
+      <c r="I49" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="O49" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="P49" s="5" t="s">
+      <c r="P49" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:16">
       <c r="A50" s="5">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B50" s="5">
         <v>1</v>
       </c>
-      <c r="C50" s="5"/>
+      <c r="C50" s="5">
+        <v>11</v>
+      </c>
       <c r="D50" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="6">
         <v>4</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="5" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L50" s="5" t="b">
         <v>1</v>
       </c>
       <c r="M50" s="5"/>
       <c r="N50" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O50" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="O50" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="P50" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:16">
       <c r="A51" s="5">
-        <v>2003</v>
-      </c>
-      <c r="B51" s="3">
-        <v>1</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" s="19"/>
+        <v>2002</v>
+      </c>
+      <c r="B51" s="5">
+        <v>1</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="5"/>
       <c r="F51" s="5">
-        <v>3</v>
-      </c>
-      <c r="G51" s="20">
+        <v>2</v>
+      </c>
+      <c r="G51" s="6">
         <v>4</v>
       </c>
-      <c r="H51" s="20"/>
-      <c r="I51" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K51" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3" t="s">
+      <c r="H51" s="6"/>
+      <c r="I51" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="O51" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="O51" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>45</v>
+      <c r="P51" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:16">
       <c r="A52" s="5">
-        <v>2004</v>
-      </c>
-      <c r="B52" s="5">
-        <v>1</v>
-      </c>
-      <c r="C52" s="5">
-        <v>2</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="5"/>
+        <v>2003</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E52" s="19"/>
       <c r="F52" s="5">
+        <v>3</v>
+      </c>
+      <c r="G52" s="20">
         <v>4</v>
       </c>
-      <c r="G52" s="6">
-        <v>4</v>
-      </c>
-      <c r="H52" s="6"/>
-      <c r="I52" s="5" t="s">
+      <c r="H52" s="20"/>
+      <c r="I52" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="J52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5" t="s">
+      <c r="J52" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="O52" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="P52" s="5" t="s">
+      <c r="P52" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:16">
       <c r="A53" s="5">
-        <v>2005</v>
-      </c>
-      <c r="B53" s="15">
-        <v>1</v>
-      </c>
-      <c r="C53" s="15">
+        <v>2004</v>
+      </c>
+      <c r="B53" s="5">
+        <v>1</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5">
         <v>4</v>
       </c>
-      <c r="D53" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="5">
-        <v>5</v>
-      </c>
-      <c r="G53" s="16">
+      <c r="G53" s="6">
         <v>4</v>
       </c>
-      <c r="H53" s="16"/>
-      <c r="I53" s="15" t="s">
+      <c r="H53" s="6"/>
+      <c r="I53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J53" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K53" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L53" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" s="15"/>
-      <c r="N53" s="15" t="s">
+      <c r="J53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="O53" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="O53" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="P53" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:16">
       <c r="A54" s="5">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B54" s="15">
         <v>1</v>
       </c>
       <c r="C54" s="15">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E54" s="15"/>
-      <c r="F54" s="15">
-        <v>6</v>
+      <c r="F54" s="5">
+        <v>5</v>
       </c>
       <c r="G54" s="16">
         <v>4</v>
       </c>
       <c r="H54" s="16"/>
       <c r="I54" s="15" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="L54" s="15" t="b">
         <v>1</v>
       </c>
       <c r="M54" s="15"/>
       <c r="N54" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="O54" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="O54" s="15" t="s">
-        <v>142</v>
-      </c>
       <c r="P54" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:16">
       <c r="A55" s="5">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B55" s="15">
         <v>1</v>
       </c>
       <c r="C55" s="15">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G55" s="16">
         <v>4</v>
       </c>
       <c r="H55" s="16"/>
       <c r="I55" s="15" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="L55" s="15" t="b">
         <v>1</v>
       </c>
       <c r="M55" s="15"/>
       <c r="N55" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="O55" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="O55" s="15" t="s">
+      <c r="P55" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:16">
+      <c r="A56" s="5">
+        <v>2007</v>
+      </c>
+      <c r="B56" s="15">
+        <v>1</v>
+      </c>
+      <c r="C56" s="15">
+        <v>5</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15">
+        <v>7</v>
+      </c>
+      <c r="G56" s="16">
+        <v>4</v>
+      </c>
+      <c r="H56" s="16"/>
+      <c r="I56" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K56" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="P55" s="5" t="s">
+      <c r="O56" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="P56" s="5" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -790,6 +790,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.5"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -814,12 +820,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1441,7 +1441,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1454,61 +1454,67 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1825,67 +1831,67 @@
   <dimension ref="A1:P56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.10833333333333" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.6416666666667" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="19.7" style="6" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="36.6083333333333" style="5" customWidth="1"/>
-    <col min="11" max="11" width="40.375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="5" customWidth="1"/>
-    <col min="13" max="15" width="11.9083333333333" style="5" customWidth="1"/>
-    <col min="16" max="16" width="26" style="5" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="9.10833333333333" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="6" customWidth="1"/>
+    <col min="4" max="4" width="17.6416666666667" style="6" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="6" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="19.7" style="7" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="36.6083333333333" style="6" customWidth="1"/>
+    <col min="11" max="11" width="40.375" style="6" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="6" customWidth="1"/>
+    <col min="13" max="15" width="11.9083333333333" style="6" customWidth="1"/>
+    <col min="16" max="16" width="26" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1893,2106 +1899,2106 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="10" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10" t="s">
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="13">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13" t="s">
+      <c r="A5" s="14">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="13" t="s">
+      <c r="H5" s="15"/>
+      <c r="I5" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="2" t="b">
+      <c r="J5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="5" t="s">
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14">
         <v>3</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="14" t="s">
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="13" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="5" t="s">
+      <c r="L6" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>3</v>
       </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14">
         <v>9</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="13" t="s">
+      <c r="F7" s="14"/>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="5" t="s">
+      <c r="J7" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13" t="s">
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>5</v>
       </c>
-      <c r="G8" s="14">
-        <v>1</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="13" t="s">
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="5" t="s">
+      <c r="J8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>5</v>
       </c>
-      <c r="B9" s="13">
-        <v>1</v>
-      </c>
-      <c r="C9" s="13">
+      <c r="B9" s="14">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14">
         <v>6</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14">
-        <v>1</v>
-      </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="13" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="5" t="s">
+      <c r="J9" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>6</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14">
-        <v>1</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="13" t="s">
+      <c r="F10" s="14"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="5" t="s">
+      <c r="J10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>7</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14">
-        <v>1</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="13" t="s">
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="5" t="s">
+      <c r="J11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="13">
+    <row r="12" s="2" customFormat="1" spans="1:16">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14">
-        <v>1</v>
-      </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="13" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="16">
+        <v>1</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L12" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="5" t="s">
+      <c r="L12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>9</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14" t="s">
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="13" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="5" t="s">
+      <c r="J13" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>10</v>
       </c>
-      <c r="B14" s="13">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13" t="s">
+      <c r="B14" s="14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <v>4</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="13" t="s">
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="5" t="s">
+      <c r="J14" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="15">
+    <row r="15" s="2" customFormat="1" spans="1:16">
+      <c r="A15" s="2">
         <v>101</v>
       </c>
-      <c r="B15" s="15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15" t="s">
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="2">
         <v>1</v>
       </c>
       <c r="G15" s="16">
         <v>1</v>
       </c>
       <c r="H15" s="16"/>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J15" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L15" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="15">
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
         <v>47061</v>
       </c>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="5" t="s">
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="15">
+      <c r="A16" s="18">
         <v>102</v>
       </c>
-      <c r="B16" s="15">
-        <v>1</v>
-      </c>
-      <c r="C16" s="15">
+      <c r="B16" s="18">
+        <v>1</v>
+      </c>
+      <c r="C16" s="18">
         <v>2</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="18">
         <v>2</v>
       </c>
-      <c r="G16" s="16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="15" t="s">
+      <c r="G16" s="19">
+        <v>1</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="5" t="s">
+      <c r="J16" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="15">
+      <c r="A17" s="18">
         <v>103</v>
       </c>
-      <c r="B17" s="15">
-        <v>1</v>
-      </c>
-      <c r="C17" s="15">
+      <c r="B17" s="18">
+        <v>1</v>
+      </c>
+      <c r="C17" s="18">
         <v>5</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="18">
         <v>9</v>
       </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="15" t="s">
+      <c r="G17" s="19">
+        <v>1</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="5" t="s">
+      <c r="J17" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="15">
+      <c r="A18" s="18">
         <v>104</v>
       </c>
-      <c r="B18" s="15">
-        <v>1</v>
-      </c>
-      <c r="C18" s="15">
+      <c r="B18" s="18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="18">
         <v>4</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="18">
         <v>3</v>
       </c>
-      <c r="G18" s="16">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="15" t="s">
+      <c r="G18" s="19">
+        <v>1</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="5" t="s">
+      <c r="J18" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="15">
+      <c r="A19" s="18">
         <v>105</v>
       </c>
-      <c r="B19" s="15">
-        <v>1</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15" t="s">
+      <c r="B19" s="18">
+        <v>1</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="18">
         <v>6</v>
       </c>
-      <c r="G19" s="16">
-        <v>1</v>
-      </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="15" t="s">
+      <c r="G19" s="19">
+        <v>1</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L19" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="5" t="s">
+      <c r="L19" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="15">
+      <c r="A20" s="18">
         <v>106</v>
       </c>
-      <c r="B20" s="15">
-        <v>1</v>
-      </c>
-      <c r="C20" s="15">
+      <c r="B20" s="18">
+        <v>1</v>
+      </c>
+      <c r="C20" s="18">
         <v>11</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="18">
         <v>7</v>
       </c>
-      <c r="G20" s="16">
-        <v>1</v>
-      </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="15" t="s">
+      <c r="G20" s="19">
+        <v>1</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="L20" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="5" t="s">
+      <c r="L20" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="15">
+      <c r="A21" s="18">
         <v>107</v>
       </c>
-      <c r="B21" s="15">
-        <v>1</v>
-      </c>
-      <c r="C21" s="15">
+      <c r="B21" s="18">
+        <v>1</v>
+      </c>
+      <c r="C21" s="18">
         <v>15</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="18">
         <v>8</v>
       </c>
-      <c r="G21" s="16">
-        <v>1</v>
-      </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="15" t="s">
+      <c r="G21" s="19">
+        <v>1</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="L21" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="5" t="s">
+      <c r="L21" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="15">
+      <c r="A22" s="18">
         <v>108</v>
       </c>
-      <c r="B22" s="15">
-        <v>1</v>
-      </c>
-      <c r="C22" s="15">
+      <c r="B22" s="18">
+        <v>1</v>
+      </c>
+      <c r="C22" s="18">
         <v>10</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="18">
         <v>11</v>
       </c>
-      <c r="G22" s="16">
-        <v>1</v>
-      </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="15" t="s">
+      <c r="G22" s="19">
+        <v>1</v>
+      </c>
+      <c r="H22" s="19"/>
+      <c r="I22" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="5" t="s">
+      <c r="J22" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="15">
+      <c r="A23" s="18">
         <v>109</v>
       </c>
-      <c r="B23" s="15">
-        <v>1</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15" t="s">
+      <c r="B23" s="18">
+        <v>1</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="18">
         <v>12</v>
       </c>
-      <c r="G23" s="16">
-        <v>1</v>
-      </c>
-      <c r="H23" s="16"/>
-      <c r="I23" s="15" t="s">
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J23" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L23" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="5" t="s">
+      <c r="J23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="15">
+    <row r="24" s="2" customFormat="1" spans="1:16">
+      <c r="A24" s="2">
         <v>110</v>
       </c>
-      <c r="B24" s="15">
-        <v>1</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15" t="s">
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="2">
         <v>13</v>
       </c>
       <c r="G24" s="16">
         <v>1</v>
       </c>
       <c r="H24" s="16"/>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J24" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L24" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="5" t="s">
+      <c r="J24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="15">
+      <c r="A25" s="18">
         <v>111</v>
       </c>
-      <c r="B25" s="15">
-        <v>1</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15" t="s">
+      <c r="B25" s="18">
+        <v>1</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="18">
         <v>14</v>
       </c>
-      <c r="G25" s="16">
-        <v>1</v>
-      </c>
-      <c r="H25" s="16"/>
-      <c r="I25" s="15" t="s">
+      <c r="G25" s="19">
+        <v>1</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="5" t="s">
+      <c r="J25" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="15">
+      <c r="A26" s="18">
         <v>112</v>
       </c>
-      <c r="B26" s="15">
-        <v>1</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15" t="s">
+      <c r="B26" s="18">
+        <v>1</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="18">
         <v>15</v>
       </c>
-      <c r="G26" s="16">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16"/>
-      <c r="I26" s="15" t="s">
+      <c r="G26" s="19">
+        <v>1</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L26" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="5" t="s">
+      <c r="J26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:16">
-      <c r="A27" s="2">
+    <row r="27" s="3" customFormat="1" spans="1:16">
+      <c r="A27" s="3">
         <v>113</v>
       </c>
-      <c r="B27" s="2">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>16</v>
       </c>
-      <c r="G27" s="18">
-        <v>1</v>
-      </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="2" t="s">
+      <c r="G27" s="20">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20"/>
+      <c r="I27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="L27" s="2" t="b">
+      <c r="L27" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="P27" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:16">
-      <c r="A28" s="3">
+    <row r="28" s="4" customFormat="1" spans="1:16">
+      <c r="A28" s="4">
         <v>114</v>
       </c>
-      <c r="B28" s="3">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3" t="s">
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="4">
         <v>17</v>
       </c>
-      <c r="G28" s="20">
-        <v>1</v>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="15" t="s">
+      <c r="G28" s="22">
+        <v>1</v>
+      </c>
+      <c r="H28" s="22"/>
+      <c r="I28" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J28" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L28" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P28" s="3" t="s">
+      <c r="J28" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:16">
-      <c r="A29" s="2">
+    <row r="29" s="3" customFormat="1" spans="1:16">
+      <c r="A29" s="3">
         <v>115</v>
       </c>
-      <c r="B29" s="2">
-        <v>1</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2" t="s">
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>18</v>
       </c>
-      <c r="G29" s="18">
-        <v>1</v>
-      </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="2" t="s">
+      <c r="G29" s="20">
+        <v>1</v>
+      </c>
+      <c r="H29" s="20"/>
+      <c r="I29" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="L29" s="2" t="b">
+      <c r="L29" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="P29" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:16">
-      <c r="A30" s="2">
+    <row r="30" s="3" customFormat="1" spans="1:16">
+      <c r="A30" s="3">
         <v>116</v>
       </c>
-      <c r="B30" s="2">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>19</v>
       </c>
-      <c r="G30" s="18">
-        <v>1</v>
-      </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="2" t="s">
+      <c r="G30" s="20">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20"/>
+      <c r="I30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="K30" s="15" t="s">
+      <c r="K30" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="L30" s="2" t="b">
+      <c r="L30" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="P30" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:16">
-      <c r="A31" s="2">
+    <row r="31" s="3" customFormat="1" spans="1:16">
+      <c r="A31" s="3">
         <v>117</v>
       </c>
-      <c r="B31" s="2">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>20</v>
       </c>
-      <c r="G31" s="18">
-        <v>1</v>
-      </c>
-      <c r="H31" s="18"/>
-      <c r="I31" s="2" t="s">
+      <c r="G31" s="20">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20"/>
+      <c r="I31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="J31" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="K31" s="15" t="s">
+      <c r="K31" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="L31" s="2" t="b">
+      <c r="L31" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="P31" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:16">
-      <c r="A32" s="2">
+    <row r="32" s="3" customFormat="1" spans="1:16">
+      <c r="A32" s="3">
         <v>118</v>
       </c>
-      <c r="B32" s="2">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2" t="s">
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>21</v>
       </c>
-      <c r="G32" s="18">
-        <v>1</v>
-      </c>
-      <c r="H32" s="18"/>
-      <c r="I32" s="2" t="s">
+      <c r="G32" s="20">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20"/>
+      <c r="I32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="K32" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="L32" s="2" t="b">
+      <c r="L32" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="P32" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="33" s="3" customFormat="1" spans="1:16">
-      <c r="A33" s="3">
+    <row r="33" s="4" customFormat="1" spans="1:16">
+      <c r="A33" s="4">
         <v>119</v>
       </c>
-      <c r="B33" s="3">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="B33" s="4">
+        <v>1</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="4">
         <v>22</v>
       </c>
-      <c r="G33" s="20">
-        <v>1</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="15" t="s">
+      <c r="G33" s="22">
+        <v>1</v>
+      </c>
+      <c r="H33" s="22"/>
+      <c r="I33" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J33" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L33" s="2" t="b">
+      <c r="J33" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L33" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="s">
+      <c r="P33" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>120</v>
       </c>
-      <c r="B34" s="3">
-        <v>1</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3" t="s">
+      <c r="B34" s="4">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="4">
         <v>10</v>
       </c>
-      <c r="G34" s="20">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3" t="s">
+      <c r="G34" s="22">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J34" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3" t="s">
+      <c r="J34" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>121</v>
       </c>
-      <c r="B35" s="5">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="B35" s="6">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="6">
         <v>23</v>
       </c>
-      <c r="G35" s="6">
-        <v>1</v>
-      </c>
-      <c r="I35" s="5" t="s">
+      <c r="G35" s="7">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J35" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L35" s="2" t="b">
+      <c r="J35" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L35" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2" t="s">
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>122</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I36" s="5" t="s">
+      <c r="I36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J36" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36" s="2" t="b">
+      <c r="J36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <v>123</v>
       </c>
-      <c r="B37" s="5">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="B37" s="6">
+        <v>1</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="6">
         <v>24</v>
       </c>
-      <c r="G37" s="6">
-        <v>1</v>
-      </c>
-      <c r="I37" s="5" t="s">
+      <c r="G37" s="7">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J37" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L37" s="2" t="b">
+      <c r="J37" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L37" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>124</v>
       </c>
-      <c r="B38" s="5">
-        <v>1</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="B38" s="6">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="6">
         <v>25</v>
       </c>
-      <c r="G38" s="6">
-        <v>1</v>
-      </c>
-      <c r="I38" s="5" t="s">
+      <c r="G38" s="7">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J38" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P38" s="2" t="s">
+      <c r="J38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <v>125</v>
       </c>
-      <c r="B39" s="5">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="B39" s="6">
+        <v>1</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="6">
         <v>26</v>
       </c>
-      <c r="G39" s="6">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5" t="s">
+      <c r="G39" s="7">
+        <v>1</v>
+      </c>
+      <c r="I39" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J39" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K39" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P39" s="2" t="s">
+      <c r="J39" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:16">
-      <c r="A40" s="5">
+      <c r="A40" s="6">
         <v>126</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6" t="s">
+      <c r="E40" s="4"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="5" t="s">
+      <c r="H40" s="7"/>
+      <c r="I40" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J40" s="15" t="s">
+      <c r="J40" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="K40" s="15" t="s">
+      <c r="K40" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="L40" s="2" t="b">
+      <c r="L40" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="2" t="s">
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:16">
-      <c r="A41" s="5">
+      <c r="A41" s="6">
         <v>127</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6">
-        <v>1</v>
-      </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="5" t="s">
+      <c r="E41" s="4"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="7">
+        <v>1</v>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="2" t="s">
+      <c r="J41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:16">
-      <c r="A42" s="5">
+      <c r="A42" s="6">
         <v>128</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6">
-        <v>1</v>
-      </c>
-      <c r="H42" s="6"/>
-      <c r="I42" s="5" t="s">
+      <c r="E42" s="4"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="7">
+        <v>1</v>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J42" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="2"/>
+      <c r="J42" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="3"/>
     </row>
     <row r="43" customFormat="1" spans="1:16">
-      <c r="A43" s="5">
+      <c r="A43" s="6">
         <v>129</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="6">
-        <v>1</v>
-      </c>
-      <c r="H43" s="6"/>
-      <c r="I43" s="5" t="s">
+      <c r="E43" s="4"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="7">
+        <v>1</v>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J43" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L43" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="2"/>
+      <c r="J43" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="3"/>
     </row>
     <row r="44" customFormat="1" spans="1:16">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>130</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="6">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6"/>
-      <c r="I44" s="5" t="s">
+      <c r="E44" s="4"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="7">
+        <v>1</v>
+      </c>
+      <c r="H44" s="7"/>
+      <c r="I44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L44" s="2" t="b">
+      <c r="J44" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="2" t="s">
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:16">
-      <c r="A45" s="5">
+      <c r="A45" s="6">
         <v>1001</v>
       </c>
-      <c r="B45" s="5">
-        <v>1</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5" t="s">
+      <c r="B45" s="6">
+        <v>1</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="5">
-        <v>1</v>
-      </c>
-      <c r="G45" s="6">
+      <c r="E45" s="4"/>
+      <c r="F45" s="6">
+        <v>1</v>
+      </c>
+      <c r="G45" s="7">
         <v>5</v>
       </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="5" t="s">
+      <c r="H45" s="7"/>
+      <c r="I45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J45" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K45" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L45" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5" t="s">
+      <c r="J45" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="P45" s="2" t="s">
+      <c r="P45" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:16">
-      <c r="A46" s="5">
+      <c r="A46" s="6">
         <v>1002</v>
       </c>
-      <c r="B46" s="5">
-        <v>1</v>
-      </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5" t="s">
+      <c r="B46" s="6">
+        <v>1</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="5">
+      <c r="E46" s="4"/>
+      <c r="F46" s="6">
         <v>2</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="7">
         <v>5</v>
       </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="5" t="s">
+      <c r="H46" s="7"/>
+      <c r="I46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J46" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L46" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5" t="s">
+      <c r="J46" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="P46" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:16">
-      <c r="A47" s="5">
+      <c r="A47" s="6">
         <v>1003</v>
       </c>
-      <c r="B47" s="5">
-        <v>1</v>
-      </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5" t="s">
+      <c r="B47" s="6">
+        <v>1</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="5">
+      <c r="E47" s="4"/>
+      <c r="F47" s="6">
         <v>3</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="7">
         <v>5</v>
       </c>
-      <c r="H47" s="6"/>
-      <c r="I47" s="5" t="s">
+      <c r="H47" s="7"/>
+      <c r="I47" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5" t="s">
+      <c r="J47" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="P47" s="2" t="s">
+      <c r="P47" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" s="4" customFormat="1" spans="1:16">
-      <c r="A48" s="4">
+    <row r="48" s="5" customFormat="1" spans="1:16">
+      <c r="A48" s="5">
         <v>1004</v>
       </c>
-      <c r="B48" s="4">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4" t="s">
+      <c r="B48" s="5">
+        <v>1</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4">
+      <c r="E48" s="5"/>
+      <c r="F48" s="5">
         <v>4</v>
       </c>
-      <c r="G48" s="22">
+      <c r="G48" s="24">
         <v>5</v>
       </c>
-      <c r="H48" s="22"/>
-      <c r="I48" s="4" t="s">
+      <c r="H48" s="24"/>
+      <c r="I48" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4" t="s">
+      <c r="J48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="P48" s="4" t="s">
+      <c r="P48" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" s="4" customFormat="1" spans="1:16">
-      <c r="A49" s="4">
+    <row r="49" s="5" customFormat="1" spans="1:16">
+      <c r="A49" s="5">
         <v>1005</v>
       </c>
-      <c r="B49" s="4">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4" t="s">
+      <c r="B49" s="5">
+        <v>1</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4">
+      <c r="E49" s="5"/>
+      <c r="F49" s="5">
         <v>5</v>
       </c>
-      <c r="G49" s="22">
+      <c r="G49" s="24">
         <v>5</v>
       </c>
-      <c r="H49" s="22"/>
-      <c r="I49" s="4" t="s">
+      <c r="H49" s="24"/>
+      <c r="I49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4" t="s">
+      <c r="J49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="P49" s="4" t="s">
+      <c r="P49" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:16">
-      <c r="A50" s="5">
+      <c r="A50" s="6">
         <v>2001</v>
       </c>
-      <c r="B50" s="5">
-        <v>1</v>
-      </c>
-      <c r="C50" s="5">
+      <c r="B50" s="6">
+        <v>1</v>
+      </c>
+      <c r="C50" s="6">
         <v>11</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5">
-        <v>1</v>
-      </c>
-      <c r="G50" s="6">
+      <c r="E50" s="6"/>
+      <c r="F50" s="6">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7">
         <v>4</v>
       </c>
-      <c r="H50" s="6"/>
-      <c r="I50" s="5" t="s">
+      <c r="H50" s="7"/>
+      <c r="I50" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="J50" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K50" s="5" t="s">
+      <c r="K50" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="L50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5" t="s">
+      <c r="L50" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="O50" s="5" t="s">
+      <c r="O50" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="P50" s="5" t="s">
+      <c r="P50" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:16">
-      <c r="A51" s="5">
+      <c r="A51" s="6">
         <v>2002</v>
       </c>
-      <c r="B51" s="5">
-        <v>1</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5" t="s">
+      <c r="B51" s="6">
+        <v>1</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5">
+      <c r="E51" s="6"/>
+      <c r="F51" s="6">
         <v>2</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="7">
         <v>4</v>
       </c>
-      <c r="H51" s="6"/>
-      <c r="I51" s="5" t="s">
+      <c r="H51" s="7"/>
+      <c r="I51" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J51" s="5" t="s">
+      <c r="J51" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K51" s="5" t="s">
+      <c r="K51" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="L51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5" t="s">
+      <c r="L51" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="O51" s="5" t="s">
+      <c r="O51" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="P51" s="5" t="s">
+      <c r="P51" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:16">
-      <c r="A52" s="5">
+      <c r="A52" s="6">
         <v>2003</v>
       </c>
-      <c r="B52" s="3">
-        <v>1</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3" t="s">
+      <c r="B52" s="4">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E52" s="19"/>
-      <c r="F52" s="5">
+      <c r="E52" s="21"/>
+      <c r="F52" s="6">
         <v>3</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="22">
         <v>4</v>
       </c>
-      <c r="H52" s="20"/>
-      <c r="I52" s="15" t="s">
+      <c r="H52" s="22"/>
+      <c r="I52" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J52" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L52" s="2" t="b">
+      <c r="J52" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3" t="s">
+      <c r="M52" s="4"/>
+      <c r="N52" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="O52" s="3" t="s">
+      <c r="O52" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="P52" s="3" t="s">
+      <c r="P52" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:16">
-      <c r="A53" s="5">
+      <c r="A53" s="6">
         <v>2004</v>
       </c>
-      <c r="B53" s="5">
-        <v>1</v>
-      </c>
-      <c r="C53" s="5">
+      <c r="B53" s="6">
+        <v>1</v>
+      </c>
+      <c r="C53" s="6">
         <v>2</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5">
+      <c r="E53" s="6"/>
+      <c r="F53" s="6">
         <v>4</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="7">
         <v>4</v>
       </c>
-      <c r="H53" s="6"/>
-      <c r="I53" s="5" t="s">
+      <c r="H53" s="7"/>
+      <c r="I53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5" t="s">
+      <c r="J53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="O53" s="5" t="s">
+      <c r="O53" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="P53" s="5" t="s">
+      <c r="P53" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:16">
-      <c r="A54" s="5">
+      <c r="A54" s="6">
         <v>2005</v>
       </c>
-      <c r="B54" s="15">
-        <v>1</v>
-      </c>
-      <c r="C54" s="15">
+      <c r="B54" s="18">
+        <v>1</v>
+      </c>
+      <c r="C54" s="18">
         <v>4</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="5">
+      <c r="E54" s="18"/>
+      <c r="F54" s="6">
         <v>5</v>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="19">
         <v>4</v>
       </c>
-      <c r="H54" s="16"/>
-      <c r="I54" s="15" t="s">
+      <c r="H54" s="19"/>
+      <c r="I54" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J54" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K54" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L54" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54" s="15"/>
-      <c r="N54" s="15" t="s">
+      <c r="J54" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="O54" s="15" t="s">
+      <c r="O54" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="P54" s="5" t="s">
+      <c r="P54" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:16">
-      <c r="A55" s="5">
+      <c r="A55" s="6">
         <v>2006</v>
       </c>
-      <c r="B55" s="15">
-        <v>1</v>
-      </c>
-      <c r="C55" s="15">
+      <c r="B55" s="18">
+        <v>1</v>
+      </c>
+      <c r="C55" s="18">
         <v>15</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15">
+      <c r="E55" s="18"/>
+      <c r="F55" s="18">
         <v>6</v>
       </c>
-      <c r="G55" s="16">
+      <c r="G55" s="19">
         <v>4</v>
       </c>
-      <c r="H55" s="16"/>
-      <c r="I55" s="15" t="s">
+      <c r="H55" s="19"/>
+      <c r="I55" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="J55" s="15" t="s">
+      <c r="J55" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="K55" s="15" t="s">
+      <c r="K55" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" s="15"/>
-      <c r="N55" s="15" t="s">
+      <c r="L55" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="O55" s="15" t="s">
+      <c r="O55" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="P55" s="5" t="s">
+      <c r="P55" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:16">
-      <c r="A56" s="5">
+      <c r="A56" s="6">
         <v>2007</v>
       </c>
-      <c r="B56" s="15">
-        <v>1</v>
-      </c>
-      <c r="C56" s="15">
+      <c r="B56" s="18">
+        <v>1</v>
+      </c>
+      <c r="C56" s="18">
         <v>5</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15">
+      <c r="E56" s="18"/>
+      <c r="F56" s="18">
         <v>7</v>
       </c>
-      <c r="G56" s="16">
+      <c r="G56" s="19">
         <v>4</v>
       </c>
-      <c r="H56" s="16"/>
-      <c r="I56" s="15" t="s">
+      <c r="H56" s="19"/>
+      <c r="I56" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J56" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K56" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L56" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15" t="s">
+      <c r="J56" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K56" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="O56" s="15" t="s">
+      <c r="O56" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="P56" s="5" t="s">
+      <c r="P56" s="6" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -773,7 +773,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -814,6 +814,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1311,137 +1317,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1490,16 +1496,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2075,8 +2084,8 @@
       <c r="K6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="14" t="b">
-        <v>1</v>
+      <c r="L6" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="14"/>
@@ -2115,8 +2124,8 @@
       <c r="K7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="14" t="b">
-        <v>1</v>
+      <c r="L7" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M7" s="14"/>
       <c r="N7" s="14"/>
@@ -2155,8 +2164,8 @@
       <c r="K8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="14" t="b">
-        <v>1</v>
+      <c r="L8" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M8" s="14"/>
       <c r="N8" s="14"/>
@@ -2195,7 +2204,7 @@
       <c r="K9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L9" s="14" t="b">
+      <c r="L9" s="16" t="b">
         <v>1</v>
       </c>
       <c r="M9" s="14"/>
@@ -2231,7 +2240,7 @@
       <c r="K10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="14" t="b">
+      <c r="L10" s="16" t="b">
         <v>1</v>
       </c>
       <c r="M10" s="14"/>
@@ -2265,8 +2274,8 @@
       <c r="K11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L11" s="14" t="b">
-        <v>1</v>
+      <c r="L11" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
@@ -2286,10 +2295,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="16">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16"/>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="17"/>
       <c r="I12" s="2" t="s">
         <v>54</v>
       </c>
@@ -2333,7 +2342,7 @@
       <c r="K13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="14" t="b">
+      <c r="L13" s="16" t="b">
         <v>1</v>
       </c>
       <c r="M13" s="14"/>
@@ -2373,8 +2382,8 @@
       <c r="K14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="14" t="b">
-        <v>1</v>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M14" s="14"/>
       <c r="N14" s="14"/>
@@ -2400,14 +2409,14 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="16">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16"/>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="17"/>
       <c r="I15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="18" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -2426,333 +2435,333 @@
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="18">
+      <c r="A16" s="19">
         <v>102</v>
       </c>
-      <c r="B16" s="18">
-        <v>1</v>
-      </c>
-      <c r="C16" s="18">
+      <c r="B16" s="19">
+        <v>1</v>
+      </c>
+      <c r="C16" s="19">
         <v>2</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="19">
         <v>2</v>
       </c>
-      <c r="G16" s="19">
-        <v>1</v>
-      </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="18" t="s">
+      <c r="G16" s="20">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
+      <c r="J16" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
       <c r="P16" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="18">
+      <c r="A17" s="19">
         <v>103</v>
       </c>
-      <c r="B17" s="18">
-        <v>1</v>
-      </c>
-      <c r="C17" s="18">
+      <c r="B17" s="19">
+        <v>1</v>
+      </c>
+      <c r="C17" s="19">
         <v>5</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="19">
         <v>9</v>
       </c>
-      <c r="G17" s="19">
-        <v>1</v>
-      </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="18" t="s">
+      <c r="G17" s="20">
+        <v>1</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
+      <c r="J17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
       <c r="P17" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="18">
+      <c r="A18" s="19">
         <v>104</v>
       </c>
-      <c r="B18" s="18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="18">
+      <c r="B18" s="19">
+        <v>1</v>
+      </c>
+      <c r="C18" s="19">
         <v>4</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="19">
         <v>3</v>
       </c>
-      <c r="G18" s="19">
-        <v>1</v>
-      </c>
-      <c r="H18" s="19"/>
-      <c r="I18" s="18" t="s">
+      <c r="G18" s="20">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
+      <c r="J18" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
       <c r="P18" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="18">
+      <c r="A19" s="19">
         <v>105</v>
       </c>
-      <c r="B19" s="18">
-        <v>1</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18" t="s">
+      <c r="B19" s="19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="19">
         <v>6</v>
       </c>
-      <c r="G19" s="19">
-        <v>1</v>
-      </c>
-      <c r="H19" s="19"/>
-      <c r="I19" s="18" t="s">
+      <c r="G19" s="20">
+        <v>1</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="L19" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
+      <c r="L19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
       <c r="P19" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="18">
+      <c r="A20" s="19">
         <v>106</v>
       </c>
-      <c r="B20" s="18">
-        <v>1</v>
-      </c>
-      <c r="C20" s="18">
+      <c r="B20" s="19">
+        <v>1</v>
+      </c>
+      <c r="C20" s="19">
         <v>11</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="19">
         <v>7</v>
       </c>
-      <c r="G20" s="19">
-        <v>1</v>
-      </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="18" t="s">
+      <c r="G20" s="20">
+        <v>1</v>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J20" s="18" t="s">
+      <c r="J20" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="L20" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
+      <c r="L20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
       <c r="P20" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="18">
+      <c r="A21" s="19">
         <v>107</v>
       </c>
-      <c r="B21" s="18">
-        <v>1</v>
-      </c>
-      <c r="C21" s="18">
+      <c r="B21" s="19">
+        <v>1</v>
+      </c>
+      <c r="C21" s="19">
         <v>15</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <v>8</v>
       </c>
-      <c r="G21" s="19">
-        <v>1</v>
-      </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="18" t="s">
+      <c r="G21" s="20">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="J21" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="L21" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
+      <c r="L21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
       <c r="P21" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="18">
+      <c r="A22" s="19">
         <v>108</v>
       </c>
-      <c r="B22" s="18">
-        <v>1</v>
-      </c>
-      <c r="C22" s="18">
+      <c r="B22" s="19">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19">
         <v>10</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <v>11</v>
       </c>
-      <c r="G22" s="19">
-        <v>1</v>
-      </c>
-      <c r="H22" s="19"/>
-      <c r="I22" s="18" t="s">
+      <c r="G22" s="20">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
+      <c r="J22" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
       <c r="P22" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="18">
+      <c r="A23" s="19">
         <v>109</v>
       </c>
-      <c r="B23" s="18">
-        <v>1</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18" t="s">
+      <c r="B23" s="19">
+        <v>1</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <v>12</v>
       </c>
-      <c r="G23" s="19">
-        <v>1</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="18" t="s">
+      <c r="G23" s="20">
+        <v>1</v>
+      </c>
+      <c r="H23" s="20"/>
+      <c r="I23" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J23" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L23" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
+      <c r="J23" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
       <c r="P23" s="6" t="s">
         <v>45</v>
       </c>
@@ -2774,10 +2783,10 @@
       <c r="F24" s="2">
         <v>13</v>
       </c>
-      <c r="G24" s="16">
-        <v>1</v>
-      </c>
-      <c r="H24" s="16"/>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="17"/>
       <c r="I24" s="2" t="s">
         <v>37</v>
       </c>
@@ -2798,81 +2807,81 @@
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="18">
+      <c r="A25" s="19">
         <v>111</v>
       </c>
-      <c r="B25" s="18">
-        <v>1</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18" t="s">
+      <c r="B25" s="19">
+        <v>1</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="19">
         <v>14</v>
       </c>
-      <c r="G25" s="19">
-        <v>1</v>
-      </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="18" t="s">
+      <c r="G25" s="20">
+        <v>1</v>
+      </c>
+      <c r="H25" s="20"/>
+      <c r="I25" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
+      <c r="J25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
       <c r="P25" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="18">
+      <c r="A26" s="19">
         <v>112</v>
       </c>
-      <c r="B26" s="18">
-        <v>1</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18" t="s">
+      <c r="B26" s="19">
+        <v>1</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="19">
         <v>15</v>
       </c>
-      <c r="G26" s="19">
-        <v>1</v>
-      </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="18" t="s">
+      <c r="G26" s="20">
+        <v>1</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L26" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
+      <c r="J26" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
       <c r="P26" s="6" t="s">
         <v>45</v>
       </c>
@@ -2894,17 +2903,17 @@
       <c r="F27" s="3">
         <v>16</v>
       </c>
-      <c r="G27" s="20">
-        <v>1</v>
-      </c>
-      <c r="H27" s="20"/>
+      <c r="G27" s="21">
+        <v>1</v>
+      </c>
+      <c r="H27" s="21"/>
       <c r="I27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J27" s="18" t="s">
+      <c r="J27" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="K27" s="18" t="s">
+      <c r="K27" s="19" t="s">
         <v>95</v>
       </c>
       <c r="L27" s="3" t="b">
@@ -2925,27 +2934,27 @@
       <c r="D28" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="22" t="s">
         <v>97</v>
       </c>
       <c r="F28" s="4">
         <v>17</v>
       </c>
-      <c r="G28" s="22">
-        <v>1</v>
-      </c>
-      <c r="H28" s="22"/>
-      <c r="I28" s="18" t="s">
+      <c r="G28" s="23">
+        <v>1</v>
+      </c>
+      <c r="H28" s="23"/>
+      <c r="I28" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J28" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L28" s="18" t="b">
-        <v>1</v>
+      <c r="J28" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="P28" s="4" t="s">
         <v>45</v>
@@ -2962,23 +2971,23 @@
       <c r="D29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="24" t="s">
         <v>99</v>
       </c>
       <c r="F29" s="3">
         <v>18</v>
       </c>
-      <c r="G29" s="20">
-        <v>1</v>
-      </c>
-      <c r="H29" s="20"/>
+      <c r="G29" s="21">
+        <v>1</v>
+      </c>
+      <c r="H29" s="21"/>
       <c r="I29" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J29" s="18" t="s">
+      <c r="J29" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="18" t="s">
+      <c r="K29" s="19" t="s">
         <v>95</v>
       </c>
       <c r="L29" s="3" t="b">
@@ -2999,23 +3008,23 @@
       <c r="D30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="24" t="s">
         <v>101</v>
       </c>
       <c r="F30" s="3">
         <v>19</v>
       </c>
-      <c r="G30" s="20">
-        <v>1</v>
-      </c>
-      <c r="H30" s="20"/>
+      <c r="G30" s="21">
+        <v>1</v>
+      </c>
+      <c r="H30" s="21"/>
       <c r="I30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J30" s="18" t="s">
+      <c r="J30" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="K30" s="18" t="s">
+      <c r="K30" s="19" t="s">
         <v>95</v>
       </c>
       <c r="L30" s="3" t="b">
@@ -3036,23 +3045,23 @@
       <c r="D31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="24" t="s">
         <v>103</v>
       </c>
       <c r="F31" s="3">
         <v>20</v>
       </c>
-      <c r="G31" s="20">
-        <v>1</v>
-      </c>
-      <c r="H31" s="20"/>
+      <c r="G31" s="21">
+        <v>1</v>
+      </c>
+      <c r="H31" s="21"/>
       <c r="I31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J31" s="18" t="s">
+      <c r="J31" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="K31" s="18" t="s">
+      <c r="K31" s="19" t="s">
         <v>95</v>
       </c>
       <c r="L31" s="3" t="b">
@@ -3073,23 +3082,23 @@
       <c r="D32" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="24" t="s">
         <v>105</v>
       </c>
       <c r="F32" s="3">
         <v>21</v>
       </c>
-      <c r="G32" s="20">
-        <v>1</v>
-      </c>
-      <c r="H32" s="20"/>
+      <c r="G32" s="21">
+        <v>1</v>
+      </c>
+      <c r="H32" s="21"/>
       <c r="I32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J32" s="18" t="s">
+      <c r="J32" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="K32" s="18" t="s">
+      <c r="K32" s="19" t="s">
         <v>95</v>
       </c>
       <c r="L32" s="3" t="b">
@@ -3109,23 +3118,23 @@
       <c r="D33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="22" t="s">
         <v>107</v>
       </c>
       <c r="F33" s="4">
         <v>22</v>
       </c>
-      <c r="G33" s="22">
-        <v>1</v>
-      </c>
-      <c r="H33" s="22"/>
-      <c r="I33" s="18" t="s">
+      <c r="G33" s="23">
+        <v>1</v>
+      </c>
+      <c r="H33" s="23"/>
+      <c r="I33" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J33" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="18" t="s">
+      <c r="J33" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L33" s="3" t="b">
@@ -3152,21 +3161,21 @@
       <c r="F34" s="4">
         <v>10</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="23">
         <v>1</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" s="18" t="b">
-        <v>1</v>
+      <c r="J34" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
@@ -3194,10 +3203,10 @@
       <c r="I35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J35" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K35" s="18" t="s">
+      <c r="J35" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L35" s="3" t="b">
@@ -3220,14 +3229,14 @@
       <c r="I36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J36" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K36" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36" s="3" t="b">
-        <v>0</v>
+      <c r="J36" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3252,10 +3261,10 @@
       <c r="I37" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J37" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="18" t="s">
+      <c r="J37" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L37" s="3" t="b">
@@ -3284,13 +3293,13 @@
       <c r="I38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J38" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L38" s="3" t="b">
+      <c r="J38" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38" s="16" t="b">
         <v>1</v>
       </c>
       <c r="P38" s="3" t="s">
@@ -3319,13 +3328,13 @@
       <c r="I39" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J39" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K39" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L39" s="3" t="b">
+      <c r="J39" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="16" t="b">
         <v>1</v>
       </c>
       <c r="P39" s="3" t="s">
@@ -3350,10 +3359,10 @@
       <c r="I40" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J40" s="18" t="s">
+      <c r="J40" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="K40" s="18" t="s">
+      <c r="K40" s="19" t="s">
         <v>119</v>
       </c>
       <c r="L40" s="3" t="b">
@@ -3384,14 +3393,14 @@
       <c r="I41" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K41" s="18" t="s">
+      <c r="J41" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L41" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
@@ -3418,13 +3427,13 @@
       <c r="I42" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J42" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K42" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="3" t="b">
+      <c r="J42" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="16" t="b">
         <v>1</v>
       </c>
       <c r="M42" s="6"/>
@@ -3450,14 +3459,14 @@
       <c r="I43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J43" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="18" t="s">
+      <c r="J43" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L43" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
@@ -3482,14 +3491,14 @@
       <c r="I44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L44" s="3" t="b">
-        <v>0</v>
+      <c r="J44" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="16" t="b">
+        <v>1</v>
       </c>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
@@ -3520,14 +3529,14 @@
       <c r="I45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J45" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K45" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L45" s="18" t="b">
-        <v>1</v>
+      <c r="J45" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
@@ -3560,14 +3569,14 @@
       <c r="I46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J46" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K46" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L46" s="18" t="b">
-        <v>1</v>
+      <c r="J46" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
@@ -3600,14 +3609,14 @@
       <c r="I47" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K47" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="18" t="b">
-        <v>1</v>
+      <c r="J47" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
@@ -3633,10 +3642,10 @@
       <c r="F48" s="5">
         <v>4</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="25">
         <v>5</v>
       </c>
-      <c r="H48" s="24"/>
+      <c r="H48" s="25"/>
       <c r="I48" s="5" t="s">
         <v>37</v>
       </c>
@@ -3646,8 +3655,8 @@
       <c r="K48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L48" s="5" t="b">
-        <v>1</v>
+      <c r="L48" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
@@ -3673,10 +3682,10 @@
       <c r="F49" s="5">
         <v>5</v>
       </c>
-      <c r="G49" s="24">
+      <c r="G49" s="25">
         <v>5</v>
       </c>
-      <c r="H49" s="24"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="5" t="s">
         <v>37</v>
       </c>
@@ -3686,8 +3695,8 @@
       <c r="K49" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L49" s="5" t="b">
-        <v>1</v>
+      <c r="L49" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
@@ -3728,8 +3737,8 @@
       <c r="K50" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="L50" s="6" t="b">
-        <v>1</v>
+      <c r="L50" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M50" s="6"/>
       <c r="N50" s="6" t="s">
@@ -3770,8 +3779,8 @@
       <c r="K51" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="L51" s="6" t="b">
-        <v>1</v>
+      <c r="L51" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M51" s="6"/>
       <c r="N51" s="6" t="s">
@@ -3795,21 +3804,21 @@
       <c r="D52" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E52" s="21"/>
+      <c r="E52" s="22"/>
       <c r="F52" s="6">
         <v>3</v>
       </c>
-      <c r="G52" s="22">
+      <c r="G52" s="23">
         <v>4</v>
       </c>
-      <c r="H52" s="22"/>
-      <c r="I52" s="18" t="s">
+      <c r="H52" s="23"/>
+      <c r="I52" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J52" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="18" t="s">
+      <c r="J52" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L52" s="3" t="b">
@@ -3856,8 +3865,8 @@
       <c r="K53" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L53" s="6" t="b">
-        <v>1</v>
+      <c r="L53" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M53" s="6"/>
       <c r="N53" s="6" t="s">
@@ -3874,40 +3883,40 @@
       <c r="A54" s="6">
         <v>2005</v>
       </c>
-      <c r="B54" s="18">
-        <v>1</v>
-      </c>
-      <c r="C54" s="18">
+      <c r="B54" s="19">
+        <v>1</v>
+      </c>
+      <c r="C54" s="19">
         <v>4</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E54" s="18"/>
+      <c r="E54" s="19"/>
       <c r="F54" s="6">
         <v>5</v>
       </c>
-      <c r="G54" s="19">
+      <c r="G54" s="20">
         <v>4</v>
       </c>
-      <c r="H54" s="19"/>
-      <c r="I54" s="18" t="s">
+      <c r="H54" s="20"/>
+      <c r="I54" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J54" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K54" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L54" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18" t="s">
+      <c r="J54" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" s="19"/>
+      <c r="N54" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="O54" s="18" t="s">
+      <c r="O54" s="19" t="s">
         <v>141</v>
       </c>
       <c r="P54" s="6" t="s">
@@ -3918,40 +3927,40 @@
       <c r="A55" s="6">
         <v>2006</v>
       </c>
-      <c r="B55" s="18">
-        <v>1</v>
-      </c>
-      <c r="C55" s="18">
+      <c r="B55" s="19">
+        <v>1</v>
+      </c>
+      <c r="C55" s="19">
         <v>15</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18">
+      <c r="E55" s="19"/>
+      <c r="F55" s="19">
         <v>6</v>
       </c>
-      <c r="G55" s="19">
+      <c r="G55" s="20">
         <v>4</v>
       </c>
-      <c r="H55" s="19"/>
-      <c r="I55" s="18" t="s">
+      <c r="H55" s="20"/>
+      <c r="I55" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="J55" s="18" t="s">
+      <c r="J55" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="K55" s="18" t="s">
+      <c r="K55" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" s="18"/>
-      <c r="N55" s="18" t="s">
+      <c r="L55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" s="19"/>
+      <c r="N55" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="O55" s="18" t="s">
+      <c r="O55" s="19" t="s">
         <v>143</v>
       </c>
       <c r="P55" s="6" t="s">
@@ -3962,40 +3971,40 @@
       <c r="A56" s="6">
         <v>2007</v>
       </c>
-      <c r="B56" s="18">
-        <v>1</v>
-      </c>
-      <c r="C56" s="18">
+      <c r="B56" s="19">
+        <v>1</v>
+      </c>
+      <c r="C56" s="19">
         <v>5</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18">
+      <c r="E56" s="19"/>
+      <c r="F56" s="19">
         <v>7</v>
       </c>
-      <c r="G56" s="19">
+      <c r="G56" s="20">
         <v>4</v>
       </c>
-      <c r="H56" s="19"/>
-      <c r="I56" s="18" t="s">
+      <c r="H56" s="20"/>
+      <c r="I56" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J56" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K56" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L56" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M56" s="18"/>
-      <c r="N56" s="18" t="s">
+      <c r="J56" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" s="19"/>
+      <c r="N56" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="O56" s="18" t="s">
+      <c r="O56" s="19" t="s">
         <v>145</v>
       </c>
       <c r="P56" s="6" t="s">

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -2274,8 +2274,8 @@
       <c r="K11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L11" s="2" t="b">
-        <v>0</v>
+      <c r="L11" s="16" t="b">
+        <v>1</v>
       </c>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
@@ -2756,8 +2756,8 @@
       <c r="K23" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L23" s="2" t="b">
-        <v>0</v>
+      <c r="L23" s="16" t="b">
+        <v>1</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="19"/>
@@ -2836,8 +2836,8 @@
       <c r="K25" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L25" s="3" t="b">
-        <v>0</v>
+      <c r="L25" s="16" t="b">
+        <v>1</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="148">
   <si>
     <t>id</t>
   </si>
@@ -503,6 +503,12 @@
   </si>
   <si>
     <t>Grid (21)</t>
+  </si>
+  <si>
+    <t>背包</t>
+  </si>
+  <si>
+    <t>Grid (40)</t>
   </si>
   <si>
     <t>我的赌场</t>
@@ -1837,7 +1843,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="6" customWidth="1"/>
@@ -2349,7 +2355,7 @@
       <c r="N13" s="14"/>
       <c r="O13" s="14"/>
       <c r="P13" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2392,99 +2398,93 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:16">
-      <c r="A15" s="2">
+    <row r="15" customFormat="1" spans="1:16">
+      <c r="A15" s="14">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:16">
+      <c r="A16" s="2">
         <v>101</v>
       </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="17">
-        <v>1</v>
-      </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="2" t="s">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J15" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2">
-        <v>47061</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="19">
-        <v>102</v>
-      </c>
-      <c r="B16" s="19">
-        <v>1</v>
-      </c>
-      <c r="C16" s="19">
-        <v>2</v>
-      </c>
-      <c r="D16" s="19" t="s">
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="J16" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="F16" s="19">
-        <v>2</v>
-      </c>
-      <c r="G16" s="20">
-        <v>1</v>
-      </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>38</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="6" t="s">
-        <v>45</v>
+      <c r="M16" s="2">
+        <v>47061</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="19">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>66</v>
@@ -2493,7 +2493,7 @@
         <v>67</v>
       </c>
       <c r="F17" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G17" s="20">
         <v>1</v>
@@ -2515,18 +2515,18 @@
       <c r="N17" s="19"/>
       <c r="O17" s="19"/>
       <c r="P17" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="19">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>68</v>
@@ -2535,7 +2535,7 @@
         <v>69</v>
       </c>
       <c r="F18" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G18" s="20">
         <v>1</v>
@@ -2562,12 +2562,14 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="19">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" s="19">
         <v>1</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19">
+        <v>4</v>
+      </c>
       <c r="D19" s="19" t="s">
         <v>70</v>
       </c>
@@ -2575,20 +2577,20 @@
         <v>71</v>
       </c>
       <c r="F19" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G19" s="20">
         <v>1</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="19" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="L19" s="2" t="b">
         <v>0</v>
@@ -2602,35 +2604,33 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="19">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="19">
         <v>1</v>
       </c>
-      <c r="C20" s="19">
-        <v>11</v>
-      </c>
+      <c r="C20" s="19"/>
       <c r="D20" s="19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F20" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="20">
         <v>1</v>
       </c>
       <c r="H20" s="20"/>
       <c r="I20" s="19" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="J20" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L20" s="2" t="b">
         <v>0</v>
@@ -2639,40 +2639,40 @@
       <c r="N20" s="19"/>
       <c r="O20" s="19"/>
       <c r="P20" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="19">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="19">
         <v>1</v>
       </c>
       <c r="C21" s="19">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D21" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>78</v>
-      </c>
       <c r="F21" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G21" s="20">
         <v>1</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="19" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="J21" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
@@ -2686,38 +2686,38 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="19">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B22" s="19">
         <v>1</v>
       </c>
       <c r="C22" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F22" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G22" s="20">
         <v>1</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="19" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22" s="16" t="b">
-        <v>1</v>
+        <v>82</v>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="19"/>
@@ -2728,12 +2728,14 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="19">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" s="19">
         <v>1</v>
       </c>
-      <c r="C23" s="19"/>
+      <c r="C23" s="19">
+        <v>10</v>
+      </c>
       <c r="D23" s="19" t="s">
         <v>83</v>
       </c>
@@ -2741,7 +2743,7 @@
         <v>84</v>
       </c>
       <c r="F23" s="19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="20">
         <v>1</v>
@@ -2766,102 +2768,102 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:16">
-      <c r="A24" s="2">
+    <row r="24" spans="1:16">
+      <c r="A24" s="19">
+        <v>109</v>
+      </c>
+      <c r="B24" s="19">
+        <v>1</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="19">
+        <v>12</v>
+      </c>
+      <c r="G24" s="20">
+        <v>1</v>
+      </c>
+      <c r="H24" s="20"/>
+      <c r="I24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:16">
+      <c r="A25" s="2">
         <v>110</v>
       </c>
-      <c r="B24" s="2">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="2">
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="2">
         <v>13</v>
       </c>
-      <c r="G24" s="17">
-        <v>1</v>
-      </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="2" t="s">
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L24" s="3" t="b">
+      <c r="J25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2" t="s">
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="19">
-        <v>111</v>
-      </c>
-      <c r="B25" s="19">
-        <v>1</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="19">
-        <v>14</v>
-      </c>
-      <c r="G25" s="20">
-        <v>1</v>
-      </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="19">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" s="19">
         <v>1</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F26" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" s="20">
         <v>1</v>
@@ -2883,123 +2885,126 @@
       <c r="N26" s="19"/>
       <c r="O26" s="19"/>
       <c r="P26" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="19">
+        <v>112</v>
+      </c>
+      <c r="B27" s="19">
+        <v>1</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" s="19">
+        <v>15</v>
+      </c>
+      <c r="G27" s="20">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20"/>
+      <c r="I27" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L27" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" spans="1:16">
-      <c r="A27" s="3">
+    <row r="28" s="3" customFormat="1" spans="1:16">
+      <c r="A28" s="3">
         <v>113</v>
       </c>
-      <c r="B27" s="3">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="3">
         <v>16</v>
       </c>
-      <c r="G27" s="21">
-        <v>1</v>
-      </c>
-      <c r="H27" s="21"/>
-      <c r="I27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="L27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" s="4" customFormat="1" spans="1:16">
-      <c r="A28" s="4">
-        <v>114</v>
-      </c>
-      <c r="B28" s="4">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
+      <c r="G28" s="21">
+        <v>1</v>
+      </c>
+      <c r="H28" s="21"/>
+      <c r="I28" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="J28" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="4">
-        <v>17</v>
-      </c>
-      <c r="G28" s="23">
-        <v>1</v>
-      </c>
-      <c r="H28" s="23"/>
-      <c r="I28" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>38</v>
-      </c>
       <c r="K28" s="19" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="L28" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P28" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="1:16">
-      <c r="A29" s="3">
-        <v>115</v>
-      </c>
-      <c r="B29" s="3">
-        <v>1</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3" t="s">
+      <c r="P28" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" s="4" customFormat="1" spans="1:16">
+      <c r="A29" s="4">
+        <v>114</v>
+      </c>
+      <c r="B29" s="4">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="3">
-        <v>18</v>
-      </c>
-      <c r="G29" s="21">
-        <v>1</v>
-      </c>
-      <c r="H29" s="21"/>
-      <c r="I29" s="3" t="s">
-        <v>94</v>
+      <c r="F29" s="4">
+        <v>17</v>
+      </c>
+      <c r="G29" s="23">
+        <v>1</v>
+      </c>
+      <c r="H29" s="23"/>
+      <c r="I29" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="L29" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="P29" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="30" s="3" customFormat="1" spans="1:16">
       <c r="A30" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
@@ -3012,20 +3017,20 @@
         <v>101</v>
       </c>
       <c r="F30" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G30" s="21">
         <v>1</v>
       </c>
       <c r="H30" s="21"/>
       <c r="I30" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L30" s="3" t="b">
         <v>0</v>
@@ -3036,7 +3041,7 @@
     </row>
     <row r="31" s="3" customFormat="1" spans="1:16">
       <c r="A31" s="3">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>1</v>
@@ -3049,20 +3054,20 @@
         <v>103</v>
       </c>
       <c r="F31" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G31" s="21">
         <v>1</v>
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J31" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L31" s="3" t="b">
         <v>0</v>
@@ -3073,7 +3078,7 @@
     </row>
     <row r="32" s="3" customFormat="1" spans="1:16">
       <c r="A32" s="3">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
@@ -3086,20 +3091,20 @@
         <v>105</v>
       </c>
       <c r="F32" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G32" s="21">
         <v>1</v>
       </c>
       <c r="H32" s="21"/>
       <c r="I32" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L32" s="3" t="b">
         <v>0</v>
@@ -3108,64 +3113,64 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" s="4" customFormat="1" spans="1:16">
-      <c r="A33" s="4">
-        <v>119</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-      <c r="D33" s="4" t="s">
+    <row r="33" s="3" customFormat="1" spans="1:16">
+      <c r="A33" s="3">
+        <v>118</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="F33" s="4">
-        <v>22</v>
-      </c>
-      <c r="G33" s="23">
-        <v>1</v>
-      </c>
-      <c r="H33" s="23"/>
-      <c r="I33" s="19" t="s">
-        <v>37</v>
+      <c r="F33" s="3">
+        <v>21</v>
+      </c>
+      <c r="G33" s="21">
+        <v>1</v>
+      </c>
+      <c r="H33" s="21"/>
+      <c r="I33" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="L33" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="P33" s="4" t="s">
+      <c r="P33" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" s="4" customFormat="1" spans="1:16">
       <c r="A34" s="4">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B34" s="4">
         <v>1</v>
       </c>
-      <c r="C34" s="4"/>
       <c r="D34" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="22" t="s">
         <v>109</v>
       </c>
       <c r="F34" s="4">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G34" s="23">
         <v>1</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4" t="s">
+      <c r="H34" s="23"/>
+      <c r="I34" s="19" t="s">
         <v>37</v>
       </c>
       <c r="J34" s="19" t="s">
@@ -3177,30 +3182,32 @@
       <c r="L34" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="6">
-        <v>121</v>
-      </c>
-      <c r="B35" s="6">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6" t="s">
+      <c r="A35" s="4">
+        <v>120</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F35" s="6">
-        <v>23</v>
-      </c>
-      <c r="G35" s="7">
-        <v>1</v>
-      </c>
-      <c r="I35" s="6" t="s">
+      <c r="E35" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="4">
+        <v>10</v>
+      </c>
+      <c r="G35" s="23">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J35" s="19" t="s">
@@ -3212,19 +3219,28 @@
       <c r="L35" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3" t="s">
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="6">
-        <v>122</v>
+        <v>121</v>
+      </c>
+      <c r="B36" s="6">
+        <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="F36" s="6">
+        <v>23</v>
+      </c>
+      <c r="G36" s="7">
+        <v>1</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>37</v>
@@ -3235,28 +3251,22 @@
       <c r="K36" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L36" s="16" t="b">
-        <v>1</v>
+      <c r="L36" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="6">
-        <v>123</v>
-      </c>
-      <c r="B37" s="6">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="F37" s="6">
-        <v>24</v>
-      </c>
-      <c r="G37" s="7">
-        <v>1</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>37</v>
@@ -3267,13 +3277,13 @@
       <c r="K37" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L37" s="3" t="b">
-        <v>0</v>
+      <c r="L37" s="16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="6">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" s="6">
         <v>1</v>
@@ -3285,7 +3295,7 @@
         <v>115</v>
       </c>
       <c r="F38" s="6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G38" s="7">
         <v>1</v>
@@ -3299,16 +3309,13 @@
       <c r="K38" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L38" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>45</v>
+      <c r="L38" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="6">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B39" s="6">
         <v>1</v>
@@ -3320,7 +3327,7 @@
         <v>117</v>
       </c>
       <c r="F39" s="6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G39" s="7">
         <v>1</v>
@@ -3341,43 +3348,44 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:16">
+    <row r="40" spans="1:16">
       <c r="A40" s="6">
-        <v>126</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="B40" s="6">
+        <v>1</v>
+      </c>
       <c r="D40" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="7"/>
+      <c r="E40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="6">
+        <v>26</v>
+      </c>
+      <c r="G40" s="7">
+        <v>1</v>
+      </c>
       <c r="I40" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="L40" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="L40" s="16" t="b">
+        <v>1</v>
+      </c>
       <c r="P40" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:16">
       <c r="A41" s="6">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3386,18 +3394,18 @@
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
-      <c r="G41" s="7">
-        <v>1</v>
+      <c r="G41" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="K41" s="19" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="L41" s="3" t="b">
         <v>0</v>
@@ -3406,17 +3414,17 @@
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
       <c r="P41" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:16">
       <c r="A42" s="6">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="6"/>
@@ -3433,22 +3441,24 @@
       <c r="K42" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L42" s="16" t="b">
-        <v>1</v>
+      <c r="L42" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
-      <c r="P42" s="3"/>
+      <c r="P42" s="3" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="43" customFormat="1" spans="1:16">
       <c r="A43" s="6">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="6"/>
@@ -3465,8 +3475,8 @@
       <c r="K43" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L43" s="3" t="b">
-        <v>0</v>
+      <c r="L43" s="16" t="b">
+        <v>1</v>
       </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
@@ -3475,12 +3485,12 @@
     </row>
     <row r="44" customFormat="1" spans="1:16">
       <c r="A44" s="6">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="6"/>
@@ -3497,33 +3507,27 @@
       <c r="K44" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L44" s="16" t="b">
-        <v>1</v>
+      <c r="L44" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="P44" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="P44" s="3"/>
     </row>
     <row r="45" customFormat="1" spans="1:16">
       <c r="A45" s="6">
-        <v>1001</v>
-      </c>
-      <c r="B45" s="6">
-        <v>1</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E45" s="4"/>
-      <c r="F45" s="6">
-        <v>1</v>
-      </c>
+      <c r="F45" s="6"/>
       <c r="G45" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="6" t="s">
@@ -3535,21 +3539,19 @@
       <c r="K45" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L45" s="3" t="b">
-        <v>0</v>
+      <c r="L45" s="16" t="b">
+        <v>1</v>
       </c>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
-      <c r="O45" s="6" t="s">
-        <v>125</v>
-      </c>
+      <c r="O45" s="6"/>
       <c r="P45" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:16">
       <c r="A46" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B46" s="6">
         <v>1</v>
@@ -3560,7 +3562,7 @@
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="7">
         <v>5</v>
@@ -3589,7 +3591,7 @@
     </row>
     <row r="47" customFormat="1" spans="1:16">
       <c r="A47" s="6">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B47" s="6">
         <v>1</v>
@@ -3600,7 +3602,7 @@
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="7">
         <v>5</v>
@@ -3627,60 +3629,60 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" s="5" customFormat="1" spans="1:16">
-      <c r="A48" s="5">
-        <v>1004</v>
-      </c>
-      <c r="B48" s="5">
-        <v>1</v>
-      </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5">
-        <v>4</v>
-      </c>
-      <c r="G48" s="25">
+    <row r="48" customFormat="1" spans="1:16">
+      <c r="A48" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B48" s="6">
+        <v>1</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="6">
+        <v>3</v>
+      </c>
+      <c r="G48" s="7">
         <v>5</v>
       </c>
-      <c r="H48" s="25"/>
-      <c r="I48" s="5" t="s">
+      <c r="H48" s="7"/>
+      <c r="I48" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K48" s="5" t="s">
+      <c r="J48" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K48" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L48" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="P48" s="5" t="s">
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="P48" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="49" s="5" customFormat="1" spans="1:16">
       <c r="A49" s="5">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B49" s="5">
         <v>1</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G49" s="25">
         <v>5</v>
@@ -3701,83 +3703,81 @@
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
       <c r="O49" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P49" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:16">
-      <c r="A50" s="6">
-        <v>2001</v>
-      </c>
-      <c r="B50" s="6">
-        <v>1</v>
-      </c>
-      <c r="C50" s="6">
-        <v>11</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6">
-        <v>1</v>
-      </c>
-      <c r="G50" s="7">
-        <v>4</v>
-      </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>76</v>
+    <row r="50" s="5" customFormat="1" spans="1:16">
+      <c r="A50" s="5">
+        <v>1005</v>
+      </c>
+      <c r="B50" s="5">
+        <v>1</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5">
+        <v>5</v>
+      </c>
+      <c r="G50" s="25">
+        <v>5</v>
+      </c>
+      <c r="H50" s="25"/>
+      <c r="I50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="L50" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="O50" s="6" t="s">
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="P50" s="6" t="s">
+      <c r="P50" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:16">
       <c r="A51" s="6">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B51" s="6">
         <v>1</v>
       </c>
-      <c r="C51" s="6"/>
+      <c r="C51" s="6">
+        <v>11</v>
+      </c>
       <c r="D51" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="7">
         <v>4</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="6" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L51" s="3" t="b">
         <v>0</v>
@@ -3790,168 +3790,166 @@
         <v>135</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:16">
       <c r="A52" s="6">
-        <v>2003</v>
-      </c>
-      <c r="B52" s="4">
-        <v>1</v>
-      </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E52" s="22"/>
+        <v>2002</v>
+      </c>
+      <c r="B52" s="6">
+        <v>1</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="6"/>
       <c r="F52" s="6">
-        <v>3</v>
-      </c>
-      <c r="G52" s="23">
+        <v>2</v>
+      </c>
+      <c r="G52" s="7">
         <v>4</v>
       </c>
-      <c r="H52" s="23"/>
-      <c r="I52" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="J52" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="19" t="s">
-        <v>38</v>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="L52" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4" t="s">
+      <c r="M52" s="6"/>
+      <c r="N52" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="O52" s="4" t="s">
+      <c r="O52" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="P52" s="4" t="s">
-        <v>45</v>
+      <c r="P52" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:16">
       <c r="A53" s="6">
-        <v>2004</v>
-      </c>
-      <c r="B53" s="6">
-        <v>1</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E53" s="6"/>
+        <v>2003</v>
+      </c>
+      <c r="B53" s="4">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="22"/>
       <c r="F53" s="6">
+        <v>3</v>
+      </c>
+      <c r="G53" s="23">
         <v>4</v>
       </c>
-      <c r="G53" s="7">
-        <v>4</v>
-      </c>
-      <c r="H53" s="7"/>
-      <c r="I53" s="6" t="s">
+      <c r="H53" s="23"/>
+      <c r="I53" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K53" s="6" t="s">
+      <c r="J53" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="19" t="s">
         <v>38</v>
       </c>
       <c r="L53" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6" t="s">
+      <c r="M53" s="4"/>
+      <c r="N53" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="O53" s="6" t="s">
+      <c r="O53" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="P53" s="6" t="s">
+      <c r="P53" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:16">
       <c r="A54" s="6">
-        <v>2005</v>
-      </c>
-      <c r="B54" s="19">
-        <v>1</v>
-      </c>
-      <c r="C54" s="19">
+        <v>2004</v>
+      </c>
+      <c r="B54" s="6">
+        <v>1</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6">
         <v>4</v>
       </c>
-      <c r="D54" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="19"/>
-      <c r="F54" s="6">
-        <v>5</v>
-      </c>
-      <c r="G54" s="20">
+      <c r="G54" s="7">
         <v>4</v>
       </c>
-      <c r="H54" s="20"/>
-      <c r="I54" s="19" t="s">
+      <c r="H54" s="7"/>
+      <c r="I54" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J54" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K54" s="19" t="s">
+      <c r="J54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K54" s="6" t="s">
         <v>38</v>
       </c>
       <c r="L54" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19" t="s">
+      <c r="M54" s="6"/>
+      <c r="N54" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="O54" s="19" t="s">
+      <c r="O54" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:16">
       <c r="A55" s="6">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B55" s="19">
         <v>1</v>
       </c>
       <c r="C55" s="19">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E55" s="19"/>
-      <c r="F55" s="19">
-        <v>6</v>
+      <c r="F55" s="6">
+        <v>5</v>
       </c>
       <c r="G55" s="20">
         <v>4</v>
       </c>
       <c r="H55" s="20"/>
       <c r="I55" s="19" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="L55" s="3" t="b">
         <v>0</v>
@@ -3964,38 +3962,38 @@
         <v>143</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:16">
       <c r="A56" s="6">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B56" s="19">
         <v>1</v>
       </c>
       <c r="C56" s="19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E56" s="19"/>
       <c r="F56" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G56" s="20">
         <v>4</v>
       </c>
       <c r="H56" s="20"/>
       <c r="I56" s="19" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="J56" s="19" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="L56" s="3" t="b">
         <v>0</v>
@@ -4008,6 +4006,50 @@
         <v>145</v>
       </c>
       <c r="P56" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:16">
+      <c r="A57" s="6">
+        <v>2007</v>
+      </c>
+      <c r="B57" s="19">
+        <v>1</v>
+      </c>
+      <c r="C57" s="19">
+        <v>5</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19">
+        <v>7</v>
+      </c>
+      <c r="G57" s="20">
+        <v>4</v>
+      </c>
+      <c r="H57" s="20"/>
+      <c r="I57" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J57" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" s="19"/>
+      <c r="N57" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="O57" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="P57" s="6" t="s">
         <v>39</v>
       </c>
     </row>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -2402,7 +2402,9 @@
       <c r="A15" s="14">
         <v>11</v>
       </c>
-      <c r="B15" s="14"/>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
         <v>60</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -171,6 +171,8 @@
 3：显示在登陆界面对应位置
 4：显示在活动页面（仅限web端）
 5: 显示在最下方导航栏（仅限web端）
+6：显示在最下方导航栏（模拟经营）
+7：显示在活动页面（模拟经营）
 参数：位置1_位置2  即 大厅显示_游戏界面显示</t>
         </r>
       </text>
@@ -323,7 +325,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="153">
   <si>
     <t>id</t>
   </si>
@@ -767,6 +769,21 @@
   </si>
   <si>
     <t>btn_lottery</t>
+  </si>
+  <si>
+    <t>好友聊天</t>
+  </si>
+  <si>
+    <t>显示位置：模拟经营大厅</t>
+  </si>
+  <si>
+    <t>游客雇员抽卡</t>
+  </si>
+  <si>
+    <t>联盟</t>
+  </si>
+  <si>
+    <t>赛季</t>
   </si>
 </sst>
 </file>
@@ -1843,7 +1860,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="6" customWidth="1"/>
@@ -4053,6 +4070,131 @@
       </c>
       <c r="P57" s="6" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" s="6">
+        <v>5001</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F58" s="6">
+        <v>1</v>
+      </c>
+      <c r="G58" s="7">
+        <v>7</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J58" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" s="6">
+        <v>5002</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" s="6">
+        <v>2</v>
+      </c>
+      <c r="G59" s="7">
+        <v>6</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J59" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" s="6">
+        <v>5003</v>
+      </c>
+      <c r="B60" s="6">
+        <v>1</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F60" s="6">
+        <v>3</v>
+      </c>
+      <c r="G60" s="7">
+        <v>6</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L60" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" s="6">
+        <v>5004</v>
+      </c>
+      <c r="B61" s="6">
+        <v>1</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F61" s="6">
+        <v>4</v>
+      </c>
+      <c r="G61" s="7">
+        <v>6</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J61" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -829,9 +829,6 @@
   </si>
   <si>
     <t>simAllLevel(5)</t>
-  </si>
-  <si>
-    <t>TURE</t>
   </si>
   <si>
     <t>显示位置：模拟经营大厅</t>
@@ -4093,8 +4090,8 @@
       <c r="K58" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L58" s="1" t="s">
-        <v>164</v>
+      <c r="L58" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="M58" s="4">
         <v>4062004</v>
@@ -4102,7 +4099,7 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4113,10 +4110,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="G59" s="7">
         <v>3</v>
@@ -4130,14 +4127,14 @@
       <c r="K59" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L59" s="1" t="s">
-        <v>164</v>
+      <c r="L59" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="M59" s="4">
         <v>4062004</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4148,10 +4145,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="G60" s="7">
         <v>5</v>
@@ -4160,19 +4157,19 @@
         <v>37</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
+      </c>
+      <c r="L60" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="M60" s="4">
         <v>4062001</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4183,10 +4180,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="G61" s="7">
         <v>5</v>
@@ -4195,19 +4192,19 @@
         <v>37</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
+      </c>
+      <c r="L61" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="M61" s="4">
         <v>4062002</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4218,10 +4215,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="G62" s="7">
         <v>5</v>
@@ -4235,14 +4232,14 @@
       <c r="K62" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L62" s="1" t="s">
-        <v>164</v>
+      <c r="L62" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="M62" s="4">
         <v>4062004</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4253,10 +4250,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="G63" s="7">
         <v>5</v>
@@ -4270,14 +4267,14 @@
       <c r="K63" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L63" s="1" t="s">
-        <v>164</v>
+      <c r="L63" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="M63" s="4">
         <v>4062003</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4288,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="G64" s="7">
         <v>2</v>
@@ -4305,11 +4302,11 @@
       <c r="K64" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="L64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P64" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -1079,12 +1079,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1659,6 +1659,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2175,38 +2184,40 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="4">
+    <row r="7" s="2" customFormat="1" spans="1:16">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
         <v>9</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="7">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="F7" s="2"/>
+      <c r="G7" s="14">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P7" s="4" t="s">
+      <c r="L7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3082,10 +3093,12 @@
       <c r="F31" s="4">
         <v>19</v>
       </c>
-      <c r="G31" s="7"/>
+      <c r="G31" s="7">
+        <v>1</v>
+      </c>
       <c r="H31" s="7"/>
       <c r="I31" s="4" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>45</v>
@@ -3743,9 +3756,7 @@
       <c r="D50" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="19">
         <v>5</v>
@@ -4310,6 +4321,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E$1:E$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="181">
   <si>
     <t>id</t>
   </si>
@@ -874,6 +874,12 @@
   </si>
   <si>
     <t>Grid (42)</t>
+  </si>
+  <si>
+    <t>拜访(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_randomvisit</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +1933,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -4084,7 +4090,7 @@
       <c r="D58" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F58" s="4"/>
@@ -4320,9 +4326,44 @@
         <v>164</v>
       </c>
     </row>
+    <row r="65" spans="1:16">
+      <c r="A65" s="4">
+        <v>5007</v>
+      </c>
+      <c r="B65" s="4">
+        <v>1</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G65" s="7">
+        <v>3</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E$1:E$1048576">
+  <conditionalFormatting sqref="E65">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E64 E66:E1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="182">
   <si>
     <t>id</t>
   </si>
@@ -721,6 +721,9 @@
   </si>
   <si>
     <t>指定生成游客(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_special_guests</t>
   </si>
   <si>
     <t>首页(网页竖版)</t>
@@ -3574,7 +3577,9 @@
       <c r="D45" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E45" s="4"/>
+      <c r="E45" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="F45" s="4"/>
       <c r="G45" s="7">
         <v>4</v>
@@ -3608,7 +3613,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -3631,7 +3636,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>46</v>
@@ -3646,7 +3651,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -3669,7 +3674,7 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>46</v>
@@ -3684,7 +3689,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3707,7 +3712,7 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>46</v>
@@ -3722,7 +3727,7 @@
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -3745,7 +3750,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>46</v>
@@ -3760,7 +3765,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -3783,7 +3788,7 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>46</v>
@@ -3800,7 +3805,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -3822,10 +3827,10 @@
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>46</v>
@@ -3840,7 +3845,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -3849,23 +3854,23 @@
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>39</v>
@@ -3880,7 +3885,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E53" s="16"/>
       <c r="F53" s="2"/>
@@ -3902,10 +3907,10 @@
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>46</v>
@@ -3922,7 +3927,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -3944,10 +3949,10 @@
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>46</v>
@@ -3964,7 +3969,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -3986,10 +3991,10 @@
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>39</v>
@@ -4006,7 +4011,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -4028,10 +4033,10 @@
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>46</v>
@@ -4048,7 +4053,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -4070,10 +4075,10 @@
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>39</v>
@@ -4088,10 +4093,10 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="7">
@@ -4102,10 +4107,10 @@
         <v>37</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L58" s="1" t="b">
         <v>1</v>
@@ -4116,7 +4121,7 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4127,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G59" s="7">
         <v>3</v>
@@ -4139,10 +4144,10 @@
         <v>37</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L59" s="1" t="b">
         <v>1</v>
@@ -4151,7 +4156,7 @@
         <v>4062004</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4162,10 +4167,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G60" s="7">
         <v>5</v>
@@ -4174,10 +4179,10 @@
         <v>37</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L60" s="1" t="b">
         <v>1</v>
@@ -4186,7 +4191,7 @@
         <v>4062001</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4197,10 +4202,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G61" s="7">
         <v>5</v>
@@ -4209,10 +4214,10 @@
         <v>37</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L61" s="1" t="b">
         <v>1</v>
@@ -4221,7 +4226,7 @@
         <v>4062002</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4232,10 +4237,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G62" s="7">
         <v>5</v>
@@ -4244,10 +4249,10 @@
         <v>37</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L62" s="1" t="b">
         <v>1</v>
@@ -4256,7 +4261,7 @@
         <v>4062004</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4267,10 +4272,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G63" s="7">
         <v>5</v>
@@ -4291,7 +4296,7 @@
         <v>4062003</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4302,10 +4307,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G64" s="7">
         <v>2</v>
@@ -4323,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4334,10 +4339,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G65" s="7">
         <v>3</v>
@@ -4355,15 +4360,15 @@
         <v>1</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E65">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E64 E66:E1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="185">
   <si>
     <t>id</t>
   </si>
@@ -522,361 +522,370 @@
     <t>btn_mail</t>
   </si>
   <si>
+    <t>simAllLevel(10)</t>
+  </si>
+  <si>
+    <t>幸运夺宝(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (21)</t>
+  </si>
+  <si>
+    <t>背包(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (40)</t>
+  </si>
+  <si>
+    <t>我的赌场(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (8)</t>
+  </si>
+  <si>
+    <t>1_20</t>
+  </si>
+  <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>simAllLevel(12)</t>
+  </si>
+  <si>
+    <t>刮刮乐(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>simAllLevel(8)</t>
+  </si>
+  <si>
+    <t>储钱罐(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
+    <t>simAllLevel(5)</t>
+  </si>
+  <si>
+    <t>等级礼包(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_levelGift</t>
+  </si>
+  <si>
+    <t>首充礼包(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>remainingAttempts(57011,1,1)</t>
+  </si>
+  <si>
+    <t>成长基金(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (1)</t>
+  </si>
+  <si>
+    <t>1_10</t>
+  </si>
+  <si>
+    <t>playerLevel(10)</t>
+  </si>
+  <si>
+    <t>签到奖励(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (3)</t>
+  </si>
+  <si>
+    <t>邮箱(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (4)</t>
+  </si>
+  <si>
+    <t>安全箱(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (5)</t>
+  </si>
+  <si>
+    <t>客服(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (6)</t>
+  </si>
+  <si>
+    <t>显示位置：大厅+登陆界面</t>
+  </si>
+  <si>
+    <t>设置(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (7)</t>
+  </si>
+  <si>
+    <t>收集拼图(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (12)</t>
+  </si>
+  <si>
+    <t>1_999</t>
+  </si>
+  <si>
+    <t>playerLevel(999)</t>
+  </si>
+  <si>
+    <t>每日充值(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (14)</t>
+  </si>
+  <si>
+    <t>排行(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (15)</t>
+  </si>
+  <si>
+    <t>任务(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (16)</t>
+  </si>
+  <si>
+    <t>夺宝(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (17)</t>
+  </si>
+  <si>
+    <t>钻石基金(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (18)</t>
+  </si>
+  <si>
+    <t>限时礼包(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (22)</t>
+  </si>
+  <si>
+    <t>财富轮盘(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (23)</t>
+  </si>
+  <si>
+    <t>买一送七(横版app版)</t>
+  </si>
+  <si>
+    <t>新手赠送(app竖版)</t>
+  </si>
+  <si>
+    <t>充值活动：福利</t>
+  </si>
+  <si>
+    <t>Grid (24)</t>
+  </si>
+  <si>
+    <t>礼包码(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (25)</t>
+  </si>
+  <si>
+    <t>新游期待榜(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (26)</t>
+  </si>
+  <si>
+    <t>充值引导(横版app版)</t>
+  </si>
+  <si>
+    <t>NOT(accountTotalRecharge(0.001))</t>
+  </si>
+  <si>
+    <t>免费旋转(横版app版)</t>
+  </si>
+  <si>
+    <t>进SLOT大厅(横版app版)</t>
+  </si>
+  <si>
+    <t>对战(横版app版)</t>
+  </si>
+  <si>
+    <t>指定生成游客(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_special_guests</t>
+  </si>
+  <si>
+    <t>simAllLevel(2)</t>
+  </si>
+  <si>
+    <t>首页(网页竖版)</t>
+  </si>
+  <si>
+    <t>tap_home</t>
+  </si>
+  <si>
+    <t>活动(网页竖版)</t>
+  </si>
+  <si>
+    <t>tap_activity</t>
+  </si>
+  <si>
+    <t>菜单(网页竖版)</t>
+  </si>
+  <si>
+    <t>btn_muen</t>
+  </si>
+  <si>
+    <t>客服(网页竖版)</t>
+  </si>
+  <si>
+    <t>btn_service</t>
+  </si>
+  <si>
+    <t>商城界面(网页竖版)</t>
+  </si>
+  <si>
+    <t>btn_shop</t>
+  </si>
+  <si>
+    <t>首充礼包(网页竖版)</t>
+  </si>
+  <si>
+    <t>sc-7</t>
+  </si>
+  <si>
+    <t>btn_first</t>
+  </si>
+  <si>
+    <t>等级礼包(网页竖版)</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
+    <t>djlb-3</t>
+  </si>
+  <si>
+    <t>btn_level_gift</t>
+  </si>
+  <si>
+    <t>每日充值(网页竖版)</t>
+  </si>
+  <si>
+    <t>qtlc-6</t>
+  </si>
+  <si>
+    <t>btn_first_daily</t>
+  </si>
+  <si>
+    <t>每日奖金(网页竖版)</t>
+  </si>
+  <si>
+    <t>mrjj-5</t>
+  </si>
+  <si>
+    <t>btn_privilege</t>
+  </si>
+  <si>
+    <t>储钱罐(网页竖版)</t>
+  </si>
+  <si>
+    <t>cqg-1</t>
+  </si>
+  <si>
+    <t>btn_pig</t>
+  </si>
+  <si>
+    <t>成长基金(网页竖版)</t>
+  </si>
+  <si>
+    <t>czjj-2</t>
+  </si>
+  <si>
+    <t>btn_growth_fund</t>
+  </si>
+  <si>
+    <t>刮刮乐(网页竖版)</t>
+  </si>
+  <si>
+    <t>ggk-4</t>
+  </si>
+  <si>
+    <t>btn_lottery</t>
+  </si>
+  <si>
+    <t>聊天(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_chat</t>
+  </si>
+  <si>
+    <t>显示位置：模拟经营大厅</t>
+  </si>
+  <si>
+    <t>好友(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_friend</t>
+  </si>
+  <si>
+    <t>雇员\游客抽卡(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_zm</t>
+  </si>
+  <si>
+    <t>联盟(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_lm</t>
+  </si>
+  <si>
+    <t>赛季(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_yjy</t>
+  </si>
+  <si>
+    <t>simAllLevel(6)</t>
+  </si>
+  <si>
+    <t>SLOT(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_games</t>
+  </si>
+  <si>
+    <t>拜访记录(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (42)</t>
+  </si>
+  <si>
     <t>simAllLevel(15)</t>
-  </si>
-  <si>
-    <t>幸运夺宝(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (21)</t>
-  </si>
-  <si>
-    <t>背包(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (40)</t>
-  </si>
-  <si>
-    <t>我的赌场(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (8)</t>
-  </si>
-  <si>
-    <t>1_20</t>
-  </si>
-  <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>刮刮乐(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>储钱罐(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
-    <t>等级礼包(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_levelGift</t>
-  </si>
-  <si>
-    <t>首充礼包(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>remainingAttempts(57011,1,1)</t>
-  </si>
-  <si>
-    <t>成长基金(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (1)</t>
-  </si>
-  <si>
-    <t>1_10</t>
-  </si>
-  <si>
-    <t>playerLevel(10)</t>
-  </si>
-  <si>
-    <t>签到奖励(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (3)</t>
-  </si>
-  <si>
-    <t>邮箱(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (4)</t>
-  </si>
-  <si>
-    <t>安全箱(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (5)</t>
-  </si>
-  <si>
-    <t>客服(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (6)</t>
-  </si>
-  <si>
-    <t>显示位置：大厅+登陆界面</t>
-  </si>
-  <si>
-    <t>设置(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (7)</t>
-  </si>
-  <si>
-    <t>收集拼图(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (12)</t>
-  </si>
-  <si>
-    <t>1_999</t>
-  </si>
-  <si>
-    <t>playerLevel(999)</t>
-  </si>
-  <si>
-    <t>每日充值(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (14)</t>
-  </si>
-  <si>
-    <t>排行(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (15)</t>
-  </si>
-  <si>
-    <t>任务(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (16)</t>
-  </si>
-  <si>
-    <t>夺宝(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (17)</t>
-  </si>
-  <si>
-    <t>钻石基金(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (18)</t>
-  </si>
-  <si>
-    <t>限时礼包(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (22)</t>
-  </si>
-  <si>
-    <t>财富轮盘(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (23)</t>
-  </si>
-  <si>
-    <t>买一送七(横版app版)</t>
-  </si>
-  <si>
-    <t>新手赠送(app竖版)</t>
-  </si>
-  <si>
-    <t>充值活动：福利</t>
-  </si>
-  <si>
-    <t>Grid (24)</t>
-  </si>
-  <si>
-    <t>礼包码(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (25)</t>
-  </si>
-  <si>
-    <t>新游期待榜(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (26)</t>
-  </si>
-  <si>
-    <t>充值引导(横版app版)</t>
-  </si>
-  <si>
-    <t>NOT(accountTotalRecharge(0.001))</t>
-  </si>
-  <si>
-    <t>免费旋转(横版app版)</t>
-  </si>
-  <si>
-    <t>进SLOT大厅(横版app版)</t>
-  </si>
-  <si>
-    <t>对战(横版app版)</t>
-  </si>
-  <si>
-    <t>指定生成游客(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_special_guests</t>
-  </si>
-  <si>
-    <t>首页(网页竖版)</t>
-  </si>
-  <si>
-    <t>tap_home</t>
-  </si>
-  <si>
-    <t>活动(网页竖版)</t>
-  </si>
-  <si>
-    <t>tap_activity</t>
-  </si>
-  <si>
-    <t>菜单(网页竖版)</t>
-  </si>
-  <si>
-    <t>btn_muen</t>
-  </si>
-  <si>
-    <t>客服(网页竖版)</t>
-  </si>
-  <si>
-    <t>btn_service</t>
-  </si>
-  <si>
-    <t>商城界面(网页竖版)</t>
-  </si>
-  <si>
-    <t>btn_shop</t>
-  </si>
-  <si>
-    <t>首充礼包(网页竖版)</t>
-  </si>
-  <si>
-    <t>sc-7</t>
-  </si>
-  <si>
-    <t>btn_first</t>
-  </si>
-  <si>
-    <t>等级礼包(网页竖版)</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>playerLevel(30)</t>
-  </si>
-  <si>
-    <t>djlb-3</t>
-  </si>
-  <si>
-    <t>btn_level_gift</t>
-  </si>
-  <si>
-    <t>每日充值(网页竖版)</t>
-  </si>
-  <si>
-    <t>qtlc-6</t>
-  </si>
-  <si>
-    <t>btn_first_daily</t>
-  </si>
-  <si>
-    <t>每日奖金(网页竖版)</t>
-  </si>
-  <si>
-    <t>mrjj-5</t>
-  </si>
-  <si>
-    <t>btn_privilege</t>
-  </si>
-  <si>
-    <t>储钱罐(网页竖版)</t>
-  </si>
-  <si>
-    <t>cqg-1</t>
-  </si>
-  <si>
-    <t>btn_pig</t>
-  </si>
-  <si>
-    <t>成长基金(网页竖版)</t>
-  </si>
-  <si>
-    <t>czjj-2</t>
-  </si>
-  <si>
-    <t>btn_growth_fund</t>
-  </si>
-  <si>
-    <t>刮刮乐(网页竖版)</t>
-  </si>
-  <si>
-    <t>ggk-4</t>
-  </si>
-  <si>
-    <t>btn_lottery</t>
-  </si>
-  <si>
-    <t>聊天(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_chat</t>
-  </si>
-  <si>
-    <t>simAllLevel(5)</t>
-  </si>
-  <si>
-    <t>显示位置：模拟经营大厅</t>
-  </si>
-  <si>
-    <t>好友(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_friend</t>
-  </si>
-  <si>
-    <t>雇员\游客抽卡(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_zm</t>
-  </si>
-  <si>
-    <t>simAllLevel(2)</t>
-  </si>
-  <si>
-    <t>联盟(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_lm</t>
-  </si>
-  <si>
-    <t>simAllLevel(10)</t>
-  </si>
-  <si>
-    <t>赛季(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_yjy</t>
-  </si>
-  <si>
-    <t>SLOT(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_games</t>
-  </si>
-  <si>
-    <t>拜访记录(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (42)</t>
   </si>
   <si>
     <t>拜访(app竖版)</t>
@@ -895,7 +904,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -940,6 +949,12 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1425,137 +1440,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1615,6 +1630,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2552,9 +2570,7 @@
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M16" s="2">
-        <v>47061</v>
-      </c>
+      <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2" t="s">
@@ -2587,10 +2603,10 @@
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="L17" s="1" t="b">
         <v>1</v>
@@ -2610,10 +2626,10 @@
         <v>5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" s="4">
         <v>9</v>
@@ -2625,10 +2641,10 @@
         <v>37</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="L18" s="1" t="b">
         <v>1</v>
@@ -2648,10 +2664,10 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F19" s="4">
         <v>3</v>
@@ -2663,10 +2679,10 @@
         <v>37</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="L19" s="1" t="b">
         <v>1</v>
@@ -2683,10 +2699,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F20" s="4">
         <v>6</v>
@@ -2721,10 +2737,10 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2">
         <v>7</v>
@@ -2737,10 +2753,10 @@
         <v>41</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
@@ -2763,10 +2779,10 @@
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F22" s="2">
         <v>8</v>
@@ -2776,13 +2792,13 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
@@ -2805,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F23" s="4">
         <v>11</v>
@@ -2840,10 +2856,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F24" s="4">
         <v>12</v>
@@ -2876,10 +2892,10 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2">
         <v>13</v>
@@ -2915,10 +2931,10 @@
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F26" s="4">
         <v>14</v>
@@ -2936,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2947,10 +2963,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F27" s="4">
         <v>15</v>
@@ -2983,10 +2999,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
@@ -2996,13 +3012,13 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
@@ -3020,10 +3036,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
@@ -3057,10 +3073,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
@@ -3070,13 +3086,13 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
@@ -3094,10 +3110,10 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F31" s="4">
         <v>19</v>
@@ -3131,10 +3147,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
@@ -3144,13 +3160,13 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
@@ -3168,10 +3184,10 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F33" s="2">
         <v>21</v>
@@ -3181,13 +3197,13 @@
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
@@ -3204,10 +3220,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F34" s="2">
         <v>22</v>
@@ -3241,10 +3257,10 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -3281,7 +3297,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2">
@@ -3315,7 +3331,7 @@
         <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>37</v>
@@ -3339,10 +3355,10 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2">
         <v>24</v>
@@ -3372,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F39" s="4">
         <v>25</v>
@@ -3408,10 +3424,10 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F40" s="2">
         <v>26</v>
@@ -3443,7 +3459,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -3455,10 +3471,10 @@
         <v>37</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L41" s="2" t="b">
         <v>0</v>
@@ -3477,7 +3493,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -3511,7 +3527,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -3543,7 +3559,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -3575,10 +3591,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="7">
@@ -3589,10 +3605,10 @@
         <v>37</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="L45" s="1" t="b">
         <v>1</v>
@@ -3613,7 +3629,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -3636,7 +3652,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>46</v>
@@ -3651,7 +3667,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -3674,7 +3690,7 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>46</v>
@@ -3689,7 +3705,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3712,7 +3728,7 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>46</v>
@@ -3727,7 +3743,7 @@
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -3750,7 +3766,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>46</v>
@@ -3765,7 +3781,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -3788,7 +3804,7 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>46</v>
@@ -3805,7 +3821,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -3817,20 +3833,20 @@
         <v>41</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>46</v>
@@ -3845,7 +3861,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -3854,23 +3870,23 @@
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>39</v>
@@ -3885,7 +3901,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E53" s="16"/>
       <c r="F53" s="2"/>
@@ -3907,10 +3923,10 @@
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>46</v>
@@ -3927,7 +3943,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -3949,10 +3965,10 @@
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>46</v>
@@ -3969,7 +3985,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -3991,10 +4007,10 @@
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>39</v>
@@ -4011,7 +4027,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -4020,23 +4036,23 @@
       </c>
       <c r="H56" s="14"/>
       <c r="I56" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>46</v>
@@ -4053,7 +4069,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -4075,10 +4091,10 @@
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>39</v>
@@ -4093,10 +4109,10 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="7">
@@ -4107,21 +4123,19 @@
         <v>37</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="L58" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M58" s="4">
-        <v>4062004</v>
-      </c>
+      <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4132,10 +4146,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G59" s="7">
         <v>3</v>
@@ -4144,19 +4158,16 @@
         <v>37</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="L59" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M59" s="4">
-        <v>4062004</v>
-      </c>
       <c r="P59" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4167,10 +4178,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G60" s="7">
         <v>5</v>
@@ -4179,10 +4190,10 @@
         <v>37</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="L60" s="1" t="b">
         <v>1</v>
@@ -4191,7 +4202,7 @@
         <v>4062001</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4202,10 +4213,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G61" s="7">
         <v>5</v>
@@ -4214,19 +4225,19 @@
         <v>37</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="L61" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M61" s="4">
+      <c r="M61" s="20">
         <v>4062002</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4237,10 +4248,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G62" s="7">
         <v>5</v>
@@ -4249,19 +4260,19 @@
         <v>37</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="L62" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M62" s="4">
+      <c r="M62" s="20">
         <v>4062004</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4272,10 +4283,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G63" s="7">
         <v>5</v>
@@ -4292,11 +4303,8 @@
       <c r="L63" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M63" s="4">
-        <v>4062003</v>
-      </c>
       <c r="P63" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4307,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G64" s="7">
         <v>2</v>
@@ -4319,16 +4327,16 @@
         <v>37</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="L64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4339,10 +4347,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G65" s="7">
         <v>3</v>
@@ -4351,16 +4359,16 @@
         <v>37</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="L65" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -522,346 +522,346 @@
     <t>btn_mail</t>
   </si>
   <si>
+    <t>幸运夺宝(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (21)</t>
+  </si>
+  <si>
+    <t>背包(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (40)</t>
+  </si>
+  <si>
+    <t>我的赌场(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (8)</t>
+  </si>
+  <si>
+    <t>1_20</t>
+  </si>
+  <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>simAllLevel(12)</t>
+  </si>
+  <si>
+    <t>刮刮乐(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>simAllLevel(8)</t>
+  </si>
+  <si>
+    <t>储钱罐(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
+    <t>simAllLevel(5)</t>
+  </si>
+  <si>
+    <t>等级礼包(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_levelGift</t>
+  </si>
+  <si>
+    <t>首充礼包(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (13)</t>
+  </si>
+  <si>
+    <t>remainingAttempts(57011,1,1)</t>
+  </si>
+  <si>
+    <t>成长基金(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (1)</t>
+  </si>
+  <si>
+    <t>1_10</t>
+  </si>
+  <si>
+    <t>playerLevel(10)</t>
+  </si>
+  <si>
+    <t>签到奖励(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (3)</t>
+  </si>
+  <si>
+    <t>邮箱(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (4)</t>
+  </si>
+  <si>
+    <t>安全箱(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (5)</t>
+  </si>
+  <si>
+    <t>客服(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (6)</t>
+  </si>
+  <si>
+    <t>显示位置：大厅+登陆界面</t>
+  </si>
+  <si>
+    <t>设置(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (7)</t>
+  </si>
+  <si>
+    <t>收集拼图(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (12)</t>
+  </si>
+  <si>
+    <t>1_999</t>
+  </si>
+  <si>
+    <t>playerLevel(999)</t>
+  </si>
+  <si>
+    <t>每日充值(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (14)</t>
+  </si>
+  <si>
+    <t>排行(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (15)</t>
+  </si>
+  <si>
+    <t>任务(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (16)</t>
+  </si>
+  <si>
+    <t>夺宝(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (17)</t>
+  </si>
+  <si>
+    <t>钻石基金(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (18)</t>
+  </si>
+  <si>
+    <t>限时礼包(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (22)</t>
+  </si>
+  <si>
+    <t>财富轮盘(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (23)</t>
+  </si>
+  <si>
+    <t>买一送七(横版app版)</t>
+  </si>
+  <si>
+    <t>新手赠送(app竖版)</t>
+  </si>
+  <si>
+    <t>充值活动：福利</t>
+  </si>
+  <si>
+    <t>Grid (24)</t>
+  </si>
+  <si>
+    <t>礼包码(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (25)</t>
+  </si>
+  <si>
+    <t>新游期待榜(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (26)</t>
+  </si>
+  <si>
+    <t>充值引导(横版app版)</t>
+  </si>
+  <si>
+    <t>NOT(accountTotalRecharge(0.001))</t>
+  </si>
+  <si>
+    <t>免费旋转(横版app版)</t>
+  </si>
+  <si>
+    <t>进SLOT大厅(横版app版)</t>
+  </si>
+  <si>
+    <t>对战(横版app版)</t>
+  </si>
+  <si>
+    <t>指定生成游客(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_special_guests</t>
+  </si>
+  <si>
+    <t>simAllLevel(2)</t>
+  </si>
+  <si>
+    <t>首页(网页竖版)</t>
+  </si>
+  <si>
+    <t>tap_home</t>
+  </si>
+  <si>
+    <t>活动(网页竖版)</t>
+  </si>
+  <si>
+    <t>tap_activity</t>
+  </si>
+  <si>
+    <t>菜单(网页竖版)</t>
+  </si>
+  <si>
+    <t>btn_muen</t>
+  </si>
+  <si>
+    <t>客服(网页竖版)</t>
+  </si>
+  <si>
+    <t>btn_service</t>
+  </si>
+  <si>
+    <t>商城界面(网页竖版)</t>
+  </si>
+  <si>
+    <t>btn_shop</t>
+  </si>
+  <si>
+    <t>首充礼包(网页竖版)</t>
+  </si>
+  <si>
+    <t>sc-7</t>
+  </si>
+  <si>
+    <t>btn_first</t>
+  </si>
+  <si>
+    <t>等级礼包(网页竖版)</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>playerLevel(30)</t>
+  </si>
+  <si>
+    <t>djlb-3</t>
+  </si>
+  <si>
+    <t>btn_level_gift</t>
+  </si>
+  <si>
+    <t>每日充值(网页竖版)</t>
+  </si>
+  <si>
+    <t>qtlc-6</t>
+  </si>
+  <si>
+    <t>btn_first_daily</t>
+  </si>
+  <si>
+    <t>每日奖金(网页竖版)</t>
+  </si>
+  <si>
+    <t>mrjj-5</t>
+  </si>
+  <si>
+    <t>btn_privilege</t>
+  </si>
+  <si>
+    <t>储钱罐(网页竖版)</t>
+  </si>
+  <si>
+    <t>cqg-1</t>
+  </si>
+  <si>
+    <t>btn_pig</t>
+  </si>
+  <si>
+    <t>成长基金(网页竖版)</t>
+  </si>
+  <si>
+    <t>czjj-2</t>
+  </si>
+  <si>
+    <t>btn_growth_fund</t>
+  </si>
+  <si>
+    <t>刮刮乐(网页竖版)</t>
+  </si>
+  <si>
+    <t>ggk-4</t>
+  </si>
+  <si>
+    <t>btn_lottery</t>
+  </si>
+  <si>
+    <t>聊天(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_chat</t>
+  </si>
+  <si>
+    <t>显示位置：模拟经营大厅</t>
+  </si>
+  <si>
+    <t>好友(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_friend</t>
+  </si>
+  <si>
+    <t>雇员\游客抽卡(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_zm</t>
+  </si>
+  <si>
+    <t>联盟(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_lm</t>
+  </si>
+  <si>
     <t>simAllLevel(10)</t>
-  </si>
-  <si>
-    <t>幸运夺宝(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (21)</t>
-  </si>
-  <si>
-    <t>背包(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (40)</t>
-  </si>
-  <si>
-    <t>我的赌场(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (8)</t>
-  </si>
-  <si>
-    <t>1_20</t>
-  </si>
-  <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>simAllLevel(12)</t>
-  </si>
-  <si>
-    <t>刮刮乐(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>simAllLevel(8)</t>
-  </si>
-  <si>
-    <t>储钱罐(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
-    <t>simAllLevel(5)</t>
-  </si>
-  <si>
-    <t>等级礼包(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_levelGift</t>
-  </si>
-  <si>
-    <t>首充礼包(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (13)</t>
-  </si>
-  <si>
-    <t>remainingAttempts(57011,1,1)</t>
-  </si>
-  <si>
-    <t>成长基金(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (1)</t>
-  </si>
-  <si>
-    <t>1_10</t>
-  </si>
-  <si>
-    <t>playerLevel(10)</t>
-  </si>
-  <si>
-    <t>签到奖励(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (3)</t>
-  </si>
-  <si>
-    <t>邮箱(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (4)</t>
-  </si>
-  <si>
-    <t>安全箱(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (5)</t>
-  </si>
-  <si>
-    <t>客服(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (6)</t>
-  </si>
-  <si>
-    <t>显示位置：大厅+登陆界面</t>
-  </si>
-  <si>
-    <t>设置(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (7)</t>
-  </si>
-  <si>
-    <t>收集拼图(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (12)</t>
-  </si>
-  <si>
-    <t>1_999</t>
-  </si>
-  <si>
-    <t>playerLevel(999)</t>
-  </si>
-  <si>
-    <t>每日充值(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (14)</t>
-  </si>
-  <si>
-    <t>排行(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (15)</t>
-  </si>
-  <si>
-    <t>任务(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (16)</t>
-  </si>
-  <si>
-    <t>夺宝(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (17)</t>
-  </si>
-  <si>
-    <t>钻石基金(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (18)</t>
-  </si>
-  <si>
-    <t>限时礼包(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (22)</t>
-  </si>
-  <si>
-    <t>财富轮盘(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (23)</t>
-  </si>
-  <si>
-    <t>买一送七(横版app版)</t>
-  </si>
-  <si>
-    <t>新手赠送(app竖版)</t>
-  </si>
-  <si>
-    <t>充值活动：福利</t>
-  </si>
-  <si>
-    <t>Grid (24)</t>
-  </si>
-  <si>
-    <t>礼包码(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (25)</t>
-  </si>
-  <si>
-    <t>新游期待榜(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (26)</t>
-  </si>
-  <si>
-    <t>充值引导(横版app版)</t>
-  </si>
-  <si>
-    <t>NOT(accountTotalRecharge(0.001))</t>
-  </si>
-  <si>
-    <t>免费旋转(横版app版)</t>
-  </si>
-  <si>
-    <t>进SLOT大厅(横版app版)</t>
-  </si>
-  <si>
-    <t>对战(横版app版)</t>
-  </si>
-  <si>
-    <t>指定生成游客(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_special_guests</t>
-  </si>
-  <si>
-    <t>simAllLevel(2)</t>
-  </si>
-  <si>
-    <t>首页(网页竖版)</t>
-  </si>
-  <si>
-    <t>tap_home</t>
-  </si>
-  <si>
-    <t>活动(网页竖版)</t>
-  </si>
-  <si>
-    <t>tap_activity</t>
-  </si>
-  <si>
-    <t>菜单(网页竖版)</t>
-  </si>
-  <si>
-    <t>btn_muen</t>
-  </si>
-  <si>
-    <t>客服(网页竖版)</t>
-  </si>
-  <si>
-    <t>btn_service</t>
-  </si>
-  <si>
-    <t>商城界面(网页竖版)</t>
-  </si>
-  <si>
-    <t>btn_shop</t>
-  </si>
-  <si>
-    <t>首充礼包(网页竖版)</t>
-  </si>
-  <si>
-    <t>sc-7</t>
-  </si>
-  <si>
-    <t>btn_first</t>
-  </si>
-  <si>
-    <t>等级礼包(网页竖版)</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>playerLevel(30)</t>
-  </si>
-  <si>
-    <t>djlb-3</t>
-  </si>
-  <si>
-    <t>btn_level_gift</t>
-  </si>
-  <si>
-    <t>每日充值(网页竖版)</t>
-  </si>
-  <si>
-    <t>qtlc-6</t>
-  </si>
-  <si>
-    <t>btn_first_daily</t>
-  </si>
-  <si>
-    <t>每日奖金(网页竖版)</t>
-  </si>
-  <si>
-    <t>mrjj-5</t>
-  </si>
-  <si>
-    <t>btn_privilege</t>
-  </si>
-  <si>
-    <t>储钱罐(网页竖版)</t>
-  </si>
-  <si>
-    <t>cqg-1</t>
-  </si>
-  <si>
-    <t>btn_pig</t>
-  </si>
-  <si>
-    <t>成长基金(网页竖版)</t>
-  </si>
-  <si>
-    <t>czjj-2</t>
-  </si>
-  <si>
-    <t>btn_growth_fund</t>
-  </si>
-  <si>
-    <t>刮刮乐(网页竖版)</t>
-  </si>
-  <si>
-    <t>ggk-4</t>
-  </si>
-  <si>
-    <t>btn_lottery</t>
-  </si>
-  <si>
-    <t>聊天(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_chat</t>
-  </si>
-  <si>
-    <t>显示位置：模拟经营大厅</t>
-  </si>
-  <si>
-    <t>好友(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_friend</t>
-  </si>
-  <si>
-    <t>雇员\游客抽卡(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_zm</t>
-  </si>
-  <si>
-    <t>联盟(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_lm</t>
   </si>
   <si>
     <t>赛季(app竖版)</t>
@@ -2444,10 +2444,10 @@
         <v>37</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="L13" s="1" t="b">
         <v>1</v>
@@ -2468,10 +2468,10 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
@@ -2508,10 +2508,10 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="7">
@@ -2546,10 +2546,10 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -2559,13 +2559,13 @@
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
@@ -2588,10 +2588,10 @@
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="F17" s="4">
         <v>2</v>
@@ -2603,10 +2603,10 @@
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L17" s="1" t="b">
         <v>1</v>
@@ -2626,10 +2626,10 @@
         <v>5</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="F18" s="4">
         <v>9</v>
@@ -2641,10 +2641,10 @@
         <v>37</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L18" s="1" t="b">
         <v>1</v>
@@ -2664,10 +2664,10 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="F19" s="4">
         <v>3</v>
@@ -2679,10 +2679,10 @@
         <v>37</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L19" s="1" t="b">
         <v>1</v>
@@ -2699,10 +2699,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="F20" s="4">
         <v>6</v>
@@ -2737,10 +2737,10 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="F21" s="2">
         <v>7</v>
@@ -2753,10 +2753,10 @@
         <v>41</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
@@ -2779,10 +2779,10 @@
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F22" s="2">
         <v>8</v>
@@ -2792,13 +2792,13 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
@@ -2821,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F23" s="4">
         <v>11</v>
@@ -2856,10 +2856,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F24" s="4">
         <v>12</v>
@@ -2892,10 +2892,10 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="F25" s="2">
         <v>13</v>
@@ -2931,10 +2931,10 @@
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="F26" s="4">
         <v>14</v>
@@ -2952,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2963,10 +2963,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="F27" s="4">
         <v>15</v>
@@ -2999,10 +2999,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
@@ -3012,13 +3012,13 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="K28" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
@@ -3036,10 +3036,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="16" t="s">
         <v>103</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>104</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
@@ -3073,10 +3073,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="16" t="s">
         <v>105</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>106</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
@@ -3086,13 +3086,13 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="K30" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
@@ -3110,10 +3110,10 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>108</v>
       </c>
       <c r="F31" s="4">
         <v>19</v>
@@ -3147,10 +3147,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="16" t="s">
         <v>109</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>110</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
@@ -3160,13 +3160,13 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="K32" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
@@ -3184,10 +3184,10 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>111</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>112</v>
       </c>
       <c r="F33" s="2">
         <v>21</v>
@@ -3197,13 +3197,13 @@
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J33" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="K33" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
@@ -3220,10 +3220,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="16" t="s">
         <v>113</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>114</v>
       </c>
       <c r="F34" s="2">
         <v>22</v>
@@ -3257,10 +3257,10 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2">
@@ -3331,7 +3331,7 @@
         <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>37</v>
@@ -3355,10 +3355,10 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="F38" s="2">
         <v>24</v>
@@ -3388,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="F39" s="4">
         <v>25</v>
@@ -3424,10 +3424,10 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F40" s="2">
         <v>26</v>
@@ -3459,7 +3459,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -3471,10 +3471,10 @@
         <v>37</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L41" s="2" t="b">
         <v>0</v>
@@ -3493,7 +3493,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -3527,7 +3527,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -3559,7 +3559,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -3591,10 +3591,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="7">
@@ -3605,10 +3605,10 @@
         <v>37</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L45" s="1" t="b">
         <v>1</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -3652,7 +3652,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>46</v>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -3690,7 +3690,7 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>46</v>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3728,7 +3728,7 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>46</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -3766,7 +3766,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>46</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -3804,7 +3804,7 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>46</v>
@@ -3821,7 +3821,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -3833,20 +3833,20 @@
         <v>41</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O51" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>46</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -3870,23 +3870,23 @@
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="J52" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="K52" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="O52" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="O52" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>39</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E53" s="16"/>
       <c r="F53" s="2"/>
@@ -3923,10 +3923,10 @@
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="O53" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>46</v>
@@ -3943,7 +3943,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -3965,10 +3965,10 @@
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="O54" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>46</v>
@@ -3985,7 +3985,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -4007,10 +4007,10 @@
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="O55" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>39</v>
@@ -4027,7 +4027,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -4036,23 +4036,23 @@
       </c>
       <c r="H56" s="14"/>
       <c r="I56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J56" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="K56" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="O56" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>46</v>
@@ -4069,7 +4069,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -4091,10 +4091,10 @@
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="O57" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>39</v>
@@ -4109,10 +4109,10 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="7">
@@ -4123,10 +4123,10 @@
         <v>37</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L58" s="1" t="b">
         <v>1</v>
@@ -4135,7 +4135,7 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4146,10 +4146,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="G59" s="7">
         <v>3</v>
@@ -4158,16 +4158,16 @@
         <v>37</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L59" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4178,10 +4178,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="G60" s="7">
         <v>5</v>
@@ -4190,10 +4190,10 @@
         <v>37</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L60" s="1" t="b">
         <v>1</v>
@@ -4202,7 +4202,7 @@
         <v>4062001</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4213,10 +4213,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="G61" s="7">
         <v>5</v>
@@ -4225,10 +4225,10 @@
         <v>37</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="L61" s="1" t="b">
         <v>1</v>
@@ -4237,7 +4237,7 @@
         <v>4062002</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4272,7 +4272,7 @@
         <v>4062004</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4304,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4336,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4368,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -522,6 +522,9 @@
     <t>btn_mail</t>
   </si>
   <si>
+    <t>simAllLevel(5)</t>
+  </si>
+  <si>
     <t>幸运夺宝(横版app版)</t>
   </si>
   <si>
@@ -570,15 +573,15 @@
     <t>Grid (11)</t>
   </si>
   <si>
-    <t>simAllLevel(5)</t>
-  </si>
-  <si>
     <t>等级礼包(app竖版)</t>
   </si>
   <si>
     <t>btn_levelGift</t>
   </si>
   <si>
+    <t>simAllLevel(3)</t>
+  </si>
+  <si>
     <t>首充礼包(横版app版)</t>
   </si>
   <si>
@@ -883,9 +886,6 @@
   </si>
   <si>
     <t>Grid (42)</t>
-  </si>
-  <si>
-    <t>simAllLevel(15)</t>
   </si>
   <si>
     <t>拜访(app竖版)</t>
@@ -2444,10 +2444,10 @@
         <v>37</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="L13" s="1" t="b">
         <v>1</v>
@@ -2468,10 +2468,10 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
@@ -2508,10 +2508,10 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="7">
@@ -2546,10 +2546,10 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -2559,13 +2559,13 @@
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
@@ -2588,10 +2588,10 @@
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" s="4">
         <v>2</v>
@@ -2603,10 +2603,10 @@
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L17" s="1" t="b">
         <v>1</v>
@@ -2626,10 +2626,10 @@
         <v>5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" s="4">
         <v>9</v>
@@ -2641,10 +2641,10 @@
         <v>37</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L18" s="1" t="b">
         <v>1</v>
@@ -2664,10 +2664,10 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" s="4">
         <v>3</v>
@@ -2679,10 +2679,10 @@
         <v>37</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="L19" s="1" t="b">
         <v>1</v>
@@ -2714,10 +2714,10 @@
         <v>37</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="L20" s="1" t="b">
         <v>1</v>
@@ -2737,10 +2737,10 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2">
         <v>7</v>
@@ -2753,10 +2753,10 @@
         <v>41</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
@@ -2779,10 +2779,10 @@
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F22" s="2">
         <v>8</v>
@@ -2792,13 +2792,13 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
@@ -2821,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="4">
         <v>11</v>
@@ -2836,10 +2836,10 @@
         <v>37</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="L23" s="1" t="b">
         <v>1</v>
@@ -2856,10 +2856,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F24" s="4">
         <v>12</v>
@@ -2892,10 +2892,10 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2">
         <v>13</v>
@@ -2931,10 +2931,10 @@
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F26" s="4">
         <v>14</v>
@@ -2952,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2963,10 +2963,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F27" s="4">
         <v>15</v>
@@ -2999,10 +2999,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
@@ -3012,13 +3012,13 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
@@ -3036,10 +3036,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
@@ -3073,10 +3073,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
@@ -3086,13 +3086,13 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
@@ -3110,10 +3110,10 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F31" s="4">
         <v>19</v>
@@ -3126,10 +3126,10 @@
         <v>37</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="L31" s="1" t="b">
         <v>1</v>
@@ -3147,10 +3147,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
@@ -3160,13 +3160,13 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
@@ -3184,10 +3184,10 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F33" s="2">
         <v>21</v>
@@ -3197,13 +3197,13 @@
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
@@ -3220,10 +3220,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F34" s="2">
         <v>22</v>
@@ -3257,10 +3257,10 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2">
@@ -3331,7 +3331,7 @@
         <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>37</v>
@@ -3355,10 +3355,10 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2">
         <v>24</v>
@@ -3388,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F39" s="4">
         <v>25</v>
@@ -3424,10 +3424,10 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F40" s="2">
         <v>26</v>
@@ -3459,7 +3459,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -3471,10 +3471,10 @@
         <v>37</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L41" s="2" t="b">
         <v>0</v>
@@ -3493,7 +3493,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -3527,7 +3527,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -3559,7 +3559,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -3591,10 +3591,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="7">
@@ -3605,10 +3605,10 @@
         <v>37</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L45" s="1" t="b">
         <v>1</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -3652,7 +3652,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>46</v>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -3690,7 +3690,7 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>46</v>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3728,7 +3728,7 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>46</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -3766,7 +3766,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>46</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -3804,7 +3804,7 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>46</v>
@@ -3821,7 +3821,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -3833,20 +3833,20 @@
         <v>41</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>46</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -3870,23 +3870,23 @@
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>39</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E53" s="16"/>
       <c r="F53" s="2"/>
@@ -3923,10 +3923,10 @@
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>46</v>
@@ -3943,7 +3943,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -3965,10 +3965,10 @@
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>46</v>
@@ -3985,7 +3985,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -4007,10 +4007,10 @@
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>39</v>
@@ -4027,7 +4027,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -4036,23 +4036,23 @@
       </c>
       <c r="H56" s="14"/>
       <c r="I56" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>46</v>
@@ -4069,7 +4069,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -4091,10 +4091,10 @@
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>39</v>
@@ -4109,10 +4109,10 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="7">
@@ -4123,10 +4123,10 @@
         <v>37</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="L58" s="1" t="b">
         <v>1</v>
@@ -4135,7 +4135,7 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4146,10 +4146,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G59" s="7">
         <v>3</v>
@@ -4158,16 +4158,16 @@
         <v>37</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="L59" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4178,10 +4178,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G60" s="7">
         <v>5</v>
@@ -4190,10 +4190,10 @@
         <v>37</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L60" s="1" t="b">
         <v>1</v>
@@ -4202,7 +4202,7 @@
         <v>4062001</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4213,10 +4213,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G61" s="7">
         <v>5</v>
@@ -4225,10 +4225,10 @@
         <v>37</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L61" s="1" t="b">
         <v>1</v>
@@ -4237,7 +4237,7 @@
         <v>4062002</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4248,10 +4248,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G62" s="7">
         <v>5</v>
@@ -4260,10 +4260,10 @@
         <v>37</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L62" s="1" t="b">
         <v>1</v>
@@ -4272,7 +4272,7 @@
         <v>4062004</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4283,10 +4283,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G63" s="7">
         <v>5</v>
@@ -4304,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4315,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G64" s="7">
         <v>2</v>
@@ -4327,16 +4327,16 @@
         <v>37</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4359,16 +4359,16 @@
         <v>37</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L65" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="189">
   <si>
     <t>id</t>
   </si>
@@ -892,6 +892,18 @@
   </si>
   <si>
     <t>btn_randomvisit</t>
+  </si>
+  <si>
+    <t>广告福利</t>
+  </si>
+  <si>
+    <t>btn_lookads</t>
+  </si>
+  <si>
+    <t>合集礼包</t>
+  </si>
+  <si>
+    <t>BundleGiftPack</t>
   </si>
 </sst>
 </file>
@@ -1954,7 +1966,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -4370,6 +4382,67 @@
       <c r="P65" s="4" t="s">
         <v>168</v>
       </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="4">
+        <v>5008</v>
+      </c>
+      <c r="B66" s="4">
+        <v>1</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G66" s="7">
+        <v>4</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L66" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="4">
+        <v>5009</v>
+      </c>
+      <c r="B67" s="4">
+        <v>1</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G67" s="7">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L67" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="L68" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E65">

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -328,7 +328,10 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-游戏中，【左侧列表】不能打开对应界面时的提示</t>
+游戏中，【左侧列表】不能打开对应界面时的提示
+0参数：表示  提示不做处理。直接读取多语言表中ID显示
+2参数：表示  任务表中的“任务”类型，计算任务数量
+暂只设计了  参数2的任务类型</t>
         </r>
       </text>
     </comment>
@@ -337,7 +340,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="191">
   <si>
     <t>id</t>
   </si>
@@ -525,6 +528,9 @@
     <t>simAllLevel(5)</t>
   </si>
   <si>
+    <t>0_4062005</t>
+  </si>
+  <si>
     <t>幸运夺宝(横版app版)</t>
   </si>
   <si>
@@ -856,6 +862,9 @@
   </si>
   <si>
     <t>btn_zm</t>
+  </si>
+  <si>
+    <t>2_4062008</t>
   </si>
   <si>
     <t>联盟(app竖版)</t>
@@ -916,7 +925,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,12 +970,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1115,12 +1118,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1452,137 +1455,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1642,9 +1645,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2072,7 +2072,7 @@
         <v>19</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N2" s="10" t="s">
         <v>16</v>
@@ -2453,7 +2453,7 @@
         <v>5</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>61</v>
@@ -2464,8 +2464,8 @@
       <c r="L13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M13" s="4">
-        <v>4062005</v>
+      <c r="M13" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="P13" s="4" t="s">
         <v>46</v>
@@ -2480,10 +2480,10 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
@@ -2520,10 +2520,10 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="7">
@@ -2558,10 +2558,10 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -2571,13 +2571,13 @@
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" s="4">
         <v>2</v>
@@ -2615,10 +2615,10 @@
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L17" s="1" t="b">
         <v>1</v>
@@ -2638,10 +2638,10 @@
         <v>5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" s="4">
         <v>9</v>
@@ -2653,10 +2653,10 @@
         <v>37</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L18" s="1" t="b">
         <v>1</v>
@@ -2676,10 +2676,10 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" s="4">
         <v>3</v>
@@ -2711,10 +2711,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="4">
         <v>6</v>
@@ -2726,10 +2726,10 @@
         <v>37</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L20" s="1" t="b">
         <v>1</v>
@@ -2749,10 +2749,10 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2">
         <v>7</v>
@@ -2765,10 +2765,10 @@
         <v>41</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2">
         <v>8</v>
@@ -2804,13 +2804,13 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
@@ -2833,10 +2833,10 @@
         <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="4">
         <v>11</v>
@@ -2848,10 +2848,10 @@
         <v>37</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L23" s="1" t="b">
         <v>1</v>
@@ -2868,10 +2868,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="4">
         <v>12</v>
@@ -2904,10 +2904,10 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="2">
         <v>13</v>
@@ -2943,10 +2943,10 @@
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" s="4">
         <v>14</v>
@@ -2964,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2975,10 +2975,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F27" s="4">
         <v>15</v>
@@ -3011,10 +3011,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
@@ -3024,13 +3024,13 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
@@ -3048,10 +3048,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" s="2">
         <v>17</v>
@@ -3085,10 +3085,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
@@ -3098,13 +3098,13 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
@@ -3122,10 +3122,10 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F31" s="4">
         <v>19</v>
@@ -3159,10 +3159,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F32" s="2">
         <v>20</v>
@@ -3172,13 +3172,13 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
@@ -3196,10 +3196,10 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F33" s="2">
         <v>21</v>
@@ -3209,13 +3209,13 @@
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
@@ -3232,10 +3232,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F34" s="2">
         <v>22</v>
@@ -3269,10 +3269,10 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2">
@@ -3343,7 +3343,7 @@
         <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>37</v>
@@ -3367,10 +3367,10 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F38" s="2">
         <v>24</v>
@@ -3400,10 +3400,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F39" s="4">
         <v>25</v>
@@ -3436,10 +3436,10 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2">
         <v>26</v>
@@ -3471,7 +3471,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -3483,10 +3483,10 @@
         <v>37</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L41" s="2" t="b">
         <v>0</v>
@@ -3505,7 +3505,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -3539,7 +3539,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -3571,7 +3571,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -3603,10 +3603,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="7">
@@ -3617,10 +3617,10 @@
         <v>37</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L45" s="1" t="b">
         <v>1</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -3664,7 +3664,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>46</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -3702,7 +3702,7 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>46</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3740,7 +3740,7 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>46</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -3778,7 +3778,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>46</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -3816,7 +3816,7 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>46</v>
@@ -3833,7 +3833,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -3845,20 +3845,20 @@
         <v>41</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>46</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -3882,23 +3882,23 @@
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>39</v>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E53" s="16"/>
       <c r="F53" s="2"/>
@@ -3935,10 +3935,10 @@
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>46</v>
@@ -3955,7 +3955,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -3977,10 +3977,10 @@
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>46</v>
@@ -3997,7 +3997,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -4019,10 +4019,10 @@
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>39</v>
@@ -4039,7 +4039,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -4048,23 +4048,23 @@
       </c>
       <c r="H56" s="14"/>
       <c r="I56" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>46</v>
@@ -4081,7 +4081,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -4103,10 +4103,10 @@
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>39</v>
@@ -4121,10 +4121,10 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="7">
@@ -4147,7 +4147,7 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4158,10 +4158,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G59" s="7">
         <v>3</v>
@@ -4179,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4190,10 +4190,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G60" s="7">
         <v>5</v>
@@ -4202,19 +4202,19 @@
         <v>37</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L60" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M60" s="4">
-        <v>4062001</v>
+      <c r="M60" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4225,10 +4225,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G61" s="7">
         <v>5</v>
@@ -4237,19 +4237,19 @@
         <v>37</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L61" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M61" s="20">
-        <v>4062002</v>
+      <c r="M61" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4260,10 +4260,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G62" s="7">
         <v>5</v>
@@ -4272,19 +4272,19 @@
         <v>37</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L62" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M62" s="20">
-        <v>4062004</v>
+      <c r="M62" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4295,10 +4295,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G63" s="7">
         <v>5</v>
@@ -4315,8 +4315,9 @@
       <c r="L63" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="M63" s="4"/>
       <c r="P63" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4327,10 +4328,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G64" s="7">
         <v>2</v>
@@ -4339,16 +4340,16 @@
         <v>37</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4359,10 +4360,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G65" s="7">
         <v>3</v>
@@ -4371,16 +4372,16 @@
         <v>37</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L65" s="1" t="b">
         <v>1</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4391,10 +4392,10 @@
         <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G66" s="7">
         <v>4</v>
@@ -4420,10 +4421,10 @@
         <v>1</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G67" s="7">
         <v>1</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -261,6 +261,15 @@
 注：如果是活动的话，则需要和 ActivityConfig.xlsx  中的开启条件保持一致
 </t>
         </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>simalllevel为当前所有场景的等级之和；（比如游戏有两个场景，场景1为50级，场景2为15级，则simALLlevel就为50+15=65级</t>
+        </r>
       </text>
     </comment>
     <comment ref="K1" authorId="0">
@@ -1118,12 +1127,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4315,7 +4324,6 @@
       <c r="L63" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M63" s="4"/>
       <c r="P63" s="4" t="s">
         <v>169</v>
       </c>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -130,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -153,7 +153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -213,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -238,7 +238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -272,7 +272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -297,7 +297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -319,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="197">
   <si>
     <t>id</t>
   </si>
@@ -366,6 +366,9 @@
     <t>对应按钮节点</t>
   </si>
   <si>
+    <t>多语言ID</t>
+  </si>
+  <si>
     <t>显示顺序</t>
   </si>
   <si>
@@ -420,6 +423,9 @@
     <t>functionNodeName</t>
   </si>
   <si>
+    <t>nameid</t>
+  </si>
+  <si>
     <t>serialNumber</t>
   </si>
   <si>
@@ -922,6 +928,18 @@
   </si>
   <si>
     <t>BundleGiftPack</t>
+  </si>
+  <si>
+    <t>运营数据(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_operationaldata</t>
+  </si>
+  <si>
+    <t>快速获取资源(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_getresources</t>
   </si>
 </sst>
 </file>
@@ -934,7 +952,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -974,6 +992,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1464,137 +1488,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1640,6 +1664,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1649,7 +1676,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1707,7 +1734,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1975,7 +2009,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -1983,19 +2017,19 @@
     <col min="3" max="3" width="14.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="23.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="19.7" style="7" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="36.6083333333333" style="4" customWidth="1"/>
-    <col min="11" max="11" width="40.375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="4" customWidth="1"/>
-    <col min="13" max="15" width="11.9083333333333" style="4" customWidth="1"/>
-    <col min="16" max="16" width="26" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="4"/>
+    <col min="6" max="7" width="14.625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="19.7" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="36.6083333333333" style="4" customWidth="1"/>
+    <col min="12" max="12" width="40.375" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.875" style="4" customWidth="1"/>
+    <col min="14" max="16" width="11.9083333333333" style="4" customWidth="1"/>
+    <col min="17" max="17" width="26" style="4" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2014,23 +2048,23 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="8" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>11</v>
@@ -2041,162 +2075,171 @@
       <c r="O1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:17">
       <c r="A2" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="8" t="s">
+      <c r="L2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="8" t="s">
+      <c r="O2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:16">
+      <c r="P2" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:17">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="G3" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="H3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>27</v>
       </c>
+      <c r="J3" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="K3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="L3" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="M3" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>33</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="12"/>
-      <c r="I4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>34</v>
+      <c r="I4" s="12"/>
+      <c r="J4" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>36</v>
+      </c>
       <c r="M4" s="11"/>
-      <c r="N4" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="N4" s="11"/>
       <c r="O4" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:16">
+        <v>35</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:17">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="14"/>
       <c r="J5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:16">
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:17">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -2205,34 +2248,33 @@
         <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="H6" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="14"/>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="2" t="b">
+        <v>44</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:16">
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:17">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -2243,33 +2285,32 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="14">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="H7" s="14">
+        <v>1</v>
+      </c>
+      <c r="I7" s="14"/>
       <c r="J7" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="2" t="b">
+        <v>47</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:16">
+      <c r="Q7" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:17">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -2278,38 +2319,38 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="2">
+        <v>50</v>
+      </c>
+      <c r="G8" s="2">
         <v>5</v>
       </c>
-      <c r="G8" s="14">
-        <v>1</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H8" s="14">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14"/>
       <c r="J8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:16">
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:17">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -2320,167 +2361,170 @@
         <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="14">
-        <v>1</v>
-      </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="H9" s="14">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:16">
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:17">
       <c r="A10" s="2">
         <v>6</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="14">
-        <v>1</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="H10" s="14">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14"/>
       <c r="J10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="4">
         <v>7</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="7">
+        <v>56</v>
+      </c>
+      <c r="F11" s="4">
+        <v>4056036</v>
+      </c>
+      <c r="H11" s="7">
         <v>2</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J11" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:17">
       <c r="A12" s="2">
         <v>8</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="14">
-        <v>1</v>
-      </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="H12" s="14">
+        <v>1</v>
+      </c>
+      <c r="I12" s="14"/>
       <c r="J12" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12" s="2" t="b">
+        <v>59</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="7">
+        <v>62</v>
+      </c>
+      <c r="F13" s="15">
+        <v>10019</v>
+      </c>
+      <c r="H13" s="7">
         <v>5</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J13" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:16">
+        <v>63</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:17">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -2489,38 +2533,38 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="2">
+        <v>66</v>
+      </c>
+      <c r="G14" s="2">
         <v>4</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="2" t="b">
+      <c r="H14" s="14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="1:16">
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="1:17">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -2529,36 +2573,37 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F15" s="4"/>
-      <c r="G15" s="7">
+      <c r="G15" s="4"/>
+      <c r="H15" s="7">
         <v>2</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="I15" s="7"/>
       <c r="J15" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:16">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:17">
       <c r="A16" s="2">
         <v>101</v>
       </c>
@@ -2567,38 +2612,38 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1</v>
-      </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L16" s="2" t="b">
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="14">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="4">
         <v>102</v>
       </c>
@@ -2609,34 +2654,34 @@
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="4">
+        <v>74</v>
+      </c>
+      <c r="G17" s="4">
         <v>2</v>
       </c>
-      <c r="G17" s="7">
-        <v>1</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>37</v>
+      <c r="H17" s="7">
+        <v>1</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="L17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>75</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="4">
         <v>103</v>
       </c>
@@ -2647,34 +2692,34 @@
         <v>5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="4">
+        <v>77</v>
+      </c>
+      <c r="G18" s="4">
         <v>9</v>
       </c>
-      <c r="G18" s="7">
-        <v>1</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>37</v>
+      <c r="H18" s="7">
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>78</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="M18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="4">
         <v>104</v>
       </c>
@@ -2685,34 +2730,34 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="4">
+        <v>80</v>
+      </c>
+      <c r="G19" s="4">
         <v>3</v>
       </c>
-      <c r="G19" s="7">
-        <v>1</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>37</v>
+      <c r="H19" s="7">
+        <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>63</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="4">
         <v>105</v>
       </c>
@@ -2720,34 +2765,34 @@
         <v>1</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="4">
+        <v>82</v>
+      </c>
+      <c r="G20" s="4">
         <v>6</v>
       </c>
-      <c r="G20" s="7">
+      <c r="H20" s="7">
         <v>4</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J20" s="4" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:16">
+        <v>83</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:17">
       <c r="A21" s="2">
         <v>106</v>
       </c>
@@ -2758,38 +2803,38 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="2">
+        <v>85</v>
+      </c>
+      <c r="G21" s="2">
         <v>7</v>
       </c>
-      <c r="G21" s="14">
-        <v>1</v>
-      </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="H21" s="14">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14"/>
       <c r="J21" s="2" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L21" s="2" t="b">
+        <v>86</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M21" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:16">
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:17">
       <c r="A22" s="2">
         <v>107</v>
       </c>
@@ -2800,38 +2845,38 @@
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="2">
+        <v>88</v>
+      </c>
+      <c r="G22" s="2">
         <v>8</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="H22" s="14">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14"/>
       <c r="J22" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22" s="2" t="b">
+        <v>90</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M22" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="4">
         <v>108</v>
       </c>
@@ -2842,34 +2887,34 @@
         <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="4">
+        <v>92</v>
+      </c>
+      <c r="G23" s="4">
         <v>11</v>
       </c>
-      <c r="G23" s="7">
-        <v>1</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>37</v>
+      <c r="H23" s="7">
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="L23" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>83</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="4">
         <v>109</v>
       </c>
@@ -2877,34 +2922,34 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" s="4">
+        <v>94</v>
+      </c>
+      <c r="G24" s="4">
         <v>12</v>
       </c>
-      <c r="G24" s="7">
+      <c r="H24" s="7">
         <v>2</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J24" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L24" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:17">
       <c r="A25" s="2">
         <v>110</v>
       </c>
@@ -2913,38 +2958,38 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="2">
+        <v>96</v>
+      </c>
+      <c r="G25" s="2">
         <v>13</v>
       </c>
-      <c r="G25" s="14">
-        <v>1</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H25" s="14">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14"/>
       <c r="J25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M25" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="4">
         <v>111</v>
       </c>
@@ -2952,31 +2997,31 @@
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="4">
+        <v>98</v>
+      </c>
+      <c r="G26" s="4">
         <v>14</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J26" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="4">
         <v>112</v>
       </c>
@@ -2984,34 +3029,34 @@
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" s="4">
+        <v>101</v>
+      </c>
+      <c r="G27" s="4">
         <v>15</v>
       </c>
-      <c r="G27" s="7">
+      <c r="H27" s="7">
         <v>2</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J27" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L27" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:17">
       <c r="A28" s="2">
         <v>113</v>
       </c>
@@ -3020,35 +3065,35 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F28" s="2">
+        <v>103</v>
+      </c>
+      <c r="G28" s="2">
         <v>16</v>
       </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="H28" s="14">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14"/>
       <c r="J28" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L28" s="2" t="b">
+        <v>105</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:16">
+      <c r="Q28" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:17">
       <c r="A29" s="2">
         <v>114</v>
       </c>
@@ -3057,35 +3102,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="F29" s="2">
+        <v>106</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="2">
         <v>17</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H29" s="14">
+        <v>1</v>
+      </c>
+      <c r="I29" s="14"/>
       <c r="J29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L29" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:16">
+      <c r="Q29" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:17">
       <c r="A30" s="2">
         <v>115</v>
       </c>
@@ -3094,35 +3139,35 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" s="2">
+        <v>108</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="2">
         <v>18</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="H30" s="14">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14"/>
       <c r="J30" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L30" s="2" t="b">
+        <v>105</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" s="4" customFormat="1" spans="1:16">
+      <c r="Q30" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" s="4" customFormat="1" spans="1:17">
       <c r="A31" s="4">
         <v>116</v>
       </c>
@@ -3131,35 +3176,35 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="4">
+        <v>110</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="4">
         <v>19</v>
       </c>
-      <c r="G31" s="7">
-        <v>1</v>
-      </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="H31" s="7">
+        <v>1</v>
+      </c>
+      <c r="I31" s="7"/>
       <c r="J31" s="4" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L31" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:16">
+        <v>63</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:17">
       <c r="A32" s="2">
         <v>117</v>
       </c>
@@ -3168,35 +3213,35 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="2">
+        <v>112</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32" s="2">
         <v>20</v>
       </c>
-      <c r="G32" s="14">
-        <v>1</v>
-      </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="H32" s="14">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14"/>
       <c r="J32" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L32" s="2" t="b">
+        <v>105</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:16">
+      <c r="Q32" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" spans="1:17">
       <c r="A33" s="2">
         <v>118</v>
       </c>
@@ -3205,35 +3250,35 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="2">
+        <v>114</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="2">
         <v>21</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="H33" s="14">
+        <v>1</v>
+      </c>
+      <c r="I33" s="14"/>
       <c r="J33" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L33" s="2" t="b">
+        <v>105</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:16">
+      <c r="Q33" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" spans="1:17">
       <c r="A34" s="2">
         <v>119</v>
       </c>
@@ -3241,35 +3286,35 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34" s="2">
+        <v>116</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G34" s="2">
         <v>22</v>
       </c>
-      <c r="G34" s="14">
-        <v>1</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H34" s="14">
+        <v>1</v>
+      </c>
+      <c r="I34" s="14"/>
       <c r="J34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M34" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:16">
+      <c r="Q34" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="1:17">
       <c r="A35" s="2">
         <v>120</v>
       </c>
@@ -3278,38 +3323,38 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F35" s="2">
+        <v>119</v>
+      </c>
+      <c r="G35" s="2">
         <v>10</v>
       </c>
-      <c r="G35" s="14">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H35" s="14">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L35" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:16">
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:17">
       <c r="A36" s="2">
         <v>121</v>
       </c>
@@ -3318,56 +3363,56 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="2">
+      <c r="G36" s="2">
         <v>23</v>
       </c>
-      <c r="G36" s="14">
-        <v>1</v>
-      </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H36" s="14">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14"/>
       <c r="J36" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M36" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
-      <c r="P36" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="4">
         <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L37" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M37" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="1:17">
       <c r="A38" s="2">
         <v>123</v>
       </c>
@@ -3376,32 +3421,32 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F38" s="2">
+        <v>123</v>
+      </c>
+      <c r="G38" s="2">
         <v>24</v>
       </c>
-      <c r="G38" s="14">
-        <v>1</v>
-      </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H38" s="14">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14"/>
       <c r="J38" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L38" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M38" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:17">
       <c r="A39" s="4">
         <v>124</v>
       </c>
@@ -3409,34 +3454,34 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F39" s="4">
+        <v>125</v>
+      </c>
+      <c r="G39" s="4">
         <v>25</v>
       </c>
-      <c r="G39" s="7">
+      <c r="H39" s="7">
         <v>2</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J39" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L39" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" spans="1:17">
       <c r="A40" s="2">
         <v>125</v>
       </c>
@@ -3445,203 +3490,208 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" s="2">
+        <v>127</v>
+      </c>
+      <c r="G40" s="2">
         <v>26</v>
       </c>
-      <c r="G40" s="14">
-        <v>1</v>
-      </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H40" s="14">
+        <v>1</v>
+      </c>
+      <c r="I40" s="14"/>
       <c r="J40" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L40" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M40" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P40" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" s="5" customFormat="1" spans="1:16">
+      <c r="Q40" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" s="5" customFormat="1" spans="1:17">
       <c r="A41" s="2">
         <v>126</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I41" s="14"/>
       <c r="J41" s="2" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="L41" s="2" t="b">
+        <v>129</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M41" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
-      <c r="P41" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" s="5" customFormat="1" spans="1:16">
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" s="5" customFormat="1" spans="1:17">
       <c r="A42" s="2">
         <v>127</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="14">
-        <v>1</v>
-      </c>
-      <c r="H42" s="14"/>
-      <c r="I42" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="14">
+        <v>1</v>
+      </c>
+      <c r="I42" s="14"/>
       <c r="J42" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M42" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
-      <c r="P42" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" s="5" customFormat="1" spans="1:16">
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" s="5" customFormat="1" spans="1:17">
       <c r="A43" s="2">
         <v>128</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="14">
-        <v>1</v>
-      </c>
-      <c r="H43" s="14"/>
-      <c r="I43" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="14">
+        <v>1</v>
+      </c>
+      <c r="I43" s="14"/>
       <c r="J43" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L43" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M43" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
-    </row>
-    <row r="44" s="5" customFormat="1" spans="1:16">
+      <c r="Q43" s="2"/>
+    </row>
+    <row r="44" s="5" customFormat="1" spans="1:17">
       <c r="A44" s="2">
         <v>129</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="14">
-        <v>1</v>
-      </c>
-      <c r="H44" s="14"/>
-      <c r="I44" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="14">
+        <v>1</v>
+      </c>
+      <c r="I44" s="14"/>
       <c r="J44" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L44" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M44" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
-    </row>
-    <row r="45" s="3" customFormat="1" spans="1:16">
+      <c r="Q44" s="2"/>
+    </row>
+    <row r="45" s="3" customFormat="1" spans="1:17">
       <c r="A45" s="4">
         <v>130</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F45" s="4"/>
-      <c r="G45" s="7">
+      <c r="G45" s="4"/>
+      <c r="H45" s="7">
         <v>4</v>
       </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="I45" s="7"/>
       <c r="J45" s="4" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="L45" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M45" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" s="5" customFormat="1" spans="1:16">
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" s="5" customFormat="1" spans="1:17">
       <c r="A46" s="2">
         <v>1001</v>
       </c>
@@ -3650,36 +3700,37 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="14">
+      <c r="G46" s="2"/>
+      <c r="H46" s="14">
         <v>5</v>
       </c>
-      <c r="H46" s="14"/>
-      <c r="I46" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I46" s="14"/>
       <c r="J46" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L46" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M46" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" s="5" customFormat="1" spans="1:16">
+        <v>137</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" s="5" customFormat="1" spans="1:17">
       <c r="A47" s="2">
         <v>1002</v>
       </c>
@@ -3688,36 +3739,37 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="14">
+      <c r="G47" s="2"/>
+      <c r="H47" s="14">
         <v>5</v>
       </c>
-      <c r="H47" s="14"/>
-      <c r="I47" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I47" s="14"/>
       <c r="J47" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M47" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
-      <c r="O47" s="2" t="s">
-        <v>137</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" s="5" customFormat="1" spans="1:16">
+        <v>139</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" s="5" customFormat="1" spans="1:17">
       <c r="A48" s="2">
         <v>1003</v>
       </c>
@@ -3726,36 +3778,37 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="14">
+      <c r="G48" s="2"/>
+      <c r="H48" s="14">
         <v>5</v>
       </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I48" s="14"/>
       <c r="J48" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L48" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" s="6" customFormat="1" spans="1:16">
+        <v>141</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" s="6" customFormat="1" spans="1:17">
       <c r="A49" s="6">
         <v>1004</v>
       </c>
@@ -3764,36 +3817,35 @@
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="19">
+      <c r="H49" s="20">
         <v>5</v>
       </c>
-      <c r="H49" s="19"/>
-      <c r="I49" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="I49" s="20"/>
       <c r="J49" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M49" s="6"/>
       <c r="N49" s="6"/>
-      <c r="O49" s="6" t="s">
-        <v>141</v>
-      </c>
+      <c r="O49" s="6"/>
       <c r="P49" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" s="6" customFormat="1" spans="1:16">
+        <v>143</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" s="6" customFormat="1" spans="1:17">
       <c r="A50" s="6">
         <v>1005</v>
       </c>
@@ -3802,36 +3854,35 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="19">
+      <c r="H50" s="20">
         <v>5</v>
       </c>
-      <c r="H50" s="19"/>
-      <c r="I50" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="I50" s="20"/>
       <c r="J50" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L50" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M50" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M50" s="6"/>
       <c r="N50" s="6"/>
-      <c r="O50" s="6" t="s">
-        <v>143</v>
-      </c>
+      <c r="O50" s="6"/>
       <c r="P50" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" s="5" customFormat="1" spans="1:16">
+        <v>145</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" s="5" customFormat="1" spans="1:17">
       <c r="A51" s="2">
         <v>2001</v>
       </c>
@@ -3842,38 +3893,39 @@
         <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="14">
+      <c r="G51" s="2"/>
+      <c r="H51" s="14">
         <v>4</v>
       </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="I51" s="14"/>
       <c r="J51" s="2" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L51" s="2" t="b">
+        <v>86</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M51" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" s="5" customFormat="1" spans="1:16">
+        <v>148</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" s="5" customFormat="1" spans="1:17">
       <c r="A52" s="2">
         <v>2002</v>
       </c>
@@ -3882,38 +3934,39 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="14">
+      <c r="G52" s="2"/>
+      <c r="H52" s="14">
         <v>4</v>
       </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="2" t="s">
-        <v>148</v>
-      </c>
+      <c r="I52" s="14"/>
       <c r="J52" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L52" s="2" t="b">
+        <v>151</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="M52" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" s="5" customFormat="1" spans="1:16">
+        <v>153</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" s="5" customFormat="1" spans="1:17">
       <c r="A53" s="2">
         <v>2003</v>
       </c>
@@ -3922,38 +3975,39 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" s="16"/>
+        <v>154</v>
+      </c>
+      <c r="E53" s="17"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="14">
+      <c r="G53" s="2"/>
+      <c r="H53" s="14">
         <v>4</v>
       </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I53" s="14"/>
       <c r="J53" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L53" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M53" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2" t="s">
-        <v>153</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" s="5" customFormat="1" spans="1:16">
+        <v>156</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" s="5" customFormat="1" spans="1:17">
       <c r="A54" s="2">
         <v>2004</v>
       </c>
@@ -3964,38 +4018,39 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="14">
+      <c r="G54" s="2"/>
+      <c r="H54" s="14">
         <v>4</v>
       </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I54" s="14"/>
       <c r="J54" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L54" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M54" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" s="5" customFormat="1" spans="1:16">
+        <v>159</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" s="5" customFormat="1" spans="1:17">
       <c r="A55" s="2">
         <v>2005</v>
       </c>
@@ -4006,38 +4061,39 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="14">
+      <c r="G55" s="2"/>
+      <c r="H55" s="14">
         <v>4</v>
       </c>
-      <c r="H55" s="14"/>
-      <c r="I55" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I55" s="14"/>
       <c r="J55" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L55" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M55" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2" t="s">
-        <v>159</v>
-      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" s="5" customFormat="1" spans="1:16">
+        <v>162</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" s="5" customFormat="1" spans="1:17">
       <c r="A56" s="2">
         <v>2006</v>
       </c>
@@ -4048,38 +4104,39 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="14">
+      <c r="G56" s="2"/>
+      <c r="H56" s="14">
         <v>4</v>
       </c>
-      <c r="H56" s="14"/>
-      <c r="I56" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="I56" s="14"/>
       <c r="J56" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L56" s="2" t="b">
+        <v>90</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M56" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" s="5" customFormat="1" spans="1:16">
+        <v>165</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" s="5" customFormat="1" spans="1:17">
       <c r="A57" s="2">
         <v>2007</v>
       </c>
@@ -4090,38 +4147,39 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="14">
+      <c r="G57" s="2"/>
+      <c r="H57" s="14">
         <v>4</v>
       </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I57" s="14"/>
       <c r="J57" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L57" s="2" t="b">
+        <v>40</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M57" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" s="3" customFormat="1" spans="1:16">
+        <v>168</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="1" spans="1:17">
       <c r="A58" s="4">
         <v>5000</v>
       </c>
@@ -4130,36 +4188,37 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F58" s="4"/>
-      <c r="G58" s="7">
+      <c r="G58" s="4"/>
+      <c r="H58" s="7">
         <v>6</v>
       </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="I58" s="7"/>
       <c r="J58" s="4" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L58" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M58" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M58" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59" s="4">
         <v>5001</v>
       </c>
@@ -4167,31 +4226,34 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F59" s="15">
+        <v>4058001</v>
+      </c>
+      <c r="H59" s="7">
+        <v>3</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M59" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="G59" s="7">
-        <v>3</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L59" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P59" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16">
+    </row>
+    <row r="60" spans="1:17">
       <c r="A60" s="4">
         <v>5002</v>
       </c>
@@ -4199,34 +4261,37 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G60" s="7">
+        <v>175</v>
+      </c>
+      <c r="F60" s="4">
+        <v>4054001</v>
+      </c>
+      <c r="H60" s="7">
         <v>5</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J60" s="4" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="L60" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16">
+        <v>135</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q60" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
       <c r="A61" s="4">
         <v>5003</v>
       </c>
@@ -4234,34 +4299,37 @@
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F61" s="15">
+        <v>4056001</v>
+      </c>
+      <c r="H61" s="7">
+        <v>5</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="M61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G61" s="7">
-        <v>5</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="L61" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M61" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="P61" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16">
+      <c r="Q61" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
       <c r="A62" s="4">
         <v>5004</v>
       </c>
@@ -4269,34 +4337,37 @@
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G62" s="7">
+        <v>181</v>
+      </c>
+      <c r="F62" s="15">
+        <v>4059000</v>
+      </c>
+      <c r="H62" s="7">
         <v>5</v>
       </c>
-      <c r="I62" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J62" s="4" t="s">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="L62" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="P62" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16">
+        <v>182</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="M62" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q62" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
       <c r="A63" s="4">
         <v>5005</v>
       </c>
@@ -4304,31 +4375,34 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="G63" s="7">
+        <v>184</v>
+      </c>
+      <c r="F63" s="4">
+        <v>10060</v>
+      </c>
+      <c r="H63" s="7">
         <v>5</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J63" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L63" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P63" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M63" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64" s="4">
         <v>5006</v>
       </c>
@@ -4336,31 +4410,31 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G64" s="7">
+        <v>186</v>
+      </c>
+      <c r="H64" s="7">
         <v>2</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J64" s="4" t="s">
-        <v>177</v>
+        <v>39</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="L64" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16">
+        <v>179</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="M64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65" s="4">
         <v>5007</v>
       </c>
@@ -4368,31 +4442,34 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G65" s="7">
+        <v>188</v>
+      </c>
+      <c r="F65" s="4">
+        <v>4057101</v>
+      </c>
+      <c r="H65" s="7">
         <v>3</v>
       </c>
-      <c r="I65" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J65" s="4" t="s">
-        <v>177</v>
+        <v>39</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="L65" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P65" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16">
+        <v>179</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="M65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
       <c r="A66" s="4">
         <v>5008</v>
       </c>
@@ -4400,28 +4477,28 @@
         <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G66" s="7">
+        <v>190</v>
+      </c>
+      <c r="H66" s="7">
         <v>4</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J66" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L66" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16">
+        <v>47</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M66" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67" s="4">
         <v>5009</v>
       </c>
@@ -4429,36 +4506,109 @@
         <v>1</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="G67" s="7">
-        <v>1</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>37</v>
+        <v>192</v>
+      </c>
+      <c r="H67" s="7">
+        <v>1</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L67" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16">
-      <c r="L68" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M67" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
+      <c r="A68" s="4">
+        <v>5010</v>
+      </c>
+      <c r="B68" s="4">
+        <v>1</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H68" s="7">
+        <v>3</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M68" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
+      <c r="A69" s="4">
+        <v>5011</v>
+      </c>
+      <c r="B69" s="4">
+        <v>1</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" s="7">
+        <v>3</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M69" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="4" t="s">
+        <v>171</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E65">
+  <conditionalFormatting sqref="F13">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F61">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E64 E66:E1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="F62">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E65:F65">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:F12 E13 E14:F58 E59 E60:F60 E61:E62 E63:F64 E66:F1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -879,6 +879,12 @@
     <t>btn_zm</t>
   </si>
   <si>
+    <t>1_9999</t>
+  </si>
+  <si>
+    <t>simAllLevel(9999)</t>
+  </si>
+  <si>
     <t>2_4062008</t>
   </si>
   <si>
@@ -888,30 +894,27 @@
     <t>btn_lm</t>
   </si>
   <si>
+    <t>赛季(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_yjy</t>
+  </si>
+  <si>
+    <t>SLOT(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_games</t>
+  </si>
+  <si>
+    <t>拜访记录(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (42)</t>
+  </si>
+  <si>
     <t>simAllLevel(10)</t>
   </si>
   <si>
-    <t>赛季(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_yjy</t>
-  </si>
-  <si>
-    <t>simAllLevel(6)</t>
-  </si>
-  <si>
-    <t>SLOT(app竖版)</t>
-  </si>
-  <si>
-    <t>btn_games</t>
-  </si>
-  <si>
-    <t>拜访记录(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (42)</t>
-  </si>
-  <si>
     <t>拜访(app竖版)</t>
   </si>
   <si>
@@ -940,6 +943,12 @@
   </si>
   <si>
     <t>btn_getresources</t>
+  </si>
+  <si>
+    <t>买一送七(app竖版)</t>
+  </si>
+  <si>
+    <t>BuyOneGetSeven</t>
   </si>
 </sst>
 </file>
@@ -952,7 +961,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -995,6 +1004,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1003,6 +1018,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1488,137 +1510,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1638,17 +1660,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1658,29 +1689,44 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2009,7 +2055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -2017,9 +2063,10 @@
     <col min="3" max="3" width="14.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="23.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
-    <col min="6" max="7" width="14.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="19.7" style="7" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="14.625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19.7" style="9" customWidth="1"/>
     <col min="10" max="10" width="18.625" style="4" customWidth="1"/>
     <col min="11" max="11" width="36.6083333333333" style="4" customWidth="1"/>
     <col min="12" max="12" width="40.375" style="4" customWidth="1"/>
@@ -2030,52 +2077,52 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -2083,126 +2130,126 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:17">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:17">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="11" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11" t="s">
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="14" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2216,10 +2263,11 @@
         <v>37</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="H5" s="14" t="s">
+      <c r="F5" s="18"/>
+      <c r="H5" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="14"/>
+      <c r="I5" s="19"/>
       <c r="J5" s="2" t="s">
         <v>39</v>
       </c>
@@ -2251,10 +2299,11 @@
         <v>42</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="H6" s="14" t="s">
+      <c r="F6" s="18"/>
+      <c r="H6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="14"/>
+      <c r="I6" s="19"/>
       <c r="J6" s="2" t="s">
         <v>43</v>
       </c>
@@ -2290,10 +2339,11 @@
       <c r="E7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="14">
-        <v>1</v>
-      </c>
-      <c r="I7" s="14"/>
+      <c r="F7" s="18"/>
+      <c r="H7" s="19">
+        <v>1</v>
+      </c>
+      <c r="I7" s="19"/>
       <c r="J7" s="2" t="s">
         <v>39</v>
       </c>
@@ -2324,13 +2374,14 @@
       <c r="E8" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="F8" s="18"/>
       <c r="G8" s="2">
         <v>5</v>
       </c>
-      <c r="H8" s="14">
-        <v>1</v>
-      </c>
-      <c r="I8" s="14"/>
+      <c r="H8" s="19">
+        <v>1</v>
+      </c>
+      <c r="I8" s="19"/>
       <c r="J8" s="2" t="s">
         <v>39</v>
       </c>
@@ -2366,10 +2417,11 @@
       <c r="E9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="14">
-        <v>1</v>
-      </c>
-      <c r="I9" s="14"/>
+      <c r="F9" s="18"/>
+      <c r="H9" s="19">
+        <v>1</v>
+      </c>
+      <c r="I9" s="19"/>
       <c r="J9" s="2" t="s">
         <v>39</v>
       </c>
@@ -2401,10 +2453,11 @@
       <c r="E10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="14">
-        <v>1</v>
-      </c>
-      <c r="I10" s="14"/>
+      <c r="F10" s="18"/>
+      <c r="H10" s="19">
+        <v>1</v>
+      </c>
+      <c r="I10" s="19"/>
       <c r="J10" s="2" t="s">
         <v>39</v>
       </c>
@@ -2434,10 +2487,10 @@
       <c r="E11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="8">
         <v>4056036</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <v>2</v>
       </c>
       <c r="J11" s="4" t="s">
@@ -2466,10 +2519,11 @@
         <v>57</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="H12" s="14">
-        <v>1</v>
-      </c>
-      <c r="I12" s="14"/>
+      <c r="F12" s="18"/>
+      <c r="H12" s="19">
+        <v>1</v>
+      </c>
+      <c r="I12" s="19"/>
       <c r="J12" s="2" t="s">
         <v>58</v>
       </c>
@@ -2499,10 +2553,10 @@
       <c r="E13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="20">
         <v>10019</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="9">
         <v>5</v>
       </c>
       <c r="J13" s="4" t="s">
@@ -2538,17 +2592,18 @@
       <c r="E14" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="F14" s="18"/>
       <c r="G14" s="2">
         <v>4</v>
       </c>
-      <c r="H14" s="14">
-        <v>1</v>
-      </c>
-      <c r="I14" s="14"/>
+      <c r="H14" s="19">
+        <v>1</v>
+      </c>
+      <c r="I14" s="19"/>
       <c r="J14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="21" t="s">
         <v>40</v>
       </c>
       <c r="L14" s="2" t="s">
@@ -2578,12 +2633,12 @@
       <c r="E15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <v>2</v>
       </c>
-      <c r="I15" s="7"/>
+      <c r="I15" s="9"/>
       <c r="J15" s="4" t="s">
         <v>39</v>
       </c>
@@ -2617,17 +2672,18 @@
       <c r="E16" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="F16" s="18"/>
       <c r="G16" s="2">
         <v>1</v>
       </c>
-      <c r="H16" s="14">
-        <v>1</v>
-      </c>
-      <c r="I16" s="14"/>
+      <c r="H16" s="19">
+        <v>1</v>
+      </c>
+      <c r="I16" s="19"/>
       <c r="J16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K16" s="21" t="s">
         <v>40</v>
       </c>
       <c r="L16" s="2" t="s">
@@ -2662,7 +2718,7 @@
       <c r="G17" s="4">
         <v>2</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="9">
         <v>1</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -2700,7 +2756,7 @@
       <c r="G18" s="4">
         <v>9</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="9">
         <v>1</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -2738,7 +2794,7 @@
       <c r="G19" s="4">
         <v>3</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="9">
         <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
@@ -2773,7 +2829,7 @@
       <c r="G20" s="4">
         <v>6</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="9">
         <v>4</v>
       </c>
       <c r="J20" s="4" t="s">
@@ -2808,13 +2864,14 @@
       <c r="E21" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="F21" s="18"/>
       <c r="G21" s="2">
         <v>7</v>
       </c>
-      <c r="H21" s="14">
-        <v>1</v>
-      </c>
-      <c r="I21" s="14"/>
+      <c r="H21" s="19">
+        <v>1</v>
+      </c>
+      <c r="I21" s="19"/>
       <c r="J21" s="2" t="s">
         <v>43</v>
       </c>
@@ -2850,13 +2907,14 @@
       <c r="E22" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="F22" s="18"/>
       <c r="G22" s="2">
         <v>8</v>
       </c>
-      <c r="H22" s="14">
-        <v>1</v>
-      </c>
-      <c r="I22" s="14"/>
+      <c r="H22" s="19">
+        <v>1</v>
+      </c>
+      <c r="I22" s="19"/>
       <c r="J22" s="2" t="s">
         <v>89</v>
       </c>
@@ -2895,7 +2953,7 @@
       <c r="G23" s="4">
         <v>11</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="9">
         <v>1</v>
       </c>
       <c r="J23" s="4" t="s">
@@ -2930,7 +2988,7 @@
       <c r="G24" s="4">
         <v>12</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="9">
         <v>2</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -2963,13 +3021,14 @@
       <c r="E25" s="2" t="s">
         <v>96</v>
       </c>
+      <c r="F25" s="18"/>
       <c r="G25" s="2">
         <v>13</v>
       </c>
-      <c r="H25" s="14">
-        <v>1</v>
-      </c>
-      <c r="I25" s="14"/>
+      <c r="H25" s="19">
+        <v>1</v>
+      </c>
+      <c r="I25" s="19"/>
       <c r="J25" s="2" t="s">
         <v>39</v>
       </c>
@@ -3037,7 +3096,7 @@
       <c r="G27" s="4">
         <v>15</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="9">
         <v>2</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -3070,13 +3129,14 @@
       <c r="E28" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="F28" s="18"/>
       <c r="G28" s="2">
         <v>16</v>
       </c>
-      <c r="H28" s="14">
-        <v>1</v>
-      </c>
-      <c r="I28" s="14"/>
+      <c r="H28" s="19">
+        <v>1</v>
+      </c>
+      <c r="I28" s="19"/>
       <c r="J28" s="2" t="s">
         <v>104</v>
       </c>
@@ -3104,16 +3164,17 @@
       <c r="D29" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="22" t="s">
         <v>107</v>
       </c>
+      <c r="F29" s="18"/>
       <c r="G29" s="2">
         <v>17</v>
       </c>
-      <c r="H29" s="14">
-        <v>1</v>
-      </c>
-      <c r="I29" s="14"/>
+      <c r="H29" s="19">
+        <v>1</v>
+      </c>
+      <c r="I29" s="19"/>
       <c r="J29" s="2" t="s">
         <v>39</v>
       </c>
@@ -3141,16 +3202,17 @@
       <c r="D30" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="22" t="s">
         <v>109</v>
       </c>
+      <c r="F30" s="18"/>
       <c r="G30" s="2">
         <v>18</v>
       </c>
-      <c r="H30" s="14">
-        <v>1</v>
-      </c>
-      <c r="I30" s="14"/>
+      <c r="H30" s="19">
+        <v>1</v>
+      </c>
+      <c r="I30" s="19"/>
       <c r="J30" s="2" t="s">
         <v>104</v>
       </c>
@@ -3178,16 +3240,17 @@
       <c r="D31" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="23" t="s">
         <v>111</v>
       </c>
+      <c r="F31" s="8"/>
       <c r="G31" s="4">
         <v>19</v>
       </c>
-      <c r="H31" s="7">
-        <v>1</v>
-      </c>
-      <c r="I31" s="7"/>
+      <c r="H31" s="9">
+        <v>1</v>
+      </c>
+      <c r="I31" s="9"/>
       <c r="J31" s="4" t="s">
         <v>39</v>
       </c>
@@ -3215,16 +3278,17 @@
       <c r="D32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="22" t="s">
         <v>113</v>
       </c>
+      <c r="F32" s="18"/>
       <c r="G32" s="2">
         <v>20</v>
       </c>
-      <c r="H32" s="14">
-        <v>1</v>
-      </c>
-      <c r="I32" s="14"/>
+      <c r="H32" s="19">
+        <v>1</v>
+      </c>
+      <c r="I32" s="19"/>
       <c r="J32" s="2" t="s">
         <v>104</v>
       </c>
@@ -3252,16 +3316,17 @@
       <c r="D33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="22" t="s">
         <v>115</v>
       </c>
+      <c r="F33" s="18"/>
       <c r="G33" s="2">
         <v>21</v>
       </c>
-      <c r="H33" s="14">
-        <v>1</v>
-      </c>
-      <c r="I33" s="14"/>
+      <c r="H33" s="19">
+        <v>1</v>
+      </c>
+      <c r="I33" s="19"/>
       <c r="J33" s="2" t="s">
         <v>104</v>
       </c>
@@ -3288,16 +3353,17 @@
       <c r="D34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="22" t="s">
         <v>117</v>
       </c>
+      <c r="F34" s="18"/>
       <c r="G34" s="2">
         <v>22</v>
       </c>
-      <c r="H34" s="14">
-        <v>1</v>
-      </c>
-      <c r="I34" s="14"/>
+      <c r="H34" s="19">
+        <v>1</v>
+      </c>
+      <c r="I34" s="19"/>
       <c r="J34" s="2" t="s">
         <v>39</v>
       </c>
@@ -3328,10 +3394,11 @@
       <c r="E35" s="2" t="s">
         <v>119</v>
       </c>
+      <c r="F35" s="18"/>
       <c r="G35" s="2">
         <v>10</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="19">
         <v>1</v>
       </c>
       <c r="I35" s="2"/>
@@ -3366,13 +3433,14 @@
         <v>120</v>
       </c>
       <c r="E36" s="2"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="2">
         <v>23</v>
       </c>
-      <c r="H36" s="14">
-        <v>1</v>
-      </c>
-      <c r="I36" s="14"/>
+      <c r="H36" s="19">
+        <v>1</v>
+      </c>
+      <c r="I36" s="19"/>
       <c r="J36" s="2" t="s">
         <v>39</v>
       </c>
@@ -3426,13 +3494,14 @@
       <c r="E38" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="F38" s="18"/>
       <c r="G38" s="2">
         <v>24</v>
       </c>
-      <c r="H38" s="14">
-        <v>1</v>
-      </c>
-      <c r="I38" s="14"/>
+      <c r="H38" s="19">
+        <v>1</v>
+      </c>
+      <c r="I38" s="19"/>
       <c r="J38" s="2" t="s">
         <v>39</v>
       </c>
@@ -3462,7 +3531,7 @@
       <c r="G39" s="4">
         <v>25</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="9">
         <v>2</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -3495,13 +3564,14 @@
       <c r="E40" s="2" t="s">
         <v>127</v>
       </c>
+      <c r="F40" s="18"/>
       <c r="G40" s="2">
         <v>26</v>
       </c>
-      <c r="H40" s="14">
-        <v>1</v>
-      </c>
-      <c r="I40" s="14"/>
+      <c r="H40" s="19">
+        <v>1</v>
+      </c>
+      <c r="I40" s="19"/>
       <c r="J40" s="2" t="s">
         <v>39</v>
       </c>
@@ -3528,12 +3598,12 @@
         <v>128</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="14" t="s">
+      <c r="H41" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I41" s="14"/>
+      <c r="I41" s="19"/>
       <c r="J41" s="2" t="s">
         <v>39</v>
       </c>
@@ -3563,12 +3633,12 @@
         <v>130</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="14">
-        <v>1</v>
-      </c>
-      <c r="I42" s="14"/>
+      <c r="H42" s="19">
+        <v>1</v>
+      </c>
+      <c r="I42" s="19"/>
       <c r="J42" s="2" t="s">
         <v>39</v>
       </c>
@@ -3598,12 +3668,12 @@
         <v>131</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="18"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="14">
-        <v>1</v>
-      </c>
-      <c r="I43" s="14"/>
+      <c r="H43" s="19">
+        <v>1</v>
+      </c>
+      <c r="I43" s="19"/>
       <c r="J43" s="2" t="s">
         <v>39</v>
       </c>
@@ -3613,7 +3683,7 @@
       <c r="L43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M43" s="19" t="b">
+      <c r="M43" s="24" t="b">
         <v>1</v>
       </c>
       <c r="N43" s="2"/>
@@ -3631,12 +3701,12 @@
         <v>132</v>
       </c>
       <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
+      <c r="F44" s="18"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="14">
-        <v>1</v>
-      </c>
-      <c r="I44" s="14"/>
+      <c r="H44" s="19">
+        <v>1</v>
+      </c>
+      <c r="I44" s="19"/>
       <c r="J44" s="2" t="s">
         <v>39</v>
       </c>
@@ -3666,12 +3736,12 @@
       <c r="E45" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F45" s="4"/>
+      <c r="F45" s="8"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="7">
+      <c r="H45" s="9">
         <v>4</v>
       </c>
-      <c r="I45" s="7"/>
+      <c r="I45" s="9"/>
       <c r="J45" s="4" t="s">
         <v>39</v>
       </c>
@@ -3703,12 +3773,12 @@
         <v>136</v>
       </c>
       <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
+      <c r="F46" s="18"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="14">
+      <c r="H46" s="19">
         <v>5</v>
       </c>
-      <c r="I46" s="14"/>
+      <c r="I46" s="19"/>
       <c r="J46" s="2" t="s">
         <v>39</v>
       </c>
@@ -3742,12 +3812,12 @@
         <v>138</v>
       </c>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
+      <c r="F47" s="18"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="14">
+      <c r="H47" s="19">
         <v>5</v>
       </c>
-      <c r="I47" s="14"/>
+      <c r="I47" s="19"/>
       <c r="J47" s="2" t="s">
         <v>39</v>
       </c>
@@ -3781,12 +3851,12 @@
         <v>140</v>
       </c>
       <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
+      <c r="F48" s="18"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="14">
+      <c r="H48" s="19">
         <v>5</v>
       </c>
-      <c r="I48" s="14"/>
+      <c r="I48" s="19"/>
       <c r="J48" s="2" t="s">
         <v>39</v>
       </c>
@@ -3820,10 +3890,11 @@
         <v>142</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="H49" s="20">
+      <c r="F49" s="25"/>
+      <c r="H49" s="25">
         <v>5</v>
       </c>
-      <c r="I49" s="20"/>
+      <c r="I49" s="25"/>
       <c r="J49" s="6" t="s">
         <v>39</v>
       </c>
@@ -3857,10 +3928,11 @@
         <v>144</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="H50" s="20">
+      <c r="F50" s="25"/>
+      <c r="H50" s="25">
         <v>5</v>
       </c>
-      <c r="I50" s="20"/>
+      <c r="I50" s="25"/>
       <c r="J50" s="6" t="s">
         <v>39</v>
       </c>
@@ -3896,12 +3968,12 @@
         <v>146</v>
       </c>
       <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
+      <c r="F51" s="18"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="14">
+      <c r="H51" s="19">
         <v>4</v>
       </c>
-      <c r="I51" s="14"/>
+      <c r="I51" s="19"/>
       <c r="J51" s="2" t="s">
         <v>43</v>
       </c>
@@ -3937,12 +4009,12 @@
         <v>149</v>
       </c>
       <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
+      <c r="F52" s="18"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="14">
+      <c r="H52" s="19">
         <v>4</v>
       </c>
-      <c r="I52" s="14"/>
+      <c r="I52" s="19"/>
       <c r="J52" s="2" t="s">
         <v>150</v>
       </c>
@@ -3977,13 +4049,13 @@
       <c r="D53" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E53" s="17"/>
-      <c r="F53" s="2"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="18"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="14">
+      <c r="H53" s="19">
         <v>4</v>
       </c>
-      <c r="I53" s="14"/>
+      <c r="I53" s="19"/>
       <c r="J53" s="2" t="s">
         <v>39</v>
       </c>
@@ -4021,12 +4093,12 @@
         <v>157</v>
       </c>
       <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
+      <c r="F54" s="18"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="14">
+      <c r="H54" s="19">
         <v>4</v>
       </c>
-      <c r="I54" s="14"/>
+      <c r="I54" s="19"/>
       <c r="J54" s="2" t="s">
         <v>39</v>
       </c>
@@ -4064,12 +4136,12 @@
         <v>160</v>
       </c>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
+      <c r="F55" s="18"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="14">
+      <c r="H55" s="19">
         <v>4</v>
       </c>
-      <c r="I55" s="14"/>
+      <c r="I55" s="19"/>
       <c r="J55" s="2" t="s">
         <v>39</v>
       </c>
@@ -4107,12 +4179,12 @@
         <v>163</v>
       </c>
       <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
+      <c r="F56" s="18"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="14">
+      <c r="H56" s="19">
         <v>4</v>
       </c>
-      <c r="I56" s="14"/>
+      <c r="I56" s="19"/>
       <c r="J56" s="2" t="s">
         <v>89</v>
       </c>
@@ -4150,12 +4222,12 @@
         <v>166</v>
       </c>
       <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
+      <c r="F57" s="18"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="14">
+      <c r="H57" s="19">
         <v>4</v>
       </c>
-      <c r="I57" s="14"/>
+      <c r="I57" s="19"/>
       <c r="J57" s="2" t="s">
         <v>39</v>
       </c>
@@ -4193,12 +4265,12 @@
       <c r="E58" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F58" s="4"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="7">
+      <c r="H58" s="9">
         <v>6</v>
       </c>
-      <c r="I58" s="7"/>
+      <c r="I58" s="9"/>
       <c r="J58" s="4" t="s">
         <v>39</v>
       </c>
@@ -4231,10 +4303,10 @@
       <c r="E59" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="20">
         <v>4058001</v>
       </c>
-      <c r="H59" s="7">
+      <c r="H59" s="9">
         <v>3</v>
       </c>
       <c r="J59" s="4" t="s">
@@ -4253,117 +4325,126 @@
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:17">
-      <c r="A60" s="4">
+    <row r="60" s="7" customFormat="1" spans="1:17">
+      <c r="A60" s="7">
         <v>5002</v>
       </c>
-      <c r="B60" s="4">
-        <v>1</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="B60" s="7">
+        <v>1</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="26">
         <v>4054001</v>
       </c>
-      <c r="H60" s="7">
+      <c r="G60" s="7"/>
+      <c r="H60" s="27">
         <v>5</v>
       </c>
-      <c r="J60" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M60" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N60" s="4" t="s">
+      <c r="I60" s="27"/>
+      <c r="J60" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="Q60" s="4" t="s">
+      <c r="K60" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M60" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q60" s="7" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="61" spans="1:17">
-      <c r="A61" s="4">
+    <row r="61" s="7" customFormat="1" spans="1:17">
+      <c r="A61" s="7">
         <v>5003</v>
       </c>
-      <c r="B61" s="4">
-        <v>1</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="B61" s="7">
+        <v>1</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" s="27">
+        <v>4056001</v>
+      </c>
+      <c r="G61" s="7"/>
+      <c r="H61" s="27">
+        <v>5</v>
+      </c>
+      <c r="I61" s="27"/>
+      <c r="J61" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="K61" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="L61" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M61" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="F61" s="15">
-        <v>4056001</v>
-      </c>
-      <c r="H61" s="7">
+      <c r="Q61" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" s="7" customFormat="1" spans="1:17">
+      <c r="A62" s="7">
+        <v>5004</v>
+      </c>
+      <c r="B62" s="7">
+        <v>1</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F62" s="27">
+        <v>4059000</v>
+      </c>
+      <c r="G62" s="7"/>
+      <c r="H62" s="27">
         <v>5</v>
       </c>
-      <c r="J61" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="M61" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N61" s="4" t="s">
+      <c r="I62" s="27"/>
+      <c r="J62" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="Q61" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17">
-      <c r="A62" s="4">
-        <v>5004</v>
-      </c>
-      <c r="B62" s="4">
-        <v>1</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F62" s="15">
-        <v>4059000</v>
-      </c>
-      <c r="H62" s="7">
-        <v>5</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="M62" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N62" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q62" s="4" t="s">
+      <c r="K62" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M62" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q62" s="7" t="s">
         <v>171</v>
       </c>
     </row>
@@ -4380,10 +4461,10 @@
       <c r="E63" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="8">
         <v>10060</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="9">
         <v>5</v>
       </c>
       <c r="J63" s="4" t="s">
@@ -4415,17 +4496,17 @@
       <c r="E64" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="H64" s="7">
+      <c r="H64" s="9">
         <v>2</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M64" s="1" t="b">
         <v>1</v>
@@ -4442,25 +4523,25 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F65" s="8">
+        <v>4057101</v>
+      </c>
+      <c r="H65" s="9">
+        <v>3</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K65" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F65" s="4">
-        <v>4057101</v>
-      </c>
-      <c r="H65" s="7">
-        <v>3</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="L65" s="4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M65" s="1" t="b">
         <v>1</v>
@@ -4477,12 +4558,12 @@
         <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="H66" s="7">
+        <v>191</v>
+      </c>
+      <c r="H66" s="9">
         <v>4</v>
       </c>
       <c r="J66" s="4" t="s">
@@ -4506,12 +4587,12 @@
         <v>1</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H67" s="7">
+        <v>193</v>
+      </c>
+      <c r="H67" s="9">
         <v>1</v>
       </c>
       <c r="J67" s="4" t="s">
@@ -4535,12 +4616,12 @@
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="H68" s="7">
+        <v>195</v>
+      </c>
+      <c r="H68" s="9">
         <v>3</v>
       </c>
       <c r="J68" s="4" t="s">
@@ -4567,12 +4648,12 @@
         <v>1</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="H69" s="7">
+        <v>197</v>
+      </c>
+      <c r="H69" s="9">
         <v>3</v>
       </c>
       <c r="J69" s="4" t="s">
@@ -4591,24 +4672,59 @@
         <v>171</v>
       </c>
     </row>
+    <row r="70" spans="1:17">
+      <c r="A70" s="4">
+        <v>5012</v>
+      </c>
+      <c r="B70" s="4">
+        <v>1</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H70" s="9">
+        <v>1</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F13">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
+  <conditionalFormatting sqref="F61">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F61">
+  <conditionalFormatting sqref="F62">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F62">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="E65:F65">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E65:F65">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  <conditionalFormatting sqref="E70:F70">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:F12 E13 E14:F58 E59 E60:F60 E61:E62 E63:F64 E66:F1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  <conditionalFormatting sqref="E1:F12 E13 E14:F58 E59 E60:F60 E61:E62 E63:F64 E66:F69 E71:F1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="198">
   <si>
     <t>id</t>
   </si>
@@ -877,12 +877,6 @@
   </si>
   <si>
     <t>btn_zm</t>
-  </si>
-  <si>
-    <t>1_9999</t>
-  </si>
-  <si>
-    <t>simAllLevel(9999)</t>
   </si>
   <si>
     <t>2_4062008</t>
@@ -1173,12 +1167,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1640,7 +1634,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1668,18 +1662,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1689,18 +1677,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1717,9 +1699,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2055,7 +2034,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -2065,8 +2044,8 @@
     <col min="5" max="5" width="21.5" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="8" customWidth="1"/>
     <col min="7" max="7" width="14.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="19.7" style="9" customWidth="1"/>
+    <col min="8" max="8" width="11.875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="19.7" style="8" customWidth="1"/>
     <col min="10" max="10" width="18.625" style="4" customWidth="1"/>
     <col min="11" max="11" width="36.6083333333333" style="4" customWidth="1"/>
     <col min="12" max="12" width="40.375" style="4" customWidth="1"/>
@@ -2076,184 +2055,184 @@
     <col min="18" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:17">
-      <c r="A2" s="10" t="s">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:18">
+      <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:17">
-      <c r="A3" s="10" t="s">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:18">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="14" t="s">
+    <row r="4" spans="1:18">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="L4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14" t="s">
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="P4" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:17">
+    <row r="5" s="2" customFormat="1" spans="1:18">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -2263,11 +2242,11 @@
         <v>37</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="18"/>
-      <c r="H5" s="19" t="s">
+      <c r="F5" s="15"/>
+      <c r="H5" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="19"/>
+      <c r="I5" s="15"/>
       <c r="J5" s="2" t="s">
         <v>39</v>
       </c>
@@ -2287,7 +2266,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:17">
+    <row r="6" s="2" customFormat="1" spans="1:18">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -2299,11 +2278,11 @@
         <v>42</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="18"/>
-      <c r="H6" s="19" t="s">
+      <c r="F6" s="15"/>
+      <c r="H6" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="19"/>
+      <c r="I6" s="15"/>
       <c r="J6" s="2" t="s">
         <v>43</v>
       </c>
@@ -2323,7 +2302,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:17">
+    <row r="7" s="2" customFormat="1" spans="1:18">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -2339,11 +2318,11 @@
       <c r="E7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="H7" s="19">
-        <v>1</v>
-      </c>
-      <c r="I7" s="19"/>
+      <c r="F7" s="15"/>
+      <c r="H7" s="15">
+        <v>1</v>
+      </c>
+      <c r="I7" s="15"/>
       <c r="J7" s="2" t="s">
         <v>39</v>
       </c>
@@ -2360,7 +2339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:17">
+    <row r="8" s="2" customFormat="1" spans="1:18">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -2374,14 +2353,14 @@
       <c r="E8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="18"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="2">
         <v>5</v>
       </c>
-      <c r="H8" s="19">
-        <v>1</v>
-      </c>
-      <c r="I8" s="19"/>
+      <c r="H8" s="15">
+        <v>1</v>
+      </c>
+      <c r="I8" s="15"/>
       <c r="J8" s="2" t="s">
         <v>39</v>
       </c>
@@ -2401,7 +2380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:17">
+    <row r="9" s="2" customFormat="1" spans="1:18">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -2417,11 +2396,11 @@
       <c r="E9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="H9" s="19">
-        <v>1</v>
-      </c>
-      <c r="I9" s="19"/>
+      <c r="F9" s="15"/>
+      <c r="H9" s="15">
+        <v>1</v>
+      </c>
+      <c r="I9" s="15"/>
       <c r="J9" s="2" t="s">
         <v>39</v>
       </c>
@@ -2441,7 +2420,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:17">
+    <row r="10" s="2" customFormat="1" spans="1:18">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -2453,11 +2432,11 @@
       <c r="E10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="18"/>
-      <c r="H10" s="19">
-        <v>1</v>
-      </c>
-      <c r="I10" s="19"/>
+      <c r="F10" s="15"/>
+      <c r="H10" s="15">
+        <v>1</v>
+      </c>
+      <c r="I10" s="15"/>
       <c r="J10" s="2" t="s">
         <v>39</v>
       </c>
@@ -2477,7 +2456,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -2490,7 +2469,7 @@
       <c r="F11" s="8">
         <v>4056036</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>2</v>
       </c>
       <c r="J11" s="4" t="s">
@@ -2509,7 +2488,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:17">
+    <row r="12" s="2" customFormat="1" spans="1:18">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -2519,11 +2498,11 @@
         <v>57</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="18"/>
-      <c r="H12" s="19">
-        <v>1</v>
-      </c>
-      <c r="I12" s="19"/>
+      <c r="F12" s="15"/>
+      <c r="H12" s="15">
+        <v>1</v>
+      </c>
+      <c r="I12" s="15"/>
       <c r="J12" s="2" t="s">
         <v>58</v>
       </c>
@@ -2543,7 +2522,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -2553,10 +2532,10 @@
       <c r="E13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="16">
         <v>10019</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>5</v>
       </c>
       <c r="J13" s="4" t="s">
@@ -2571,14 +2550,15 @@
       <c r="M13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="N13" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="N13" s="4"/>
       <c r="Q13" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:17">
+      <c r="R13" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:18">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -2592,18 +2572,18 @@
       <c r="E14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="18"/>
+      <c r="F14" s="15"/>
       <c r="G14" s="2">
         <v>4</v>
       </c>
-      <c r="H14" s="19">
-        <v>1</v>
-      </c>
-      <c r="I14" s="19"/>
+      <c r="H14" s="15">
+        <v>1</v>
+      </c>
+      <c r="I14" s="15"/>
       <c r="J14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" s="17" t="s">
         <v>40</v>
       </c>
       <c r="L14" s="2" t="s">
@@ -2619,7 +2599,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:17">
+    <row r="15" s="3" customFormat="1" spans="1:18">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -2635,10 +2615,10 @@
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>2</v>
       </c>
-      <c r="I15" s="9"/>
+      <c r="I15" s="8"/>
       <c r="J15" s="4" t="s">
         <v>39</v>
       </c>
@@ -2658,7 +2638,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:17">
+    <row r="16" s="2" customFormat="1" spans="1:18">
       <c r="A16" s="2">
         <v>101</v>
       </c>
@@ -2672,18 +2652,18 @@
       <c r="E16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="18"/>
+      <c r="F16" s="15"/>
       <c r="G16" s="2">
         <v>1</v>
       </c>
-      <c r="H16" s="19">
-        <v>1</v>
-      </c>
-      <c r="I16" s="19"/>
+      <c r="H16" s="15">
+        <v>1</v>
+      </c>
+      <c r="I16" s="15"/>
       <c r="J16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K16" s="21" t="s">
+      <c r="K16" s="17" t="s">
         <v>40</v>
       </c>
       <c r="L16" s="2" t="s">
@@ -2718,7 +2698,7 @@
       <c r="G17" s="4">
         <v>2</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>1</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -2756,7 +2736,7 @@
       <c r="G18" s="4">
         <v>9</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>1</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -2794,7 +2774,7 @@
       <c r="G19" s="4">
         <v>3</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
@@ -2829,7 +2809,7 @@
       <c r="G20" s="4">
         <v>6</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>4</v>
       </c>
       <c r="J20" s="4" t="s">
@@ -2864,14 +2844,14 @@
       <c r="E21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="18"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="2">
         <v>7</v>
       </c>
-      <c r="H21" s="19">
-        <v>1</v>
-      </c>
-      <c r="I21" s="19"/>
+      <c r="H21" s="15">
+        <v>1</v>
+      </c>
+      <c r="I21" s="15"/>
       <c r="J21" s="2" t="s">
         <v>43</v>
       </c>
@@ -2907,14 +2887,14 @@
       <c r="E22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="18"/>
+      <c r="F22" s="15"/>
       <c r="G22" s="2">
         <v>8</v>
       </c>
-      <c r="H22" s="19">
-        <v>1</v>
-      </c>
-      <c r="I22" s="19"/>
+      <c r="H22" s="15">
+        <v>1</v>
+      </c>
+      <c r="I22" s="15"/>
       <c r="J22" s="2" t="s">
         <v>89</v>
       </c>
@@ -2953,7 +2933,7 @@
       <c r="G23" s="4">
         <v>11</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <v>1</v>
       </c>
       <c r="J23" s="4" t="s">
@@ -2988,7 +2968,7 @@
       <c r="G24" s="4">
         <v>12</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <v>2</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -3021,14 +3001,14 @@
       <c r="E25" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F25" s="18"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="2">
         <v>13</v>
       </c>
-      <c r="H25" s="19">
-        <v>1</v>
-      </c>
-      <c r="I25" s="19"/>
+      <c r="H25" s="15">
+        <v>1</v>
+      </c>
+      <c r="I25" s="15"/>
       <c r="J25" s="2" t="s">
         <v>39</v>
       </c>
@@ -3096,7 +3076,7 @@
       <c r="G27" s="4">
         <v>15</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <v>2</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -3129,14 +3109,14 @@
       <c r="E28" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="18"/>
+      <c r="F28" s="15"/>
       <c r="G28" s="2">
         <v>16</v>
       </c>
-      <c r="H28" s="19">
-        <v>1</v>
-      </c>
-      <c r="I28" s="19"/>
+      <c r="H28" s="15">
+        <v>1</v>
+      </c>
+      <c r="I28" s="15"/>
       <c r="J28" s="2" t="s">
         <v>104</v>
       </c>
@@ -3164,17 +3144,17 @@
       <c r="D29" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F29" s="18"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="2">
         <v>17</v>
       </c>
-      <c r="H29" s="19">
-        <v>1</v>
-      </c>
-      <c r="I29" s="19"/>
+      <c r="H29" s="15">
+        <v>1</v>
+      </c>
+      <c r="I29" s="15"/>
       <c r="J29" s="2" t="s">
         <v>39</v>
       </c>
@@ -3202,17 +3182,17 @@
       <c r="D30" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="18"/>
+      <c r="F30" s="15"/>
       <c r="G30" s="2">
         <v>18</v>
       </c>
-      <c r="H30" s="19">
-        <v>1</v>
-      </c>
-      <c r="I30" s="19"/>
+      <c r="H30" s="15">
+        <v>1</v>
+      </c>
+      <c r="I30" s="15"/>
       <c r="J30" s="2" t="s">
         <v>104</v>
       </c>
@@ -3240,17 +3220,17 @@
       <c r="D31" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="19" t="s">
         <v>111</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="4">
         <v>19</v>
       </c>
-      <c r="H31" s="9">
-        <v>1</v>
-      </c>
-      <c r="I31" s="9"/>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="8"/>
       <c r="J31" s="4" t="s">
         <v>39</v>
       </c>
@@ -3278,17 +3258,17 @@
       <c r="D32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="18"/>
+      <c r="F32" s="15"/>
       <c r="G32" s="2">
         <v>20</v>
       </c>
-      <c r="H32" s="19">
-        <v>1</v>
-      </c>
-      <c r="I32" s="19"/>
+      <c r="H32" s="15">
+        <v>1</v>
+      </c>
+      <c r="I32" s="15"/>
       <c r="J32" s="2" t="s">
         <v>104</v>
       </c>
@@ -3316,17 +3296,17 @@
       <c r="D33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="18"/>
+      <c r="F33" s="15"/>
       <c r="G33" s="2">
         <v>21</v>
       </c>
-      <c r="H33" s="19">
-        <v>1</v>
-      </c>
-      <c r="I33" s="19"/>
+      <c r="H33" s="15">
+        <v>1</v>
+      </c>
+      <c r="I33" s="15"/>
       <c r="J33" s="2" t="s">
         <v>104</v>
       </c>
@@ -3353,17 +3333,17 @@
       <c r="D34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="18"/>
+      <c r="F34" s="15"/>
       <c r="G34" s="2">
         <v>22</v>
       </c>
-      <c r="H34" s="19">
-        <v>1</v>
-      </c>
-      <c r="I34" s="19"/>
+      <c r="H34" s="15">
+        <v>1</v>
+      </c>
+      <c r="I34" s="15"/>
       <c r="J34" s="2" t="s">
         <v>39</v>
       </c>
@@ -3394,11 +3374,11 @@
       <c r="E35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="18"/>
+      <c r="F35" s="15"/>
       <c r="G35" s="2">
         <v>10</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="15">
         <v>1</v>
       </c>
       <c r="I35" s="2"/>
@@ -3433,14 +3413,14 @@
         <v>120</v>
       </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="18"/>
+      <c r="F36" s="15"/>
       <c r="G36" s="2">
         <v>23</v>
       </c>
-      <c r="H36" s="19">
-        <v>1</v>
-      </c>
-      <c r="I36" s="19"/>
+      <c r="H36" s="15">
+        <v>1</v>
+      </c>
+      <c r="I36" s="15"/>
       <c r="J36" s="2" t="s">
         <v>39</v>
       </c>
@@ -3494,14 +3474,14 @@
       <c r="E38" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F38" s="18"/>
+      <c r="F38" s="15"/>
       <c r="G38" s="2">
         <v>24</v>
       </c>
-      <c r="H38" s="19">
-        <v>1</v>
-      </c>
-      <c r="I38" s="19"/>
+      <c r="H38" s="15">
+        <v>1</v>
+      </c>
+      <c r="I38" s="15"/>
       <c r="J38" s="2" t="s">
         <v>39</v>
       </c>
@@ -3531,7 +3511,7 @@
       <c r="G39" s="4">
         <v>25</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="8">
         <v>2</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -3564,14 +3544,14 @@
       <c r="E40" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F40" s="18"/>
+      <c r="F40" s="15"/>
       <c r="G40" s="2">
         <v>26</v>
       </c>
-      <c r="H40" s="19">
-        <v>1</v>
-      </c>
-      <c r="I40" s="19"/>
+      <c r="H40" s="15">
+        <v>1</v>
+      </c>
+      <c r="I40" s="15"/>
       <c r="J40" s="2" t="s">
         <v>39</v>
       </c>
@@ -3598,12 +3578,12 @@
         <v>128</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="18"/>
+      <c r="F41" s="15"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="I41" s="19"/>
+      <c r="I41" s="15"/>
       <c r="J41" s="2" t="s">
         <v>39</v>
       </c>
@@ -3633,12 +3613,12 @@
         <v>130</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="18"/>
+      <c r="F42" s="15"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="19">
-        <v>1</v>
-      </c>
-      <c r="I42" s="19"/>
+      <c r="H42" s="15">
+        <v>1</v>
+      </c>
+      <c r="I42" s="15"/>
       <c r="J42" s="2" t="s">
         <v>39</v>
       </c>
@@ -3668,12 +3648,12 @@
         <v>131</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="18"/>
+      <c r="F43" s="15"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="19">
-        <v>1</v>
-      </c>
-      <c r="I43" s="19"/>
+      <c r="H43" s="15">
+        <v>1</v>
+      </c>
+      <c r="I43" s="15"/>
       <c r="J43" s="2" t="s">
         <v>39</v>
       </c>
@@ -3683,7 +3663,7 @@
       <c r="L43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M43" s="24" t="b">
+      <c r="M43" s="20" t="b">
         <v>1</v>
       </c>
       <c r="N43" s="2"/>
@@ -3701,12 +3681,12 @@
         <v>132</v>
       </c>
       <c r="E44" s="2"/>
-      <c r="F44" s="18"/>
+      <c r="F44" s="15"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="19">
-        <v>1</v>
-      </c>
-      <c r="I44" s="19"/>
+      <c r="H44" s="15">
+        <v>1</v>
+      </c>
+      <c r="I44" s="15"/>
       <c r="J44" s="2" t="s">
         <v>39</v>
       </c>
@@ -3738,10 +3718,10 @@
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="9">
+      <c r="H45" s="8">
         <v>4</v>
       </c>
-      <c r="I45" s="9"/>
+      <c r="I45" s="8"/>
       <c r="J45" s="4" t="s">
         <v>39</v>
       </c>
@@ -3773,12 +3753,12 @@
         <v>136</v>
       </c>
       <c r="E46" s="2"/>
-      <c r="F46" s="18"/>
+      <c r="F46" s="15"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="19">
+      <c r="H46" s="15">
         <v>5</v>
       </c>
-      <c r="I46" s="19"/>
+      <c r="I46" s="15"/>
       <c r="J46" s="2" t="s">
         <v>39</v>
       </c>
@@ -3812,12 +3792,12 @@
         <v>138</v>
       </c>
       <c r="E47" s="2"/>
-      <c r="F47" s="18"/>
+      <c r="F47" s="15"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="19">
+      <c r="H47" s="15">
         <v>5</v>
       </c>
-      <c r="I47" s="19"/>
+      <c r="I47" s="15"/>
       <c r="J47" s="2" t="s">
         <v>39</v>
       </c>
@@ -3851,12 +3831,12 @@
         <v>140</v>
       </c>
       <c r="E48" s="2"/>
-      <c r="F48" s="18"/>
+      <c r="F48" s="15"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="19">
+      <c r="H48" s="15">
         <v>5</v>
       </c>
-      <c r="I48" s="19"/>
+      <c r="I48" s="15"/>
       <c r="J48" s="2" t="s">
         <v>39</v>
       </c>
@@ -3878,7 +3858,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" s="6" customFormat="1" spans="1:17">
+    <row r="49" s="6" customFormat="1" spans="1:18">
       <c r="A49" s="6">
         <v>1004</v>
       </c>
@@ -3890,11 +3870,11 @@
         <v>142</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="25"/>
-      <c r="H49" s="25">
+      <c r="F49" s="21"/>
+      <c r="H49" s="21">
         <v>5</v>
       </c>
-      <c r="I49" s="25"/>
+      <c r="I49" s="21"/>
       <c r="J49" s="6" t="s">
         <v>39</v>
       </c>
@@ -3916,7 +3896,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" s="6" customFormat="1" spans="1:17">
+    <row r="50" s="6" customFormat="1" spans="1:18">
       <c r="A50" s="6">
         <v>1005</v>
       </c>
@@ -3928,11 +3908,11 @@
         <v>144</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="25"/>
-      <c r="H50" s="25">
+      <c r="F50" s="21"/>
+      <c r="H50" s="21">
         <v>5</v>
       </c>
-      <c r="I50" s="25"/>
+      <c r="I50" s="21"/>
       <c r="J50" s="6" t="s">
         <v>39</v>
       </c>
@@ -3954,7 +3934,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" s="5" customFormat="1" spans="1:17">
+    <row r="51" s="5" customFormat="1" spans="1:18">
       <c r="A51" s="2">
         <v>2001</v>
       </c>
@@ -3968,12 +3948,12 @@
         <v>146</v>
       </c>
       <c r="E51" s="2"/>
-      <c r="F51" s="18"/>
+      <c r="F51" s="15"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="19">
+      <c r="H51" s="15">
         <v>4</v>
       </c>
-      <c r="I51" s="19"/>
+      <c r="I51" s="15"/>
       <c r="J51" s="2" t="s">
         <v>43</v>
       </c>
@@ -3997,7 +3977,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" s="5" customFormat="1" spans="1:17">
+    <row r="52" s="5" customFormat="1" spans="1:18">
       <c r="A52" s="2">
         <v>2002</v>
       </c>
@@ -4009,12 +3989,12 @@
         <v>149</v>
       </c>
       <c r="E52" s="2"/>
-      <c r="F52" s="18"/>
+      <c r="F52" s="15"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="19">
+      <c r="H52" s="15">
         <v>4</v>
       </c>
-      <c r="I52" s="19"/>
+      <c r="I52" s="15"/>
       <c r="J52" s="2" t="s">
         <v>150</v>
       </c>
@@ -4038,7 +4018,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" s="5" customFormat="1" spans="1:17">
+    <row r="53" s="5" customFormat="1" spans="1:18">
       <c r="A53" s="2">
         <v>2003</v>
       </c>
@@ -4049,13 +4029,13 @@
       <c r="D53" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="15"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="19">
+      <c r="H53" s="15">
         <v>4</v>
       </c>
-      <c r="I53" s="19"/>
+      <c r="I53" s="15"/>
       <c r="J53" s="2" t="s">
         <v>39</v>
       </c>
@@ -4079,7 +4059,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" s="5" customFormat="1" spans="1:17">
+    <row r="54" s="5" customFormat="1" spans="1:18">
       <c r="A54" s="2">
         <v>2004</v>
       </c>
@@ -4093,12 +4073,12 @@
         <v>157</v>
       </c>
       <c r="E54" s="2"/>
-      <c r="F54" s="18"/>
+      <c r="F54" s="15"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="19">
+      <c r="H54" s="15">
         <v>4</v>
       </c>
-      <c r="I54" s="19"/>
+      <c r="I54" s="15"/>
       <c r="J54" s="2" t="s">
         <v>39</v>
       </c>
@@ -4122,7 +4102,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" s="5" customFormat="1" spans="1:17">
+    <row r="55" s="5" customFormat="1" spans="1:18">
       <c r="A55" s="2">
         <v>2005</v>
       </c>
@@ -4136,12 +4116,12 @@
         <v>160</v>
       </c>
       <c r="E55" s="2"/>
-      <c r="F55" s="18"/>
+      <c r="F55" s="15"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="19">
+      <c r="H55" s="15">
         <v>4</v>
       </c>
-      <c r="I55" s="19"/>
+      <c r="I55" s="15"/>
       <c r="J55" s="2" t="s">
         <v>39</v>
       </c>
@@ -4165,7 +4145,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" s="5" customFormat="1" spans="1:17">
+    <row r="56" s="5" customFormat="1" spans="1:18">
       <c r="A56" s="2">
         <v>2006</v>
       </c>
@@ -4179,12 +4159,12 @@
         <v>163</v>
       </c>
       <c r="E56" s="2"/>
-      <c r="F56" s="18"/>
+      <c r="F56" s="15"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="19">
+      <c r="H56" s="15">
         <v>4</v>
       </c>
-      <c r="I56" s="19"/>
+      <c r="I56" s="15"/>
       <c r="J56" s="2" t="s">
         <v>89</v>
       </c>
@@ -4208,7 +4188,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" s="5" customFormat="1" spans="1:17">
+    <row r="57" s="5" customFormat="1" spans="1:18">
       <c r="A57" s="2">
         <v>2007</v>
       </c>
@@ -4222,12 +4202,12 @@
         <v>166</v>
       </c>
       <c r="E57" s="2"/>
-      <c r="F57" s="18"/>
+      <c r="F57" s="15"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="19">
+      <c r="H57" s="15">
         <v>4</v>
       </c>
-      <c r="I57" s="19"/>
+      <c r="I57" s="15"/>
       <c r="J57" s="2" t="s">
         <v>39</v>
       </c>
@@ -4251,7 +4231,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" s="3" customFormat="1" spans="1:17">
+    <row r="58" s="3" customFormat="1" spans="1:18">
       <c r="A58" s="4">
         <v>5000</v>
       </c>
@@ -4267,10 +4247,10 @@
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="9">
+      <c r="H58" s="8">
         <v>6</v>
       </c>
-      <c r="I58" s="9"/>
+      <c r="I58" s="8"/>
       <c r="J58" s="4" t="s">
         <v>39</v>
       </c>
@@ -4290,7 +4270,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:18">
       <c r="A59" s="4">
         <v>5001</v>
       </c>
@@ -4303,10 +4283,10 @@
       <c r="E59" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="16">
         <v>4058001</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="8">
         <v>3</v>
       </c>
       <c r="J59" s="4" t="s">
@@ -4325,7 +4305,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="60" s="7" customFormat="1" spans="1:17">
+    <row r="60" s="7" customFormat="1" spans="1:18">
       <c r="A60" s="7">
         <v>5002</v>
       </c>
@@ -4339,34 +4319,35 @@
       <c r="E60" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F60" s="26">
+      <c r="F60" s="22">
         <v>4054001</v>
       </c>
       <c r="G60" s="7"/>
-      <c r="H60" s="27">
+      <c r="H60" s="22">
         <v>5</v>
       </c>
-      <c r="I60" s="27"/>
-      <c r="J60" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="M60" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="N60" s="7" t="s">
-        <v>178</v>
-      </c>
+      <c r="I60" s="22"/>
+      <c r="J60" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M60" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" s="7"/>
       <c r="Q60" s="7" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="61" s="7" customFormat="1" spans="1:17">
+      <c r="R60" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" s="7" customFormat="1" spans="1:18">
       <c r="A61" s="7">
         <v>5003</v>
       </c>
@@ -4375,39 +4356,40 @@
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F61" s="27">
+        <v>178</v>
+      </c>
+      <c r="F61" s="22">
         <v>4056001</v>
       </c>
       <c r="G61" s="7"/>
-      <c r="H61" s="27">
+      <c r="H61" s="22">
         <v>5</v>
       </c>
-      <c r="I61" s="27"/>
-      <c r="J61" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="M61" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="N61" s="7" t="s">
-        <v>178</v>
-      </c>
+      <c r="I61" s="22"/>
+      <c r="J61" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M61" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="7"/>
       <c r="Q61" s="7" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="62" s="7" customFormat="1" spans="1:17">
+      <c r="R61" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" s="7" customFormat="1" spans="1:18">
       <c r="A62" s="7">
         <v>5004</v>
       </c>
@@ -4416,39 +4398,40 @@
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F62" s="27">
+        <v>180</v>
+      </c>
+      <c r="F62" s="22">
         <v>4059000</v>
       </c>
       <c r="G62" s="7"/>
-      <c r="H62" s="27">
+      <c r="H62" s="22">
         <v>5</v>
       </c>
-      <c r="I62" s="27"/>
-      <c r="J62" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="K62" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="L62" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="M62" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="N62" s="7" t="s">
-        <v>178</v>
-      </c>
+      <c r="I62" s="22"/>
+      <c r="J62" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M62" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" s="7"/>
       <c r="Q62" s="7" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="63" spans="1:17">
+      <c r="R62" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
       <c r="A63" s="4">
         <v>5005</v>
       </c>
@@ -4456,15 +4439,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F63" s="8">
         <v>10060</v>
       </c>
-      <c r="H63" s="9">
+      <c r="H63" s="8">
         <v>5</v>
       </c>
       <c r="J63" s="4" t="s">
@@ -4483,7 +4466,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:18">
       <c r="A64" s="4">
         <v>5006</v>
       </c>
@@ -4491,22 +4474,22 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="H64" s="8">
+        <v>2</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K64" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="H64" s="9">
-        <v>2</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="L64" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M64" s="1" t="b">
         <v>1</v>
@@ -4523,25 +4506,25 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F65" s="8">
         <v>4057101</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65" s="8">
         <v>3</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M65" s="1" t="b">
         <v>1</v>
@@ -4558,12 +4541,12 @@
         <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="H66" s="9">
+        <v>189</v>
+      </c>
+      <c r="H66" s="8">
         <v>4</v>
       </c>
       <c r="J66" s="4" t="s">
@@ -4587,12 +4570,12 @@
         <v>1</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H67" s="9">
+        <v>191</v>
+      </c>
+      <c r="H67" s="8">
         <v>1</v>
       </c>
       <c r="J67" s="4" t="s">
@@ -4616,12 +4599,12 @@
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H68" s="9">
+        <v>193</v>
+      </c>
+      <c r="H68" s="8">
         <v>3</v>
       </c>
       <c r="J68" s="4" t="s">
@@ -4648,12 +4631,12 @@
         <v>1</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H69" s="9">
+        <v>195</v>
+      </c>
+      <c r="H69" s="8">
         <v>3</v>
       </c>
       <c r="J69" s="4" t="s">
@@ -4680,12 +4663,12 @@
         <v>1</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H70" s="9">
+        <v>197</v>
+      </c>
+      <c r="H70" s="8">
         <v>1</v>
       </c>
       <c r="J70" s="4" t="s">

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="203">
   <si>
     <t>id</t>
   </si>
@@ -540,69 +540,72 @@
     <t>btn_mail</t>
   </si>
   <si>
+    <t>1_3</t>
+  </si>
+  <si>
+    <t>simAllLevel(3)</t>
+  </si>
+  <si>
+    <t>0_4062005</t>
+  </si>
+  <si>
+    <t>幸运夺宝(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (21)</t>
+  </si>
+  <si>
+    <t>背包(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (40)</t>
+  </si>
+  <si>
+    <t>我的赌场(横版app版)</t>
+  </si>
+  <si>
+    <t>Grid (8)</t>
+  </si>
+  <si>
+    <t>1_20</t>
+  </si>
+  <si>
+    <t>playerLevel(20)</t>
+  </si>
+  <si>
+    <t>每日奖金(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (9)</t>
+  </si>
+  <si>
+    <t>simAllLevel(12)</t>
+  </si>
+  <si>
+    <t>刮刮乐(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (10)</t>
+  </si>
+  <si>
+    <t>simAllLevel(8)</t>
+  </si>
+  <si>
+    <t>储钱罐(app竖版)</t>
+  </si>
+  <si>
+    <t>Grid (11)</t>
+  </si>
+  <si>
     <t>simAllLevel(5)</t>
   </si>
   <si>
-    <t>0_4062005</t>
-  </si>
-  <si>
-    <t>幸运夺宝(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (21)</t>
-  </si>
-  <si>
-    <t>背包(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (40)</t>
-  </si>
-  <si>
-    <t>我的赌场(横版app版)</t>
-  </si>
-  <si>
-    <t>Grid (8)</t>
-  </si>
-  <si>
-    <t>1_20</t>
-  </si>
-  <si>
-    <t>playerLevel(20)</t>
-  </si>
-  <si>
-    <t>每日奖金(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (9)</t>
-  </si>
-  <si>
-    <t>simAllLevel(12)</t>
-  </si>
-  <si>
-    <t>刮刮乐(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (10)</t>
-  </si>
-  <si>
-    <t>simAllLevel(8)</t>
-  </si>
-  <si>
-    <t>储钱罐(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (11)</t>
-  </si>
-  <si>
     <t>等级礼包(app竖版)</t>
   </si>
   <si>
     <t>btn_levelGift</t>
   </si>
   <si>
-    <t>simAllLevel(3)</t>
-  </si>
-  <si>
     <t>首充礼包(横版app版)</t>
   </si>
   <si>
@@ -879,6 +882,12 @@
     <t>btn_zm</t>
   </si>
   <si>
+    <t>1_9999</t>
+  </si>
+  <si>
+    <t>simAllLevel(999)</t>
+  </si>
+  <si>
     <t>2_4062008</t>
   </si>
   <si>
@@ -886,6 +895,12 @@
   </si>
   <si>
     <t>btn_lm</t>
+  </si>
+  <si>
+    <t>1_8</t>
+  </si>
+  <si>
+    <t>0_4062002</t>
   </si>
   <si>
     <t>赛季(app竖版)</t>
@@ -1167,12 +1182,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2539,23 +2554,25 @@
         <v>5</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="Q13" s="4" t="s">
         <v>48</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:18">
@@ -2567,10 +2584,10 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="2">
@@ -2608,10 +2625,10 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="4"/>
@@ -2647,10 +2664,10 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="2">
@@ -2661,13 +2678,13 @@
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K16" s="17" t="s">
         <v>40</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M16" s="2" t="b">
         <v>0</v>
@@ -2690,10 +2707,10 @@
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" s="4">
         <v>2</v>
@@ -2705,10 +2722,10 @@
         <v>39</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M17" s="1" t="b">
         <v>1</v>
@@ -2728,10 +2745,10 @@
         <v>5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" s="4">
         <v>9</v>
@@ -2743,10 +2760,10 @@
         <v>39</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M18" s="1" t="b">
         <v>1</v>
@@ -2766,10 +2783,10 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G19" s="4">
         <v>3</v>
@@ -2781,10 +2798,10 @@
         <v>39</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="M19" s="1" t="b">
         <v>1</v>
@@ -2801,10 +2818,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G20" s="4">
         <v>6</v>
@@ -2816,10 +2833,10 @@
         <v>39</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="M20" s="1" t="b">
         <v>1</v>
@@ -2839,10 +2856,10 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="15"/>
       <c r="G21" s="2">
@@ -2856,10 +2873,10 @@
         <v>43</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M21" s="2" t="b">
         <v>0</v>
@@ -2882,10 +2899,10 @@
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="2">
@@ -2896,13 +2913,13 @@
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M22" s="2" t="b">
         <v>0</v>
@@ -2925,10 +2942,10 @@
         <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" s="4">
         <v>11</v>
@@ -2940,10 +2957,10 @@
         <v>39</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="M23" s="1" t="b">
         <v>1</v>
@@ -2960,10 +2977,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G24" s="4">
         <v>12</v>
@@ -2996,10 +3013,10 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="2">
@@ -3036,10 +3053,10 @@
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G26" s="4">
         <v>14</v>
@@ -3057,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -3068,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G27" s="4">
         <v>15</v>
@@ -3104,10 +3121,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="2">
@@ -3118,13 +3135,13 @@
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M28" s="2" t="b">
         <v>0</v>
@@ -3142,10 +3159,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="2">
@@ -3180,10 +3197,10 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="2">
@@ -3194,13 +3211,13 @@
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M30" s="2" t="b">
         <v>0</v>
@@ -3218,10 +3235,10 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="4">
@@ -3235,10 +3252,10 @@
         <v>39</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="M31" s="1" t="b">
         <v>1</v>
@@ -3256,10 +3273,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="2">
@@ -3270,13 +3287,13 @@
       </c>
       <c r="I32" s="15"/>
       <c r="J32" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M32" s="2" t="b">
         <v>0</v>
@@ -3294,10 +3311,10 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="2">
@@ -3308,13 +3325,13 @@
       </c>
       <c r="I33" s="15"/>
       <c r="J33" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M33" s="2" t="b">
         <v>0</v>
@@ -3331,10 +3348,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="2">
@@ -3369,10 +3386,10 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="2">
@@ -3410,7 +3427,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="15"/>
@@ -3445,7 +3462,7 @@
         <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>39</v>
@@ -3469,10 +3486,10 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="2">
@@ -3503,10 +3520,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G39" s="4">
         <v>25</v>
@@ -3539,10 +3556,10 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="2">
@@ -3575,7 +3592,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="15"/>
@@ -3588,10 +3605,10 @@
         <v>39</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M41" s="2" t="b">
         <v>0</v>
@@ -3610,7 +3627,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="15"/>
@@ -3645,7 +3662,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="15"/>
@@ -3678,7 +3695,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="15"/>
@@ -3711,10 +3728,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="4"/>
@@ -3726,10 +3743,10 @@
         <v>39</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M45" s="1" t="b">
         <v>1</v>
@@ -3750,7 +3767,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="15"/>
@@ -3774,7 +3791,7 @@
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>48</v>
@@ -3789,7 +3806,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="15"/>
@@ -3813,7 +3830,7 @@
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q47" s="2" t="s">
         <v>48</v>
@@ -3828,7 +3845,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="15"/>
@@ -3852,7 +3869,7 @@
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q48" s="2" t="s">
         <v>48</v>
@@ -3867,7 +3884,7 @@
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="21"/>
@@ -3890,7 +3907,7 @@
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
       <c r="P49" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>48</v>
@@ -3905,7 +3922,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="21"/>
@@ -3928,7 +3945,7 @@
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
       <c r="P50" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>48</v>
@@ -3945,7 +3962,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="15"/>
@@ -3958,20 +3975,20 @@
         <v>43</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>48</v>
@@ -3986,7 +4003,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="15"/>
@@ -3996,23 +4013,23 @@
       </c>
       <c r="I52" s="15"/>
       <c r="J52" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>41</v>
@@ -4027,7 +4044,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E53" s="18"/>
       <c r="F53" s="15"/>
@@ -4050,10 +4067,10 @@
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>48</v>
@@ -4070,7 +4087,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="15"/>
@@ -4093,10 +4110,10 @@
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q54" s="2" t="s">
         <v>48</v>
@@ -4113,7 +4130,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="15"/>
@@ -4136,10 +4153,10 @@
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q55" s="2" t="s">
         <v>41</v>
@@ -4156,7 +4173,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="15"/>
@@ -4166,23 +4183,23 @@
       </c>
       <c r="I56" s="15"/>
       <c r="J56" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>48</v>
@@ -4199,7 +4216,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="15"/>
@@ -4222,10 +4239,10 @@
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>41</v>
@@ -4240,10 +4257,10 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="4"/>
@@ -4255,10 +4272,10 @@
         <v>39</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="M58" s="1" t="b">
         <v>1</v>
@@ -4267,7 +4284,7 @@
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
       <c r="Q58" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -4278,10 +4295,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F59" s="16">
         <v>4058001</v>
@@ -4293,16 +4310,16 @@
         <v>39</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="M59" s="1" t="b">
         <v>1</v>
       </c>
       <c r="Q59" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" s="7" customFormat="1" spans="1:18">
@@ -4314,10 +4331,10 @@
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F60" s="22">
         <v>4054001</v>
@@ -4328,23 +4345,25 @@
       </c>
       <c r="I60" s="22"/>
       <c r="J60" s="4" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="M60" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="N60" s="7"/>
+      <c r="N60" s="7" t="s">
+        <v>179</v>
+      </c>
       <c r="Q60" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R60" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" s="7" customFormat="1" spans="1:18">
@@ -4356,10 +4375,10 @@
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F61" s="22">
         <v>4056001</v>
@@ -4370,23 +4389,25 @@
       </c>
       <c r="I61" s="22"/>
       <c r="J61" s="4" t="s">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="M61" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="N61" s="7"/>
+      <c r="N61" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="Q61" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R61" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" s="7" customFormat="1" spans="1:18">
@@ -4398,10 +4419,10 @@
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F62" s="22">
         <v>4059000</v>
@@ -4412,23 +4433,25 @@
       </c>
       <c r="I62" s="22"/>
       <c r="J62" s="4" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="M62" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="N62" s="7"/>
+      <c r="N62" s="7" t="s">
+        <v>179</v>
+      </c>
       <c r="Q62" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R62" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -4439,10 +4462,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F63" s="8">
         <v>10060</v>
@@ -4463,7 +4486,7 @@
         <v>1</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -4474,10 +4497,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H64" s="8">
         <v>2</v>
@@ -4486,16 +4509,16 @@
         <v>39</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="M64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="Q64" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -4506,10 +4529,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F65" s="8">
         <v>4057101</v>
@@ -4521,16 +4544,16 @@
         <v>39</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="M65" s="1" t="b">
         <v>1</v>
       </c>
       <c r="Q65" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -4541,10 +4564,10 @@
         <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H66" s="8">
         <v>4</v>
@@ -4570,10 +4593,10 @@
         <v>1</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H67" s="8">
         <v>1</v>
@@ -4599,10 +4622,10 @@
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H68" s="8">
         <v>3</v>
@@ -4620,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="Q68" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:17">
@@ -4631,28 +4654,31 @@
         <v>1</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H69" s="8">
         <v>3</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="M69" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="N69" s="7" t="s">
+        <v>179</v>
+      </c>
       <c r="Q69" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="1:17">
@@ -4663,10 +4689,10 @@
         <v>1</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H70" s="8">
         <v>1</v>
@@ -4684,7 +4710,7 @@
         <v>1</v>
       </c>
       <c r="Q70" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="201">
   <si>
     <t>id</t>
   </si>
@@ -895,12 +895,6 @@
   </si>
   <si>
     <t>btn_lm</t>
-  </si>
-  <si>
-    <t>1_8</t>
-  </si>
-  <si>
-    <t>0_4062002</t>
   </si>
   <si>
     <t>赛季(app竖版)</t>
@@ -970,7 +964,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1034,6 +1028,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1519,137 +1519,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1720,6 +1720,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1791,6 +1794,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4389,19 +4397,19 @@
       </c>
       <c r="I61" s="22"/>
       <c r="J61" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="M61" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="N61" s="4" t="s">
-        <v>183</v>
+      <c r="N61" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="Q61" s="7" t="s">
         <v>172</v>
@@ -4419,10 +4427,10 @@
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F62" s="22">
         <v>4059000</v>
@@ -4462,10 +4470,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F63" s="8">
         <v>10060</v>
@@ -4497,10 +4505,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H64" s="8">
         <v>2</v>
@@ -4509,10 +4517,10 @@
         <v>39</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M64" s="1" t="b">
         <v>1</v>
@@ -4529,10 +4537,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F65" s="8">
         <v>4057101</v>
@@ -4544,10 +4552,10 @@
         <v>39</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M65" s="1" t="b">
         <v>1</v>
@@ -4563,11 +4571,14 @@
       <c r="B66" s="4">
         <v>1</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>193</v>
+      <c r="C66" s="24">
+        <v>25</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>191</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H66" s="8">
         <v>4</v>
@@ -4592,11 +4603,14 @@
       <c r="B67" s="4">
         <v>1</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>195</v>
+      <c r="C67" s="24">
+        <v>14</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H67" s="8">
         <v>1</v>
@@ -4622,10 +4636,10 @@
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H68" s="8">
         <v>3</v>
@@ -4654,10 +4668,10 @@
         <v>1</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H69" s="8">
         <v>3</v>
@@ -4688,11 +4702,14 @@
       <c r="B70" s="4">
         <v>1</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>201</v>
+      <c r="C70" s="24">
+        <v>19</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>199</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H70" s="8">
         <v>1</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -684,10 +684,10 @@
     <t>Grid (15)</t>
   </si>
   <si>
-    <t>任务(app竖版)</t>
-  </si>
-  <si>
-    <t>Grid (16)</t>
+    <t>成就勋章(app竖版)</t>
+  </si>
+  <si>
+    <t>btn_rwtxz</t>
   </si>
   <si>
     <t>夺宝(横版app版)</t>
@@ -1649,7 +1649,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1705,9 +1705,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -3245,7 +3242,7 @@
       <c r="D31" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="4" t="s">
         <v>112</v>
       </c>
       <c r="F31" s="8"/>
@@ -3253,17 +3250,17 @@
         <v>19</v>
       </c>
       <c r="H31" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="M31" s="1" t="b">
         <v>1</v>
@@ -3688,7 +3685,7 @@
       <c r="L43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M43" s="20" t="b">
+      <c r="M43" s="19" t="b">
         <v>1</v>
       </c>
       <c r="N43" s="2"/>
@@ -3895,11 +3892,11 @@
         <v>143</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="21"/>
-      <c r="H49" s="21">
+      <c r="F49" s="20"/>
+      <c r="H49" s="20">
         <v>5</v>
       </c>
-      <c r="I49" s="21"/>
+      <c r="I49" s="20"/>
       <c r="J49" s="6" t="s">
         <v>39</v>
       </c>
@@ -3933,11 +3930,11 @@
         <v>145</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="21"/>
-      <c r="H50" s="21">
+      <c r="F50" s="20"/>
+      <c r="H50" s="20">
         <v>5</v>
       </c>
-      <c r="I50" s="21"/>
+      <c r="I50" s="20"/>
       <c r="J50" s="6" t="s">
         <v>39</v>
       </c>
@@ -4344,14 +4341,14 @@
       <c r="E60" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F60" s="22">
+      <c r="F60" s="21">
         <v>4054001</v>
       </c>
       <c r="G60" s="7"/>
-      <c r="H60" s="22">
+      <c r="H60" s="21">
         <v>5</v>
       </c>
-      <c r="I60" s="22"/>
+      <c r="I60" s="21"/>
       <c r="J60" s="4" t="s">
         <v>177</v>
       </c>
@@ -4361,7 +4358,7 @@
       <c r="L60" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="M60" s="23" t="b">
+      <c r="M60" s="22" t="b">
         <v>1</v>
       </c>
       <c r="N60" s="7" t="s">
@@ -4388,14 +4385,14 @@
       <c r="E61" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F61" s="22">
+      <c r="F61" s="21">
         <v>4056001</v>
       </c>
       <c r="G61" s="7"/>
-      <c r="H61" s="22">
+      <c r="H61" s="21">
         <v>5</v>
       </c>
-      <c r="I61" s="22"/>
+      <c r="I61" s="21"/>
       <c r="J61" s="4" t="s">
         <v>177</v>
       </c>
@@ -4405,7 +4402,7 @@
       <c r="L61" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="M61" s="23" t="b">
+      <c r="M61" s="22" t="b">
         <v>1</v>
       </c>
       <c r="N61" s="7" t="s">
@@ -4432,14 +4429,14 @@
       <c r="E62" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F62" s="22">
+      <c r="F62" s="21">
         <v>4059000</v>
       </c>
       <c r="G62" s="7"/>
-      <c r="H62" s="22">
+      <c r="H62" s="21">
         <v>5</v>
       </c>
-      <c r="I62" s="22"/>
+      <c r="I62" s="21"/>
       <c r="J62" s="4" t="s">
         <v>177</v>
       </c>
@@ -4449,7 +4446,7 @@
       <c r="L62" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="M62" s="23" t="b">
+      <c r="M62" s="22" t="b">
         <v>1</v>
       </c>
       <c r="N62" s="7" t="s">
@@ -4571,10 +4568,10 @@
       <c r="B66" s="4">
         <v>1</v>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="23">
         <v>25</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="D66" s="23" t="s">
         <v>191</v>
       </c>
       <c r="E66" s="4" t="s">
@@ -4603,10 +4600,10 @@
       <c r="B67" s="4">
         <v>1</v>
       </c>
-      <c r="C67" s="24">
+      <c r="C67" s="23">
         <v>14</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="D67" s="23" t="s">
         <v>193</v>
       </c>
       <c r="E67" s="4" t="s">
@@ -4702,10 +4699,10 @@
       <c r="B70" s="4">
         <v>1</v>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="23">
         <v>19</v>
       </c>
-      <c r="D70" s="24" t="s">
+      <c r="D70" s="23" t="s">
         <v>199</v>
       </c>
       <c r="E70" s="4" t="s">

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GameFunction" sheetId="1" r:id="rId1"/>
@@ -3245,7 +3245,9 @@
       <c r="E31" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="8"/>
+      <c r="F31" s="8">
+        <v>4042004</v>
+      </c>
       <c r="G31" s="4">
         <v>19</v>
       </c>
@@ -4485,7 +4487,7 @@
         <v>47</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="M63" s="1" t="b">
         <v>1</v>

--- a/poker/resources/sample/GameFunction.xlsx
+++ b/poker/resources/sample/GameFunction.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="203">
   <si>
     <t>id</t>
   </si>
@@ -952,6 +952,12 @@
   </si>
   <si>
     <t>BuyOneGetSeven</t>
+  </si>
+  <si>
+    <t>好友同玩</t>
+  </si>
+  <si>
+    <t>显示位置：slot游戏</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2060,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.10833333333333" style="4" customWidth="1"/>
@@ -4727,6 +4733,35 @@
       </c>
       <c r="Q70" s="4" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
+      <c r="A71" s="4">
+        <v>5013</v>
+      </c>
+      <c r="B71" s="4">
+        <v>1</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H71" s="8">
+        <v>2</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="4" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
